--- a/internacional/Contraste_biologia.xlsx
+++ b/internacional/Contraste_biologia.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Capacidad de carga</t>
+          <t>Ciclo del nitrógeno</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -630,37 +630,49 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>1</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ciclo del nitrógeno</t>
+          <t>Ciclos del fósforo y del azufre</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -669,46 +681,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="n">
         <v>8</v>
       </c>
-      <c r="G4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
       <c r="Z4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ciclos del fósforo y del azufre</t>
+          <t>Propagación de enfermedades y control de brotes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,19 +705,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Propagación de enfermedades y control de brotes</t>
+          <t>Equilibrio de Hardy-Weinberg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -743,50 +767,17 @@
       <c r="D6" t="n">
         <v>11</v>
       </c>
-      <c r="G6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1</v>
-      </c>
       <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Equilibrio de Hardy-Weinberg</t>
+          <t>Especiación y macroevolución</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -795,10 +786,52 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" t="n">
         <v>11</v>
       </c>
-      <c r="D7" t="n">
-        <v>11</v>
+      <c r="M7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -810,7 +843,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Especiación y macroevolución</t>
+          <t>Evidencias de la evolución</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -819,25 +852,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -845,10 +881,7 @@
       <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="V8" t="n">
@@ -861,6 +894,12 @@
         <v>1</v>
       </c>
       <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1</v>
       </c>
       <c r="AC8" t="n">
@@ -876,7 +915,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evidencias de la evolución</t>
+          <t>Herencia ligada al sexo, alelos múltiples y poligénica</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -885,28 +924,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>8</v>
+        <v>8.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.5</v>
       </c>
       <c r="M9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -914,7 +950,7 @@
       <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>1</v>
       </c>
       <c r="V9" t="n">
@@ -927,9 +963,6 @@
         <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
         <v>1</v>
       </c>
       <c r="AB9" t="n">
@@ -948,7 +981,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
+          <t>Impulso nervioso y sinapsis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -968,8 +1001,11 @@
       <c r="G10" t="n">
         <v>8.5</v>
       </c>
-      <c r="L10" t="n">
-        <v>11</v>
+      <c r="I10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -977,7 +1013,13 @@
       <c r="P10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
         <v>1</v>
       </c>
       <c r="Y10" t="n">
@@ -986,6 +1028,9 @@
       <c r="Z10" t="n">
         <v>1</v>
       </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
       <c r="AB10" t="n">
         <v>1</v>
       </c>
@@ -993,16 +1038,13 @@
         <v>1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Herencia ligada al sexo, alelos múltiples y poligénica</t>
+          <t>Ingeniería genética y ADN recombinante</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1011,22 +1053,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
         <v>8.5</v>
       </c>
-      <c r="L11" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M11" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1034,19 +1073,22 @@
       <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" t="n">
         <v>1</v>
       </c>
       <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1</v>
       </c>
       <c r="AB11" t="n">
@@ -1065,7 +1107,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Impulso nervioso y sinapsis</t>
+          <t>Inmunidad adaptativa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1074,13 +1116,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G12" t="n">
         <v>8.5</v>
@@ -1088,6 +1130,12 @@
       <c r="I12" t="n">
         <v>9.5</v>
       </c>
+      <c r="L12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>7</v>
+      </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
@@ -1097,25 +1145,19 @@
       <c r="R12" t="n">
         <v>1</v>
       </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
       <c r="Y12" t="n">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
         <v>1</v>
       </c>
       <c r="AD12" t="n">
@@ -1125,7 +1167,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ingeniería genética y ADN recombinante</t>
+          <t>Inmunidad innata</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1139,56 +1181,41 @@
       <c r="D13" t="n">
         <v>9</v>
       </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
       <c r="G13" t="n">
         <v>8.5</v>
       </c>
+      <c r="I13" t="n">
+        <v>9.5</v>
+      </c>
       <c r="M13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
-      <c r="V13" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
       <c r="Y13" t="n">
         <v>1</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1</v>
-      </c>
       <c r="AB13" t="n">
         <v>1</v>
       </c>
-      <c r="AC13" t="n">
-        <v>1</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Inmunidad adaptativa</t>
+          <t>Nutrición mineral de las plantas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1197,19 +1224,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>9.5</v>
@@ -1220,22 +1247,16 @@
       <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
       <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
       <c r="Y14" t="n">
         <v>1</v>
       </c>
       <c r="Z14" t="n">
         <v>1</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>1</v>
       </c>
       <c r="AD14" t="n">
@@ -1245,7 +1266,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Inmunidad innata</t>
+          <t>Regulación de la expresión génica</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1259,18 +1280,36 @@
       <c r="D15" t="n">
         <v>9</v>
       </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
       <c r="G15" t="n">
         <v>8.5</v>
       </c>
       <c r="I15" t="n">
         <v>9.5</v>
       </c>
+      <c r="J15" t="n">
+        <v>9</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
       <c r="W15" t="n">
         <v>1</v>
       </c>
@@ -1280,17 +1319,26 @@
       <c r="Z15" t="n">
         <v>1</v>
       </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
       <c r="AB15" t="n">
         <v>1</v>
       </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
       <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nutrición mineral de las plantas</t>
+          <t>Relación superficie-volumen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1299,19 +1347,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
         <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4</v>
+        <v>8.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7</v>
       </c>
       <c r="L16" t="n">
         <v>9.5</v>
@@ -1325,13 +1373,16 @@
       <c r="U16" t="n">
         <v>1</v>
       </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
       <c r="Y16" t="n">
         <v>1</v>
       </c>
       <c r="Z16" t="n">
         <v>1</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AB16" t="n">
         <v>1</v>
       </c>
       <c r="AD16" t="n">
@@ -1341,7 +1392,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Regulación de la expresión génica</t>
+          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1355,6 +1406,9 @@
       <c r="D17" t="n">
         <v>9</v>
       </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
       <c r="F17" t="n">
         <v>8</v>
       </c>
@@ -1365,10 +1419,13 @@
         <v>9.5</v>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -1377,9 +1434,6 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
@@ -1413,7 +1467,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Relación superficie-volumen</t>
+          <t>Sistema endocrino y hormonas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1422,10 +1476,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
       </c>
       <c r="F18" t="n">
         <v>8</v>
@@ -1433,21 +1490,36 @@
       <c r="G18" t="n">
         <v>8.5</v>
       </c>
+      <c r="I18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
       <c r="L18" t="n">
         <v>9.5</v>
       </c>
+      <c r="M18" t="n">
+        <v>7</v>
+      </c>
       <c r="O18" t="n">
         <v>1</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
       <c r="U18" t="n">
         <v>1</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
       <c r="Y18" t="n">
         <v>1</v>
       </c>
@@ -1457,14 +1529,20 @@
       <c r="AB18" t="n">
         <v>1</v>
       </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
       <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Modelo estímulo-respuesta y retroalimentación negativa</t>
+          <t>Sistema inmunitario</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1478,9 +1556,6 @@
       <c r="D19" t="n">
         <v>9</v>
       </c>
-      <c r="E19" t="n">
-        <v>8</v>
-      </c>
       <c r="F19" t="n">
         <v>8</v>
       </c>
@@ -1490,9 +1565,15 @@
       <c r="I19" t="n">
         <v>9.5</v>
       </c>
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
       <c r="L19" t="n">
         <v>9.5</v>
       </c>
+      <c r="M19" t="n">
+        <v>7</v>
+      </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
@@ -1502,6 +1583,9 @@
       <c r="R19" t="n">
         <v>1</v>
       </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
       <c r="U19" t="n">
         <v>1</v>
       </c>
@@ -1514,13 +1598,7 @@
       <c r="Z19" t="n">
         <v>1</v>
       </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="n">
         <v>1</v>
       </c>
       <c r="AD19" t="n">
@@ -1533,7 +1611,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sistema endocrino y hormonas</t>
+          <t>Transmisión de patógenos</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1547,17 +1625,14 @@
       <c r="D20" t="n">
         <v>9</v>
       </c>
-      <c r="E20" t="n">
-        <v>8</v>
-      </c>
       <c r="F20" t="n">
         <v>8</v>
       </c>
       <c r="G20" t="n">
         <v>8.5</v>
       </c>
-      <c r="I20" t="n">
-        <v>9.5</v>
+      <c r="J20" t="n">
+        <v>9</v>
       </c>
       <c r="L20" t="n">
         <v>9.5</v>
@@ -1568,7 +1643,7 @@
       <c r="P20" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
@@ -1586,23 +1661,14 @@
       <c r="Z20" t="n">
         <v>1</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sistema inmunitario</t>
+          <t>Virus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1622,12 +1688,6 @@
       <c r="G21" t="n">
         <v>8.5</v>
       </c>
-      <c r="I21" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>9</v>
-      </c>
       <c r="L21" t="n">
         <v>9.5</v>
       </c>
@@ -1637,12 +1697,6 @@
       <c r="P21" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
@@ -1655,191 +1709,179 @@
       <c r="Z21" t="n">
         <v>1</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Termorregulación</t>
+          <t>Especies clave</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>alineado</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>10</v>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" t="n">
-        <v>8</v>
-      </c>
-      <c r="G22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
+          <t>no_aplica</t>
+        </is>
       </c>
       <c r="W22" t="n">
         <v>1</v>
       </c>
-      <c r="Y22" t="n">
-        <v>1</v>
-      </c>
       <c r="Z22" t="n">
         <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Transmisión de patógenos</t>
+          <t>Biomas y clasificación de ambientes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
-      </c>
-      <c r="D23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
-      <c r="G23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>9</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="I23" t="n">
         <v>9.5</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="R23" t="n">
         <v>1</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1</v>
-      </c>
       <c r="Z23" t="n">
         <v>1</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Virus</t>
+          <t>Ciclo de vida de los animales</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
-      </c>
-      <c r="D24" t="n">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="W24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1</v>
-      </c>
       <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Especies clave</t>
+          <t>Competencia por recursos</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no_aplica</t>
-        </is>
+          <t>previo</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
       </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
       <c r="Z25" t="n">
         <v>1</v>
       </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
       <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomas y clasificación de ambientes</t>
+          <t>Ecosistemas naturales, rurales y urbanos</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1848,24 +1890,18 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
-      </c>
-      <c r="I26" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1</v>
-      </c>
       <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>1</v>
       </c>
       <c r="AE26" t="n">
@@ -1875,7 +1911,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ciclo de vida de los animales</t>
+          <t>Grupos de plantas</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1886,38 +1922,29 @@
       <c r="C27" t="n">
         <v>3</v>
       </c>
-      <c r="E27" t="n">
-        <v>2</v>
-      </c>
       <c r="F27" t="n">
         <v>8</v>
       </c>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
       <c r="I27" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Competencia por recursos</t>
+          <t>Grupos de vertebrados</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1926,61 +1953,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
         <v>6</v>
       </c>
-      <c r="I28" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>9</v>
-      </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ecosistemas naturales, rurales y urbanos</t>
+          <t>Invertebrados e insectos</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1992,25 +1986,31 @@
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>11</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grupos de plantas</t>
+          <t>Partes de la planta y sus funciones</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2019,17 +2019,44 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
       </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
       <c r="Z30" t="n">
         <v>1</v>
       </c>
@@ -2037,13 +2064,19 @@
         <v>1</v>
       </c>
       <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Grupos de vertebrados</t>
+          <t>Grandes grupos taxonómicos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2058,22 +2091,31 @@
         <v>8</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
         <v>6</v>
       </c>
+      <c r="J31" t="n">
+        <v>7</v>
+      </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
       <c r="AB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Invertebrados e insectos</t>
+          <t>Reproducción sexual de las plantas con flor</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2082,34 +2124,43 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8</v>
       </c>
       <c r="F32" t="n">
         <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>7</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="U32" t="n">
+      <c r="Z32" t="n">
         <v>1</v>
       </c>
       <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Partes de la planta y sus funciones</t>
+          <t>Sistema digestivo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2118,7 +2169,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
@@ -2127,7 +2178,10 @@
         <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
       </c>
       <c r="K33" t="n">
         <v>9</v>
@@ -2135,12 +2189,12 @@
       <c r="L33" t="n">
         <v>9.5</v>
       </c>
+      <c r="M33" t="n">
+        <v>7</v>
+      </c>
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
@@ -2150,9 +2204,6 @@
       <c r="W33" t="n">
         <v>1</v>
       </c>
-      <c r="Y33" t="n">
-        <v>1</v>
-      </c>
       <c r="Z33" t="n">
         <v>1</v>
       </c>
@@ -2163,16 +2214,13 @@
         <v>1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Grandes grupos taxonómicos</t>
+          <t>Sistema excretor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2181,34 +2229,52 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
         <v>8</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.5</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
       <c r="Z34" t="n">
         <v>1</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1</v>
-      </c>
       <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Reproducción sexual de las plantas con flor</t>
+          <t>Sistema locomotor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2217,10 +2283,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
-      </c>
-      <c r="E35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
         <v>8</v>
@@ -2229,110 +2292,119 @@
         <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="Z35" t="n">
         <v>1</v>
       </c>
-      <c r="AC35" t="n">
-        <v>1</v>
-      </c>
       <c r="AD35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sistema digestivo</t>
+          <t>Acervo génico y frecuencias alélicas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11</v>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="n">
-        <v>5</v>
-      </c>
-      <c r="K36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J36" t="n">
         <v>9</v>
       </c>
       <c r="L36" t="n">
+        <v>11</v>
+      </c>
+      <c r="M36" t="n">
         <v>9.5</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="T36" t="n">
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
         <v>1</v>
       </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
       <c r="W36" t="n">
         <v>1</v>
       </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
       <c r="Z36" t="n">
         <v>1</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AA36" t="n">
         <v>1</v>
       </c>
       <c r="AD36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sistema excretor</t>
+          <t>Adaptaciones conductuales</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="n">
         <v>4</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
       </c>
-      <c r="G37" t="n">
-        <v>8.5</v>
-      </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
       </c>
-      <c r="P37" t="n">
-        <v>1</v>
-      </c>
       <c r="U37" t="n">
         <v>1</v>
       </c>
@@ -2342,56 +2414,80 @@
       <c r="Y37" t="n">
         <v>1</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>1</v>
       </c>
       <c r="AC37" t="n">
         <v>1</v>
       </c>
       <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sistema locomotor</t>
+          <t>Adaptaciones estructurales</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>11</v>
+      </c>
+      <c r="E38" t="n">
         <v>4</v>
       </c>
       <c r="F38" t="n">
         <v>8</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>11</v>
+      </c>
+      <c r="M38" t="n">
+        <v>7</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
       </c>
-      <c r="P38" t="n">
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
       </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
       <c r="AD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Acervo génico y frecuencias alélicas</t>
+          <t>ADN y cromosomas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2400,25 +2496,34 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>9</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J39" t="n">
         <v>7</v>
       </c>
-      <c r="D39" t="n">
-        <v>11</v>
-      </c>
-      <c r="F39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G39" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>9</v>
-      </c>
       <c r="L39" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M39" t="n">
-        <v>9.5</v>
+        <v>7</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -2426,6 +2531,9 @@
       <c r="P39" t="n">
         <v>1</v>
       </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
@@ -2444,7 +2552,10 @@
       <c r="Z39" t="n">
         <v>1</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
         <v>1</v>
       </c>
       <c r="AD39" t="n">
@@ -2457,7 +2568,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Adaptaciones conductuales</t>
+          <t>Agricultura y seguridad alimentaria</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2466,52 +2577,55 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
         <v>10</v>
       </c>
-      <c r="E40" t="n">
-        <v>4</v>
-      </c>
       <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="I40" t="n">
-        <v>3</v>
+      <c r="G40" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" t="n">
+        <v>8</v>
       </c>
       <c r="L40" t="n">
         <v>11</v>
       </c>
+      <c r="M40" t="n">
+        <v>7</v>
+      </c>
       <c r="O40" t="n">
         <v>1</v>
       </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
       <c r="U40" t="n">
         <v>1</v>
       </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
         <v>1</v>
       </c>
       <c r="Y40" t="n">
         <v>1</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="Z40" t="n">
         <v>1</v>
       </c>
       <c r="AC40" t="n">
         <v>1</v>
       </c>
       <c r="AD40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE40" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Adaptaciones estructurales</t>
+          <t>Amenazas a la biodiversidad</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2523,33 +2637,54 @@
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
-      </c>
-      <c r="E41" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F41" t="n">
         <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" t="n">
+        <v>8</v>
       </c>
       <c r="L41" t="n">
         <v>11</v>
       </c>
+      <c r="M41" t="n">
+        <v>7</v>
+      </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
       <c r="W41" t="n">
         <v>1</v>
       </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
       <c r="Y41" t="n">
         <v>1</v>
       </c>
       <c r="Z41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
         <v>1</v>
       </c>
       <c r="AC41" t="n">
@@ -2565,7 +2700,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ADN y cromosomas</t>
+          <t>ATP y energía en los sistemas vivos</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2577,22 +2712,19 @@
         <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
-      </c>
-      <c r="E42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I42" t="n">
         <v>9.5</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L42" t="n">
         <v>9.5</v>
@@ -2600,9 +2732,6 @@
       <c r="M42" t="n">
         <v>9.5</v>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
       <c r="O42" t="n">
         <v>1</v>
       </c>
@@ -2624,10 +2753,16 @@
       <c r="W42" t="n">
         <v>1</v>
       </c>
+      <c r="X42" t="n">
+        <v>1</v>
+      </c>
       <c r="Y42" t="n">
         <v>1</v>
       </c>
       <c r="Z42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA42" t="n">
         <v>1</v>
       </c>
       <c r="AB42" t="n">
@@ -2646,7 +2781,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Agricultura y seguridad alimentaria</t>
+          <t>Atributos de las poblaciones</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2655,19 +2790,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
-      </c>
-      <c r="L43" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -2675,10 +2807,7 @@
       <c r="P43" t="n">
         <v>1</v>
       </c>
-      <c r="U43" t="n">
-        <v>1</v>
-      </c>
-      <c r="X43" t="n">
+      <c r="W43" t="n">
         <v>1</v>
       </c>
       <c r="Y43" t="n">
@@ -2687,17 +2816,20 @@
       <c r="Z43" t="n">
         <v>1</v>
       </c>
+      <c r="AB43" t="n">
+        <v>1</v>
+      </c>
       <c r="AC43" t="n">
         <v>1</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AE43" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Amenazas a la biodiversidad</t>
+          <t>Biodiversidad</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2709,19 +2841,31 @@
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L44" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>7</v>
+      </c>
+      <c r="K44" t="n">
+        <v>8</v>
+      </c>
+      <c r="M44" t="n">
+        <v>7</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
@@ -2732,7 +2876,10 @@
       <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="U44" t="n">
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="V44" t="n">
         <v>1</v>
       </c>
       <c r="W44" t="n">
@@ -2745,9 +2892,6 @@
         <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
         <v>1</v>
       </c>
       <c r="AC44" t="n">
@@ -2763,7 +2907,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ATP y energía en los sistemas vivos</t>
+          <t>Biomoléculas</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2778,30 +2922,24 @@
         <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
         <v>8.5</v>
       </c>
-      <c r="I45" t="n">
-        <v>9.5</v>
-      </c>
       <c r="J45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L45" t="n">
         <v>9.5</v>
       </c>
       <c r="M45" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
         <v>1</v>
       </c>
       <c r="S45" t="n">
@@ -2844,7 +2982,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Atributos de las poblaciones</t>
+          <t>Biotecnología microbiana</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2853,26 +2991,35 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F46" t="n">
         <v>8</v>
       </c>
-      <c r="G46" t="n">
-        <v>8.5</v>
+      <c r="I46" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M46" t="n">
+        <v>7</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
         <v>1</v>
       </c>
       <c r="W46" t="n">
         <v>1</v>
       </c>
+      <c r="X46" t="n">
+        <v>1</v>
+      </c>
       <c r="Y46" t="n">
         <v>1</v>
       </c>
@@ -2883,6 +3030,9 @@
         <v>1</v>
       </c>
       <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1</v>
       </c>
       <c r="AE46" t="n">
@@ -2892,7 +3042,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Biodiversidad</t>
+          <t>Biotecnología vegetal y agroindustria</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2901,31 +3051,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
         <v>11</v>
       </c>
-      <c r="E47" t="n">
-        <v>6</v>
-      </c>
       <c r="F47" t="n">
         <v>8</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
-      </c>
-      <c r="I47" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="M47" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
@@ -2933,18 +3071,9 @@
       <c r="P47" t="n">
         <v>1</v>
       </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1</v>
-      </c>
       <c r="V47" t="n">
         <v>1</v>
       </c>
-      <c r="W47" t="n">
-        <v>1</v>
-      </c>
       <c r="X47" t="n">
         <v>1</v>
       </c>
@@ -2952,6 +3081,9 @@
         <v>1</v>
       </c>
       <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
         <v>1</v>
       </c>
       <c r="AC47" t="n">
@@ -2967,7 +3099,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Biomoléculas</t>
+          <t>Cadena alimentaria</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2976,73 +3108,49 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
         <v>10</v>
       </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G48" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J48" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
       </c>
       <c r="L48" t="n">
         <v>9.5</v>
       </c>
       <c r="M48" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="P48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1</v>
-      </c>
       <c r="U48" t="n">
         <v>1</v>
       </c>
-      <c r="V48" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1</v>
-      </c>
       <c r="Y48" t="n">
         <v>1</v>
       </c>
       <c r="Z48" t="n">
         <v>1</v>
       </c>
-      <c r="AA48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1</v>
-      </c>
       <c r="AD48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE48" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Biotecnología microbiana</t>
+          <t>Cambio climático y seres vivos</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3051,58 +3159,52 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
         <v>8</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L49" t="n">
         <v>9.5</v>
       </c>
       <c r="M49" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
-      <c r="V49" t="n">
+      <c r="U49" t="n">
         <v>1</v>
       </c>
       <c r="W49" t="n">
         <v>1</v>
       </c>
-      <c r="X49" t="n">
-        <v>1</v>
-      </c>
       <c r="Y49" t="n">
         <v>1</v>
       </c>
       <c r="Z49" t="n">
         <v>1</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AA49" t="n">
         <v>1</v>
       </c>
       <c r="AC49" t="n">
         <v>1</v>
       </c>
       <c r="AD49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE49" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Biotecnología vegetal y agroindustria</t>
+          <t>Célula animal y célula vegetal</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3114,27 +3216,39 @@
         <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7</v>
       </c>
       <c r="F50" t="n">
         <v>8</v>
       </c>
       <c r="G50" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I50" t="n">
+        <v>7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>7</v>
+      </c>
+      <c r="K50" t="n">
+        <v>9</v>
+      </c>
+      <c r="L50" t="n">
+        <v>9.5</v>
       </c>
       <c r="M50" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="P50" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1</v>
-      </c>
-      <c r="X50" t="n">
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
         <v>1</v>
       </c>
       <c r="Y50" t="n">
@@ -3150,16 +3264,13 @@
         <v>1</v>
       </c>
       <c r="AD50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE50" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cadena alimentaria</t>
+          <t>Célula procariota y eucariota</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3168,46 +3279,70 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F51" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="L51" t="n">
+        <v>11</v>
+      </c>
+      <c r="M51" t="n">
         <v>9.5</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
       <c r="U51" t="n">
         <v>1</v>
       </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
       <c r="Y51" t="n">
         <v>1</v>
       </c>
       <c r="Z51" t="n">
         <v>1</v>
       </c>
+      <c r="AA51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1</v>
+      </c>
       <c r="AD51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE51" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cambio climático y seres vivos</t>
+          <t>Ciclo de vida de las plantas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3216,46 +3351,43 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2</v>
       </c>
       <c r="F52" t="n">
         <v>8</v>
       </c>
-      <c r="L52" t="n">
-        <v>9.5</v>
+      <c r="G52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="U52" t="n">
-        <v>1</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1</v>
-      </c>
       <c r="Y52" t="n">
         <v>1</v>
       </c>
       <c r="Z52" t="n">
         <v>1</v>
       </c>
-      <c r="AA52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1</v>
-      </c>
       <c r="AD52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE52" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Célula animal y célula vegetal</t>
+          <t>Papel de los seres vivos en el ciclo del agua</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3264,33 +3396,27 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
-      </c>
-      <c r="E53" t="n">
-        <v>7</v>
-      </c>
-      <c r="F53" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
         <v>8</v>
-      </c>
-      <c r="G53" t="n">
-        <v>6</v>
-      </c>
-      <c r="I53" t="n">
-        <v>7</v>
-      </c>
-      <c r="K53" t="n">
-        <v>9</v>
       </c>
       <c r="L53" t="n">
         <v>9.5</v>
       </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
-      <c r="T53" t="n">
+      <c r="M53" t="n">
+        <v>7</v>
+      </c>
+      <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
@@ -3299,23 +3425,17 @@
       <c r="Y53" t="n">
         <v>1</v>
       </c>
-      <c r="Z53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1</v>
-      </c>
       <c r="AD53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE53" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Célula procariota y eucariota</t>
+          <t>Ciclos del carbono y del oxígeno</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3333,16 +3453,22 @@
         <v>8</v>
       </c>
       <c r="G54" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
+      <c r="K54" t="n">
+        <v>8</v>
+      </c>
+      <c r="L54" t="n">
         <v>9.5</v>
       </c>
-      <c r="L54" t="n">
-        <v>11</v>
-      </c>
       <c r="M54" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
@@ -3353,6 +3479,9 @@
       <c r="R54" t="n">
         <v>1</v>
       </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
       <c r="U54" t="n">
         <v>1</v>
       </c>
@@ -3360,6 +3489,9 @@
         <v>1</v>
       </c>
       <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" t="n">
         <v>1</v>
       </c>
       <c r="Y54" t="n">
@@ -3387,7 +3519,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las plantas</t>
+          <t>Circulación e intercambio capilar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3396,43 +3528,49 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
         <v>11</v>
       </c>
-      <c r="E55" t="n">
-        <v>2</v>
-      </c>
       <c r="F55" t="n">
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" t="n">
-        <v>2</v>
+        <v>8.5</v>
+      </c>
+      <c r="L55" t="n">
+        <v>9.5</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
       <c r="Y55" t="n">
         <v>1</v>
       </c>
       <c r="Z55" t="n">
         <v>1</v>
       </c>
+      <c r="AC55" t="n">
+        <v>1</v>
+      </c>
       <c r="AD55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE55" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Papel de los seres vivos en el ciclo del agua</t>
+          <t>Clasificación de seres vivos por sus rasgos</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3441,40 +3579,52 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>11</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
         <v>7</v>
       </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="G56" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I56" t="n">
-        <v>5</v>
-      </c>
-      <c r="L56" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="n">
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="Y56" t="n">
         <v>1</v>
       </c>
-      <c r="AD56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE56" t="n">
+      <c r="Z56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC56" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ciclos del carbono y del oxígeno</t>
+          <t>Clasificación jerárquica y nomenclatura</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3483,62 +3633,38 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>11</v>
+      </c>
+      <c r="E57" t="n">
         <v>6</v>
       </c>
-      <c r="D57" t="n">
-        <v>9</v>
-      </c>
-      <c r="F57" t="n">
-        <v>8</v>
-      </c>
       <c r="G57" t="n">
-        <v>6</v>
-      </c>
-      <c r="I57" t="n">
-        <v>5</v>
-      </c>
-      <c r="K57" t="n">
-        <v>9</v>
-      </c>
-      <c r="L57" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7</v>
       </c>
       <c r="M57" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
       </c>
-      <c r="R57" t="n">
-        <v>1</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1</v>
-      </c>
       <c r="V57" t="n">
         <v>1</v>
       </c>
       <c r="W57" t="n">
         <v>1</v>
       </c>
-      <c r="X57" t="n">
-        <v>1</v>
-      </c>
       <c r="Y57" t="n">
         <v>1</v>
       </c>
       <c r="Z57" t="n">
         <v>1</v>
       </c>
-      <c r="AA57" t="n">
-        <v>1</v>
-      </c>
       <c r="AB57" t="n">
         <v>1</v>
       </c>
@@ -3546,16 +3672,13 @@
         <v>1</v>
       </c>
       <c r="AD57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE57" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Circulación e intercambio capilar</t>
+          <t>Concepto de especie</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3564,26 +3687,26 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" t="n">
         <v>11</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G58" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7</v>
       </c>
       <c r="L58" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
       <c r="U58" t="n">
         <v>1</v>
       </c>
@@ -3600,13 +3723,16 @@
         <v>1</v>
       </c>
       <c r="AD58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE58" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Clasificación de seres vivos por sus rasgos</t>
+          <t>Conservación de la biodiversidad</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3620,25 +3746,40 @@
       <c r="D59" t="n">
         <v>11</v>
       </c>
-      <c r="E59" t="n">
-        <v>2</v>
-      </c>
       <c r="F59" t="n">
         <v>8</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="J59" t="n">
+        <v>7</v>
+      </c>
+      <c r="K59" t="n">
+        <v>8</v>
+      </c>
+      <c r="L59" t="n">
+        <v>11</v>
+      </c>
+      <c r="M59" t="n">
+        <v>7</v>
       </c>
       <c r="O59" t="n">
         <v>1</v>
       </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
       <c r="R59" t="n">
         <v>1</v>
       </c>
-      <c r="W59" t="n">
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
         <v>1</v>
       </c>
       <c r="Y59" t="n">
@@ -3647,17 +3788,17 @@
       <c r="Z59" t="n">
         <v>1</v>
       </c>
-      <c r="AB59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC59" t="n">
+      <c r="AD59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE59" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Clasificación jerárquica y nomenclatura</t>
+          <t>Conservación e inocuidad de los alimentos</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3666,49 +3807,25 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
         <v>11</v>
       </c>
-      <c r="E60" t="n">
-        <v>6</v>
-      </c>
-      <c r="G60" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M60" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P60" t="n">
-        <v>1</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y60" t="n">
+      <c r="F60" t="n">
+        <v>8</v>
+      </c>
+      <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="Z60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD60" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Concepto de especie</t>
+          <t>Contagio y prevención de enfermedades</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3717,23 +3834,32 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F61" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>9</v>
       </c>
       <c r="L61" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="O61" t="n">
         <v>1</v>
       </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
       <c r="U61" t="n">
         <v>1</v>
       </c>
@@ -3746,20 +3872,14 @@
       <c r="Z61" t="n">
         <v>1</v>
       </c>
-      <c r="AC61" t="n">
-        <v>1</v>
-      </c>
       <c r="AD61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE61" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Conservación de la biodiversidad</t>
+          <t>Contaminación y sus efectos en los seres vivos</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3771,55 +3891,43 @@
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
-      </c>
-      <c r="F62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G62" t="n">
         <v>6</v>
       </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>8</v>
       </c>
-      <c r="J62" t="n">
-        <v>9</v>
-      </c>
       <c r="L62" t="n">
-        <v>11</v>
-      </c>
-      <c r="O62" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>1</v>
+        <v>9.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7</v>
       </c>
       <c r="U62" t="n">
         <v>1</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="W62" t="n">
         <v>1</v>
       </c>
       <c r="Z62" t="n">
         <v>1</v>
       </c>
+      <c r="AB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1</v>
+      </c>
       <c r="AD62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE62" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Conservación e inocuidad de los alimentos</t>
+          <t>Crecimiento poblacional</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3828,7 +3936,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
         <v>11</v>
@@ -3836,17 +3944,44 @@
       <c r="F63" t="n">
         <v>8</v>
       </c>
+      <c r="G63" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>9</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7</v>
+      </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1</v>
+      </c>
       <c r="Z63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE63" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Contagio y prevención de enfermedades</t>
+          <t>Depredación</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3855,52 +3990,55 @@
         </is>
       </c>
       <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>11</v>
+      </c>
+      <c r="F64" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G64" t="n">
         <v>2</v>
       </c>
-      <c r="D64" t="n">
+      <c r="I64" t="n">
+        <v>5</v>
+      </c>
+      <c r="J64" t="n">
         <v>9</v>
       </c>
-      <c r="F64" t="n">
-        <v>8</v>
-      </c>
-      <c r="G64" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K64" t="n">
-        <v>9</v>
-      </c>
-      <c r="L64" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O64" t="n">
         <v>1</v>
       </c>
       <c r="P64" t="n">
         <v>1</v>
       </c>
-      <c r="T64" t="n">
-        <v>1</v>
-      </c>
-      <c r="U64" t="n">
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
         <v>1</v>
       </c>
       <c r="W64" t="n">
         <v>1</v>
       </c>
-      <c r="Y64" t="n">
-        <v>1</v>
-      </c>
       <c r="Z64" t="n">
         <v>1</v>
       </c>
-      <c r="AD64" t="n">
+      <c r="AB64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE64" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Contaminación y sus efectos en los seres vivos</t>
+          <t>Diferenciación y especialización celular</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3909,40 +4047,76 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E65" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" t="n">
+        <v>10.5</v>
       </c>
       <c r="G65" t="n">
         <v>6</v>
       </c>
+      <c r="J65" t="n">
+        <v>7</v>
+      </c>
+      <c r="K65" t="n">
+        <v>9</v>
+      </c>
       <c r="L65" t="n">
         <v>9.5</v>
       </c>
+      <c r="M65" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
       <c r="U65" t="n">
         <v>1</v>
       </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
       <c r="W65" t="n">
         <v>1</v>
       </c>
+      <c r="X65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1</v>
+      </c>
       <c r="Z65" t="n">
         <v>1</v>
       </c>
+      <c r="AA65" t="n">
+        <v>1</v>
+      </c>
       <c r="AB65" t="n">
         <v>1</v>
       </c>
-      <c r="AC65" t="n">
-        <v>1</v>
-      </c>
       <c r="AD65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE65" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Crecimiento poblacional</t>
+          <t>Difusión y ósmosis</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3954,17 +4128,20 @@
         <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F66" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G66" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
         <v>9</v>
       </c>
+      <c r="L66" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O66" t="n">
         <v>1</v>
       </c>
@@ -3974,16 +4151,25 @@
       <c r="S66" t="n">
         <v>1</v>
       </c>
+      <c r="U66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1</v>
+      </c>
       <c r="Y66" t="n">
         <v>1</v>
       </c>
       <c r="Z66" t="n">
         <v>1</v>
       </c>
-      <c r="AA66" t="n">
+      <c r="AB66" t="n">
         <v>1</v>
       </c>
       <c r="AC66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD66" t="n">
         <v>1</v>
       </c>
       <c r="AE66" t="n">
@@ -3993,7 +4179,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Depredación</t>
+          <t>Digestión química y absorción de nutrientes</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4002,33 +4188,33 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="F67" t="n">
+        <v>8</v>
+      </c>
+      <c r="G67" t="n">
         <v>4</v>
-      </c>
-      <c r="D67" t="n">
-        <v>11</v>
-      </c>
-      <c r="F67" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G67" t="n">
-        <v>2</v>
       </c>
       <c r="I67" t="n">
         <v>5</v>
       </c>
       <c r="J67" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="L67" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M67" t="n">
+        <v>7</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="P67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S67" t="n">
+      <c r="U67" t="n">
         <v>1</v>
       </c>
       <c r="W67" t="n">
@@ -4043,14 +4229,14 @@
       <c r="AC67" t="n">
         <v>1</v>
       </c>
-      <c r="AE67" t="n">
+      <c r="AD67" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Diferenciación y especialización celular</t>
+          <t>Diversidad genética de poblaciones</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4059,28 +4245,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
-      </c>
-      <c r="E68" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F68" t="n">
         <v>10.5</v>
       </c>
       <c r="G68" t="n">
-        <v>6</v>
-      </c>
-      <c r="K68" t="n">
-        <v>9</v>
+        <v>8.5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>7</v>
       </c>
       <c r="L68" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M68" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -4088,31 +4268,25 @@
       <c r="P68" t="n">
         <v>1</v>
       </c>
-      <c r="T68" t="n">
+      <c r="S68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
         <v>1</v>
       </c>
-      <c r="V68" t="n">
-        <v>1</v>
-      </c>
       <c r="W68" t="n">
         <v>1</v>
       </c>
-      <c r="X68" t="n">
-        <v>1</v>
-      </c>
       <c r="Y68" t="n">
         <v>1</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
       </c>
-      <c r="AA68" t="n">
-        <v>1</v>
-      </c>
       <c r="AB68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC68" t="n">
         <v>1</v>
       </c>
       <c r="AD68" t="n">
@@ -4125,7 +4299,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Difusión y ósmosis</t>
+          <t>Ecosistemas acuáticos y marinos</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4134,45 +4308,18 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
         <v>9</v>
       </c>
-      <c r="F69" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G69" t="n">
-        <v>6</v>
-      </c>
-      <c r="J69" t="n">
-        <v>9</v>
-      </c>
       <c r="L69" t="n">
         <v>9.5</v>
       </c>
-      <c r="O69" t="n">
-        <v>1</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1</v>
-      </c>
-      <c r="S69" t="n">
-        <v>1</v>
-      </c>
       <c r="U69" t="n">
         <v>1</v>
       </c>
-      <c r="W69" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>1</v>
-      </c>
       <c r="Z69" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB69" t="n">
         <v>1</v>
       </c>
       <c r="AC69" t="n">
@@ -4188,7 +4335,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Digestión química y absorción de nutrientes</t>
+          <t>Energía de los alimentos y balance energético</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4197,7 +4344,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
         <v>10</v>
@@ -4206,10 +4353,7 @@
         <v>8</v>
       </c>
       <c r="G70" t="n">
-        <v>4</v>
-      </c>
-      <c r="I70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L70" t="n">
         <v>9.5</v>
@@ -4220,7 +4364,7 @@
       <c r="U70" t="n">
         <v>1</v>
       </c>
-      <c r="W70" t="n">
+      <c r="X70" t="n">
         <v>1</v>
       </c>
       <c r="Z70" t="n">
@@ -4239,7 +4383,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Diversidad genética de poblaciones</t>
+          <t>Enfermedades infecciosas y no infecciosas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4248,22 +4392,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F71" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="J71" t="n">
         <v>9</v>
       </c>
+      <c r="K71" t="n">
+        <v>9</v>
+      </c>
       <c r="L71" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -4274,12 +4421,18 @@
       <c r="S71" t="n">
         <v>1</v>
       </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
       <c r="U71" t="n">
         <v>1</v>
       </c>
       <c r="W71" t="n">
         <v>1</v>
       </c>
+      <c r="X71" t="n">
+        <v>1</v>
+      </c>
       <c r="Y71" t="n">
         <v>1</v>
       </c>
@@ -4293,16 +4446,13 @@
         <v>1</v>
       </c>
       <c r="AD71" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE71" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ecosistemas acuáticos y marinos</t>
+          <t>Enzimas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4311,18 +4461,60 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F72" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>6</v>
+      </c>
+      <c r="I72" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>7</v>
       </c>
       <c r="L72" t="n">
         <v>9.5</v>
       </c>
+      <c r="M72" t="n">
+        <v>7</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
       <c r="U72" t="n">
         <v>1</v>
       </c>
+      <c r="W72" t="n">
+        <v>1</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1</v>
+      </c>
       <c r="Z72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB72" t="n">
         <v>1</v>
       </c>
       <c r="AC72" t="n">
@@ -4338,7 +4530,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Energía de los alimentos y balance energético</t>
+          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4347,46 +4539,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F73" t="n">
         <v>8</v>
       </c>
-      <c r="G73" t="n">
-        <v>6</v>
-      </c>
-      <c r="L73" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="U73" t="n">
-        <v>1</v>
-      </c>
-      <c r="X73" t="n">
+      <c r="Y73" t="n">
         <v>1</v>
       </c>
       <c r="Z73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD73" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enfermedades infecciosas y no infecciosas</t>
+          <t>Estructura del ADN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4395,47 +4569,50 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G74" t="n">
         <v>6</v>
       </c>
+      <c r="I74" t="n">
+        <v>9.5</v>
+      </c>
       <c r="J74" t="n">
         <v>9</v>
       </c>
-      <c r="K74" t="n">
-        <v>9</v>
-      </c>
       <c r="L74" t="n">
         <v>9.5</v>
       </c>
+      <c r="M74" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O74" t="n">
         <v>1</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
       </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
       <c r="S74" t="n">
         <v>1</v>
       </c>
-      <c r="T74" t="n">
-        <v>1</v>
-      </c>
       <c r="U74" t="n">
         <v>1</v>
       </c>
+      <c r="V74" t="n">
+        <v>1</v>
+      </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
-      <c r="X74" t="n">
-        <v>1</v>
-      </c>
       <c r="Y74" t="n">
         <v>1</v>
       </c>
@@ -4449,13 +4626,16 @@
         <v>1</v>
       </c>
       <c r="AD74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE74" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Enzimas</t>
+          <t>Estructuras celulares básicas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4467,44 +4647,47 @@
         <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7</v>
       </c>
       <c r="F75" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G75" t="n">
         <v>6</v>
       </c>
-      <c r="I75" t="n">
-        <v>9.5</v>
-      </c>
       <c r="J75" t="n">
+        <v>7</v>
+      </c>
+      <c r="K75" t="n">
         <v>9</v>
       </c>
       <c r="L75" t="n">
         <v>9.5</v>
       </c>
+      <c r="M75" t="n">
+        <v>7</v>
+      </c>
       <c r="O75" t="n">
         <v>1</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
       </c>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
-      <c r="S75" t="n">
+      <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
         <v>1</v>
       </c>
+      <c r="V75" t="n">
+        <v>1</v>
+      </c>
       <c r="W75" t="n">
         <v>1</v>
       </c>
-      <c r="X75" t="n">
-        <v>1</v>
-      </c>
       <c r="Y75" t="n">
         <v>1</v>
       </c>
@@ -4521,16 +4704,13 @@
         <v>1</v>
       </c>
       <c r="AD75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE75" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
+          <t>Estructuras del cuerpo animal y su función</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4539,28 +4719,73 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E76" t="n">
+        <v>7</v>
       </c>
       <c r="F76" t="n">
         <v>8</v>
       </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K76" t="n">
+        <v>9</v>
+      </c>
+      <c r="L76" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M76" t="n">
+        <v>7</v>
+      </c>
       <c r="O76" t="n">
         <v>1</v>
       </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
       <c r="Y76" t="n">
         <v>1</v>
       </c>
       <c r="Z76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE76" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Estructura del ADN</t>
+          <t>Eutrofización</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4569,73 +4794,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D77" t="n">
         <v>10</v>
       </c>
-      <c r="F77" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G77" t="n">
-        <v>6</v>
-      </c>
-      <c r="I77" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J77" t="n">
-        <v>9</v>
-      </c>
-      <c r="L77" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M77" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
-      </c>
-      <c r="P77" t="n">
-        <v>1</v>
-      </c>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
-      <c r="S77" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" t="n">
-        <v>1</v>
-      </c>
-      <c r="V77" t="n">
-        <v>1</v>
-      </c>
-      <c r="W77" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>1</v>
-      </c>
       <c r="Z77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE77" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Estructuras celulares básicas</t>
+          <t>Extinción de especies</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4644,13 +4815,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78" t="n">
-        <v>9</v>
-      </c>
-      <c r="E78" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F78" t="n">
         <v>8</v>
@@ -4658,56 +4826,41 @@
       <c r="G78" t="n">
         <v>6</v>
       </c>
-      <c r="K78" t="n">
+      <c r="I78" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J78" t="n">
         <v>9</v>
       </c>
-      <c r="L78" t="n">
-        <v>9.5</v>
-      </c>
       <c r="M78" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="P78" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>1</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1</v>
-      </c>
-      <c r="V78" t="n">
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="n">
         <v>1</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
-      <c r="Y78" t="n">
+      <c r="X78" t="n">
         <v>1</v>
       </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
-      <c r="AA78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>1</v>
-      </c>
       <c r="AC78" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD78" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Estructuras del cuerpo animal y su función</t>
+          <t>Factores bióticos y abióticos</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4716,29 +4869,32 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F79" t="n">
         <v>8</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
-      </c>
-      <c r="K79" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>7</v>
       </c>
       <c r="L79" t="n">
         <v>9.5</v>
       </c>
+      <c r="M79" t="n">
+        <v>7</v>
+      </c>
       <c r="O79" t="n">
         <v>1</v>
       </c>
@@ -4748,7 +4904,7 @@
       <c r="R79" t="n">
         <v>1</v>
       </c>
-      <c r="T79" t="n">
+      <c r="S79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
@@ -4763,7 +4919,7 @@
       <c r="Z79" t="n">
         <v>1</v>
       </c>
-      <c r="AB79" t="n">
+      <c r="AA79" t="n">
         <v>1</v>
       </c>
       <c r="AC79" t="n">
@@ -4779,7 +4935,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Eutrofización</t>
+          <t>Factores limitantes de las poblaciones</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4791,16 +4947,52 @@
         <v>7</v>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="F80" t="n">
+        <v>8</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J80" t="n">
+        <v>9</v>
+      </c>
+      <c r="M80" t="n">
+        <v>7</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="W80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1</v>
       </c>
       <c r="Z80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE80" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Extinción de especies</t>
+          <t>Fecundación y desarrollo embrionario</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4809,10 +5001,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
         <v>8</v>
@@ -4821,18 +5013,24 @@
         <v>6</v>
       </c>
       <c r="I81" t="n">
+        <v>4</v>
+      </c>
+      <c r="J81" t="n">
+        <v>7</v>
+      </c>
+      <c r="L81" t="n">
         <v>9.5</v>
       </c>
-      <c r="J81" t="n">
-        <v>9</v>
+      <c r="M81" t="n">
+        <v>9.5</v>
       </c>
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
-      <c r="S81" t="n">
+      <c r="U81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="n">
         <v>1</v>
       </c>
       <c r="W81" t="n">
@@ -4841,17 +5039,29 @@
       <c r="X81" t="n">
         <v>1</v>
       </c>
+      <c r="Y81" t="n">
+        <v>1</v>
+      </c>
       <c r="Z81" t="n">
         <v>1</v>
       </c>
-      <c r="AC81" t="n">
+      <c r="AA81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE81" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Factores bióticos y abióticos</t>
+          <t>Fermentación y respiración anaerobia</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4860,54 +5070,39 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>9</v>
-      </c>
-      <c r="E82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G82" t="n">
         <v>6</v>
       </c>
-      <c r="I82" t="n">
-        <v>5</v>
-      </c>
-      <c r="J82" t="n">
-        <v>9</v>
-      </c>
       <c r="L82" t="n">
         <v>9.5</v>
       </c>
+      <c r="M82" t="n">
+        <v>7</v>
+      </c>
       <c r="O82" t="n">
         <v>1</v>
       </c>
       <c r="P82" t="n">
         <v>1</v>
       </c>
-      <c r="R82" t="n">
-        <v>1</v>
-      </c>
-      <c r="S82" t="n">
-        <v>1</v>
-      </c>
       <c r="U82" t="n">
         <v>1</v>
       </c>
-      <c r="W82" t="n">
-        <v>1</v>
-      </c>
       <c r="Y82" t="n">
         <v>1</v>
       </c>
       <c r="Z82" t="n">
         <v>1</v>
       </c>
-      <c r="AA82" t="n">
+      <c r="AB82" t="n">
         <v>1</v>
       </c>
       <c r="AC82" t="n">
@@ -4923,7 +5118,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Factores limitantes de las poblaciones</t>
+          <t>Filogenia y parentesco evolutivo</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4935,7 +5130,7 @@
         <v>7</v>
       </c>
       <c r="D83" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F83" t="n">
         <v>8</v>
@@ -4943,8 +5138,11 @@
       <c r="G83" t="n">
         <v>8.5</v>
       </c>
-      <c r="J83" t="n">
-        <v>9</v>
+      <c r="I83" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M83" t="n">
+        <v>9.5</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
@@ -4952,7 +5150,10 @@
       <c r="P83" t="n">
         <v>1</v>
       </c>
-      <c r="S83" t="n">
+      <c r="R83" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" t="n">
         <v>1</v>
       </c>
       <c r="W83" t="n">
@@ -4967,17 +5168,20 @@
       <c r="AA83" t="n">
         <v>1</v>
       </c>
+      <c r="AB83" t="n">
+        <v>1</v>
+      </c>
       <c r="AC83" t="n">
         <v>1</v>
       </c>
-      <c r="AE83" t="n">
+      <c r="AD83" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Fecundación y desarrollo embrionario</t>
+          <t>Flujo de energía y pirámides ecológicas</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -4986,29 +5190,41 @@
         </is>
       </c>
       <c r="C84" t="n">
+        <v>7</v>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="n">
         <v>6</v>
       </c>
-      <c r="D84" t="n">
+      <c r="F84" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J84" t="n">
         <v>9</v>
       </c>
-      <c r="F84" t="n">
+      <c r="K84" t="n">
         <v>8</v>
-      </c>
-      <c r="G84" t="n">
-        <v>6</v>
-      </c>
-      <c r="I84" t="n">
-        <v>4</v>
       </c>
       <c r="L84" t="n">
         <v>9.5</v>
       </c>
       <c r="M84" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O84" t="n">
         <v>1</v>
       </c>
+      <c r="P84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
       <c r="U84" t="n">
         <v>1</v>
       </c>
@@ -5031,6 +5247,9 @@
         <v>1</v>
       </c>
       <c r="AB84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC84" t="n">
         <v>1</v>
       </c>
       <c r="AD84" t="n">
@@ -5043,7 +5262,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Fermentación y respiración anaerobia</t>
+          <t>Fósiles y registro fósil</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5055,16 +5274,22 @@
         <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F85" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
-      </c>
-      <c r="L85" t="n">
-        <v>9.5</v>
+        <v>4</v>
+      </c>
+      <c r="I85" t="n">
+        <v>8</v>
+      </c>
+      <c r="J85" t="n">
+        <v>9</v>
+      </c>
+      <c r="M85" t="n">
+        <v>7</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
@@ -5072,7 +5297,16 @@
       <c r="P85" t="n">
         <v>1</v>
       </c>
-      <c r="U85" t="n">
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="W85" t="n">
         <v>1</v>
       </c>
       <c r="Y85" t="n">
@@ -5085,9 +5319,6 @@
         <v>1</v>
       </c>
       <c r="AC85" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD85" t="n">
         <v>1</v>
       </c>
       <c r="AE85" t="n">
@@ -5097,7 +5328,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Filogenia y parentesco evolutivo</t>
+          <t>Fotosíntesis</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5106,22 +5337,34 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D86" t="n">
         <v>9</v>
       </c>
+      <c r="E86" t="n">
+        <v>8</v>
+      </c>
       <c r="F86" t="n">
         <v>8</v>
       </c>
       <c r="G86" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I86" t="n">
+        <v>5</v>
+      </c>
+      <c r="J86" t="n">
+        <v>7</v>
+      </c>
+      <c r="K86" t="n">
+        <v>8</v>
+      </c>
+      <c r="L86" t="n">
         <v>9.5</v>
       </c>
       <c r="M86" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
@@ -5132,12 +5375,18 @@
       <c r="R86" t="n">
         <v>1</v>
       </c>
+      <c r="U86" t="n">
+        <v>1</v>
+      </c>
       <c r="V86" t="n">
         <v>1</v>
       </c>
       <c r="W86" t="n">
         <v>1</v>
       </c>
+      <c r="X86" t="n">
+        <v>1</v>
+      </c>
       <c r="Y86" t="n">
         <v>1</v>
       </c>
@@ -5154,13 +5403,16 @@
         <v>1</v>
       </c>
       <c r="AD86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE86" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Flujo de energía y pirámides ecológicas</t>
+          <t>Genes y alelos</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5169,22 +5421,25 @@
         </is>
       </c>
       <c r="C87" t="n">
+        <v>6</v>
+      </c>
+      <c r="D87" t="n">
+        <v>9</v>
+      </c>
+      <c r="E87" t="n">
+        <v>9</v>
+      </c>
+      <c r="F87" t="n">
+        <v>8</v>
+      </c>
+      <c r="G87" t="n">
+        <v>6</v>
+      </c>
+      <c r="I87" t="n">
+        <v>8</v>
+      </c>
+      <c r="J87" t="n">
         <v>7</v>
-      </c>
-      <c r="D87" t="n">
-        <v>10</v>
-      </c>
-      <c r="E87" t="n">
-        <v>6</v>
-      </c>
-      <c r="F87" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G87" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J87" t="n">
-        <v>9</v>
       </c>
       <c r="L87" t="n">
         <v>9.5</v>
@@ -5192,12 +5447,18 @@
       <c r="M87" t="n">
         <v>9.5</v>
       </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
       <c r="O87" t="n">
         <v>1</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
       </c>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
       <c r="S87" t="n">
         <v>1</v>
       </c>
@@ -5208,9 +5469,6 @@
         <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>1</v>
-      </c>
-      <c r="X87" t="n">
         <v>1</v>
       </c>
       <c r="Y87" t="n">
@@ -5238,7 +5496,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Fósiles y registro fósil</t>
+          <t>Genética humana y enfermedades hereditarias</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5247,7 +5505,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
         <v>9</v>
@@ -5256,16 +5514,16 @@
         <v>8</v>
       </c>
       <c r="G88" t="n">
-        <v>4</v>
-      </c>
-      <c r="I88" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J88" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="L88" t="n">
+        <v>9.5</v>
       </c>
       <c r="M88" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
@@ -5273,16 +5531,10 @@
       <c r="P88" t="n">
         <v>1</v>
       </c>
-      <c r="R88" t="n">
-        <v>1</v>
-      </c>
-      <c r="S88" t="n">
-        <v>1</v>
-      </c>
-      <c r="V88" t="n">
-        <v>1</v>
-      </c>
-      <c r="W88" t="n">
+      <c r="U88" t="n">
+        <v>1</v>
+      </c>
+      <c r="X88" t="n">
         <v>1</v>
       </c>
       <c r="Y88" t="n">
@@ -5295,6 +5547,9 @@
         <v>1</v>
       </c>
       <c r="AC88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD88" t="n">
         <v>1</v>
       </c>
       <c r="AE88" t="n">
@@ -5304,7 +5559,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Fotosíntesis</t>
+          <t>Genotipo y fenotipo</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5313,28 +5568,25 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D89" t="n">
         <v>9</v>
       </c>
-      <c r="E89" t="n">
-        <v>8</v>
-      </c>
       <c r="F89" t="n">
         <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>6</v>
-      </c>
-      <c r="I89" t="n">
-        <v>5</v>
+        <v>8.5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>7</v>
       </c>
       <c r="L89" t="n">
         <v>9.5</v>
       </c>
       <c r="M89" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
@@ -5342,9 +5594,6 @@
       <c r="P89" t="n">
         <v>1</v>
       </c>
-      <c r="R89" t="n">
-        <v>1</v>
-      </c>
       <c r="U89" t="n">
         <v>1</v>
       </c>
@@ -5354,9 +5603,6 @@
       <c r="W89" t="n">
         <v>1</v>
       </c>
-      <c r="X89" t="n">
-        <v>1</v>
-      </c>
       <c r="Y89" t="n">
         <v>1</v>
       </c>
@@ -5366,23 +5612,17 @@
       <c r="AA89" t="n">
         <v>1</v>
       </c>
-      <c r="AB89" t="n">
-        <v>1</v>
-      </c>
       <c r="AC89" t="n">
         <v>1</v>
       </c>
       <c r="AD89" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE89" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Genes y alelos</t>
+          <t>Grupos de alimentos y dieta balanceada</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5391,82 +5631,31 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
         <v>9</v>
       </c>
-      <c r="E90" t="n">
-        <v>9</v>
-      </c>
       <c r="F90" t="n">
         <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>6</v>
-      </c>
-      <c r="I90" t="n">
-        <v>8</v>
-      </c>
-      <c r="J90" t="n">
-        <v>9</v>
-      </c>
-      <c r="L90" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M90" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="P90" t="n">
-        <v>1</v>
-      </c>
-      <c r="R90" t="n">
-        <v>1</v>
-      </c>
-      <c r="S90" t="n">
-        <v>1</v>
-      </c>
-      <c r="U90" t="n">
-        <v>1</v>
-      </c>
-      <c r="V90" t="n">
-        <v>1</v>
-      </c>
-      <c r="W90" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y90" t="n">
+      <c r="X90" t="n">
         <v>1</v>
       </c>
       <c r="Z90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE90" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Genética humana y enfermedades hereditarias</t>
+          <t>Hábitat y ecosistemas comunes</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5475,55 +5664,43 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
         <v>9</v>
       </c>
+      <c r="E91" t="n">
+        <v>2</v>
+      </c>
       <c r="F91" t="n">
         <v>8</v>
       </c>
       <c r="G91" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L91" t="n">
-        <v>9.5</v>
+        <v>2</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" t="n">
+        <v>7</v>
       </c>
       <c r="O91" t="n">
         <v>1</v>
       </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="X91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>1</v>
-      </c>
       <c r="Z91" t="n">
         <v>1</v>
       </c>
-      <c r="AB91" t="n">
-        <v>1</v>
-      </c>
       <c r="AC91" t="n">
         <v>1</v>
       </c>
       <c r="AD91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE91" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Genotipo y fenotipo</t>
+          <t>Hábitos de vida saludable</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5532,7 +5709,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>9</v>
@@ -5541,14 +5718,11 @@
         <v>8</v>
       </c>
       <c r="G92" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
         <v>9.5</v>
       </c>
-      <c r="M92" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O92" t="n">
         <v>1</v>
       </c>
@@ -5558,19 +5732,13 @@
       <c r="U92" t="n">
         <v>1</v>
       </c>
-      <c r="V92" t="n">
-        <v>1</v>
-      </c>
-      <c r="W92" t="n">
-        <v>1</v>
-      </c>
       <c r="Y92" t="n">
         <v>1</v>
       </c>
       <c r="Z92" t="n">
         <v>1</v>
       </c>
-      <c r="AA92" t="n">
+      <c r="AB92" t="n">
         <v>1</v>
       </c>
       <c r="AC92" t="n">
@@ -5583,7 +5751,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Grupos de alimentos y dieta balanceada</t>
+          <t>Herencia de rasgos</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5592,31 +5760,55 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
         <v>8</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="I93" t="n">
+        <v>8</v>
+      </c>
+      <c r="L93" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M93" t="n">
+        <v>7</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="X93" t="n">
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y93" t="n">
         <v>1</v>
       </c>
       <c r="Z93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD93" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Hábitat y ecosistemas comunes</t>
+          <t>Herencia mendeliana</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5625,40 +5817,76 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="n">
         <v>9</v>
-      </c>
-      <c r="E94" t="n">
-        <v>2</v>
       </c>
       <c r="F94" t="n">
         <v>8</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="J94" t="n">
+        <v>7</v>
+      </c>
+      <c r="L94" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M94" t="n">
+        <v>7</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
       </c>
+      <c r="P94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="n">
+        <v>1</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>1</v>
+      </c>
       <c r="Z94" t="n">
         <v>1</v>
       </c>
+      <c r="AA94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>1</v>
+      </c>
       <c r="AC94" t="n">
         <v>1</v>
       </c>
       <c r="AD94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE94" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Hábitos de vida saludable</t>
+          <t>Historia de la vida en la Tierra</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5667,27 +5895,42 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="n">
         <v>9</v>
       </c>
       <c r="F95" t="n">
         <v>8</v>
       </c>
-      <c r="G95" t="n">
-        <v>2</v>
-      </c>
-      <c r="L95" t="n">
-        <v>9.5</v>
+      <c r="I95" t="n">
+        <v>8</v>
+      </c>
+      <c r="J95" t="n">
+        <v>9</v>
+      </c>
+      <c r="M95" t="n">
+        <v>7</v>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="P95" t="n">
-        <v>1</v>
-      </c>
-      <c r="U95" t="n">
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" t="n">
+        <v>1</v>
+      </c>
+      <c r="W95" t="n">
         <v>1</v>
       </c>
       <c r="Y95" t="n">
@@ -5696,20 +5939,20 @@
       <c r="Z95" t="n">
         <v>1</v>
       </c>
-      <c r="AB95" t="n">
+      <c r="AA95" t="n">
         <v>1</v>
       </c>
       <c r="AC95" t="n">
         <v>1</v>
       </c>
-      <c r="AD95" t="n">
+      <c r="AE95" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Herencia de rasgos</t>
+          <t>Homeostasis</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5718,25 +5961,31 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F96" t="n">
         <v>8</v>
       </c>
       <c r="G96" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="I96" t="n">
-        <v>8</v>
+        <v>9.5</v>
+      </c>
+      <c r="J96" t="n">
+        <v>7</v>
+      </c>
+      <c r="K96" t="n">
+        <v>9</v>
       </c>
       <c r="L96" t="n">
         <v>9.5</v>
       </c>
       <c r="M96" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -5744,10 +5993,16 @@
       <c r="P96" t="n">
         <v>1</v>
       </c>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>1</v>
+      </c>
       <c r="U96" t="n">
         <v>1</v>
       </c>
-      <c r="V96" t="n">
+      <c r="W96" t="n">
         <v>1</v>
       </c>
       <c r="Y96" t="n">
@@ -5756,17 +6011,26 @@
       <c r="Z96" t="n">
         <v>1</v>
       </c>
+      <c r="AA96" t="n">
+        <v>1</v>
+      </c>
       <c r="AB96" t="n">
         <v>1</v>
       </c>
+      <c r="AC96" t="n">
+        <v>1</v>
+      </c>
       <c r="AD96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE96" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Herencia mendeliana</t>
+          <t>Impacto humano en los ecosistemas</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5775,31 +6039,31 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>10</v>
-      </c>
-      <c r="E97" t="n">
         <v>9</v>
       </c>
       <c r="F97" t="n">
         <v>8</v>
       </c>
       <c r="G97" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
+        <v>5</v>
+      </c>
+      <c r="J97" t="n">
+        <v>9</v>
+      </c>
+      <c r="K97" t="n">
         <v>8</v>
       </c>
       <c r="L97" t="n">
         <v>9.5</v>
       </c>
       <c r="M97" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N97" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
@@ -5807,13 +6071,19 @@
       <c r="P97" t="n">
         <v>1</v>
       </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
       <c r="U97" t="n">
         <v>1</v>
       </c>
-      <c r="V97" t="n">
-        <v>1</v>
-      </c>
       <c r="W97" t="n">
+        <v>1</v>
+      </c>
+      <c r="X97" t="n">
         <v>1</v>
       </c>
       <c r="Y97" t="n">
@@ -5841,7 +6111,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Historia de la vida en la Tierra</t>
+          <t>Inmunidad activa, pasiva y vacunas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5850,39 +6120,33 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
-        <v>10</v>
-      </c>
-      <c r="E98" t="n">
         <v>9</v>
       </c>
       <c r="F98" t="n">
         <v>8</v>
       </c>
-      <c r="I98" t="n">
-        <v>8</v>
-      </c>
-      <c r="J98" t="n">
+      <c r="G98" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K98" t="n">
         <v>9</v>
       </c>
-      <c r="M98" t="n">
+      <c r="L98" t="n">
         <v>9.5</v>
       </c>
-      <c r="N98" t="n">
-        <v>1</v>
-      </c>
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="R98" t="n">
-        <v>1</v>
-      </c>
-      <c r="S98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
+      <c r="P98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" t="n">
         <v>1</v>
       </c>
       <c r="W98" t="n">
@@ -5894,20 +6158,17 @@
       <c r="Z98" t="n">
         <v>1</v>
       </c>
-      <c r="AA98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE98" t="n">
+      <c r="AB98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD98" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Homeostasis</t>
+          <t>Intercambio de gases en animales</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5916,38 +6177,35 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D99" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F99" t="n">
         <v>8</v>
       </c>
       <c r="G99" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I99" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K99" t="n">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="J99" t="n">
+        <v>7</v>
       </c>
       <c r="L99" t="n">
         <v>9.5</v>
       </c>
+      <c r="M99" t="n">
+        <v>7</v>
+      </c>
       <c r="O99" t="n">
         <v>1</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
       </c>
-      <c r="R99" t="n">
-        <v>1</v>
-      </c>
-      <c r="T99" t="n">
-        <v>1</v>
-      </c>
       <c r="U99" t="n">
         <v>1</v>
       </c>
@@ -5960,26 +6218,17 @@
       <c r="Z99" t="n">
         <v>1</v>
       </c>
-      <c r="AA99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>1</v>
-      </c>
       <c r="AC99" t="n">
         <v>1</v>
       </c>
       <c r="AD99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE99" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Impacto humano en los ecosistemas</t>
+          <t>Intercambio de gases en plantas</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5988,73 +6237,43 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>9</v>
-      </c>
-      <c r="F100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
-      </c>
-      <c r="J100" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L100" t="n">
         <v>9.5</v>
       </c>
-      <c r="O100" t="n">
-        <v>1</v>
-      </c>
       <c r="P100" t="n">
         <v>1</v>
       </c>
-      <c r="R100" t="n">
-        <v>1</v>
-      </c>
-      <c r="S100" t="n">
-        <v>1</v>
-      </c>
       <c r="U100" t="n">
         <v>1</v>
       </c>
       <c r="W100" t="n">
         <v>1</v>
       </c>
-      <c r="X100" t="n">
-        <v>1</v>
-      </c>
       <c r="Y100" t="n">
         <v>1</v>
       </c>
       <c r="Z100" t="n">
         <v>1</v>
       </c>
-      <c r="AA100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC100" t="n">
-        <v>1</v>
-      </c>
       <c r="AD100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE100" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Inmunidad activa, pasiva y vacunas</t>
+          <t>La célula como unidad de la vida</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6063,16 +6282,25 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
         <v>9</v>
       </c>
+      <c r="E101" t="n">
+        <v>7</v>
+      </c>
       <c r="F101" t="n">
         <v>8</v>
       </c>
       <c r="G101" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="I101" t="n">
+        <v>7</v>
+      </c>
+      <c r="J101" t="n">
+        <v>7</v>
       </c>
       <c r="K101" t="n">
         <v>9</v>
@@ -6080,38 +6308,62 @@
       <c r="L101" t="n">
         <v>9.5</v>
       </c>
+      <c r="M101" t="n">
+        <v>7</v>
+      </c>
       <c r="O101" t="n">
         <v>1</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
       </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
       <c r="T101" t="n">
         <v>1</v>
       </c>
       <c r="U101" t="n">
         <v>1</v>
       </c>
+      <c r="V101" t="n">
+        <v>1</v>
+      </c>
       <c r="W101" t="n">
         <v>1</v>
       </c>
+      <c r="X101" t="n">
+        <v>1</v>
+      </c>
       <c r="Y101" t="n">
         <v>1</v>
       </c>
       <c r="Z101" t="n">
         <v>1</v>
       </c>
+      <c r="AA101" t="n">
+        <v>1</v>
+      </c>
       <c r="AB101" t="n">
         <v>1</v>
       </c>
+      <c r="AC101" t="n">
+        <v>1</v>
+      </c>
       <c r="AD101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE101" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Intercambio de gases en animales</t>
+          <t>Mecanismos de microevolución</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6120,32 +6372,29 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D102" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F102" t="n">
         <v>8</v>
       </c>
-      <c r="G102" t="n">
-        <v>6</v>
-      </c>
-      <c r="I102" t="n">
-        <v>5</v>
-      </c>
       <c r="L102" t="n">
         <v>9.5</v>
       </c>
+      <c r="M102" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="P102" t="n">
-        <v>1</v>
-      </c>
       <c r="U102" t="n">
         <v>1</v>
       </c>
+      <c r="V102" t="n">
+        <v>1</v>
+      </c>
       <c r="W102" t="n">
         <v>1</v>
       </c>
@@ -6155,17 +6404,23 @@
       <c r="Z102" t="n">
         <v>1</v>
       </c>
+      <c r="AA102" t="n">
+        <v>1</v>
+      </c>
       <c r="AC102" t="n">
         <v>1</v>
       </c>
       <c r="AD102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE102" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Intercambio de gases en plantas</t>
+          <t>Medidas de biodiversidad</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6174,25 +6429,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G103" t="n">
-        <v>6</v>
-      </c>
-      <c r="I103" t="n">
-        <v>7</v>
-      </c>
-      <c r="L103" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P103" t="n">
-        <v>1</v>
-      </c>
-      <c r="U103" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="W103" t="n">
         <v>1</v>
@@ -6203,14 +6446,17 @@
       <c r="Z103" t="n">
         <v>1</v>
       </c>
-      <c r="AD103" t="n">
+      <c r="AB103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE103" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>La célula como unidad de la vida</t>
+          <t>Meiosis</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6219,50 +6465,38 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
         <v>9</v>
       </c>
       <c r="E104" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F104" t="n">
         <v>8</v>
       </c>
       <c r="G104" t="n">
-        <v>6</v>
-      </c>
-      <c r="I104" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J104" t="n">
         <v>7</v>
       </c>
-      <c r="J104" t="n">
-        <v>9</v>
-      </c>
-      <c r="K104" t="n">
-        <v>9</v>
-      </c>
       <c r="L104" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M104" t="n">
         <v>9.5</v>
       </c>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
       <c r="O104" t="n">
         <v>1</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
       </c>
-      <c r="R104" t="n">
-        <v>1</v>
-      </c>
-      <c r="S104" t="n">
-        <v>1</v>
-      </c>
-      <c r="T104" t="n">
-        <v>1</v>
-      </c>
       <c r="U104" t="n">
         <v>1</v>
       </c>
@@ -6270,9 +6504,6 @@
         <v>1</v>
       </c>
       <c r="W104" t="n">
-        <v>1</v>
-      </c>
-      <c r="X104" t="n">
         <v>1</v>
       </c>
       <c r="Y104" t="n">
@@ -6300,7 +6531,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mecanismos de microevolución</t>
+          <t>Membrana celular</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6309,29 +6540,35 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>10.5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>6</v>
+      </c>
+      <c r="J105" t="n">
+        <v>9</v>
       </c>
       <c r="L105" t="n">
         <v>9.5</v>
       </c>
-      <c r="M105" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O105" t="n">
         <v>1</v>
       </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1</v>
+      </c>
       <c r="U105" t="n">
         <v>1</v>
       </c>
-      <c r="V105" t="n">
-        <v>1</v>
-      </c>
       <c r="W105" t="n">
         <v>1</v>
       </c>
@@ -6341,7 +6578,7 @@
       <c r="Z105" t="n">
         <v>1</v>
       </c>
-      <c r="AA105" t="n">
+      <c r="AB105" t="n">
         <v>1</v>
       </c>
       <c r="AC105" t="n">
@@ -6357,7 +6594,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Medidas de biodiversidad</t>
+          <t>Microorganismos</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6366,13 +6603,43 @@
         </is>
       </c>
       <c r="C106" t="n">
+        <v>2</v>
+      </c>
+      <c r="D106" t="n">
+        <v>10</v>
+      </c>
+      <c r="F106" t="n">
+        <v>8</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4</v>
+      </c>
+      <c r="I106" t="n">
+        <v>8</v>
+      </c>
+      <c r="J106" t="n">
+        <v>9</v>
+      </c>
+      <c r="L106" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M106" t="n">
         <v>7</v>
       </c>
-      <c r="D106" t="n">
-        <v>11</v>
-      </c>
-      <c r="G106" t="n">
-        <v>8.5</v>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1</v>
+      </c>
+      <c r="R106" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
+      <c r="U106" t="n">
+        <v>1</v>
       </c>
       <c r="W106" t="n">
         <v>1</v>
@@ -6383,17 +6650,14 @@
       <c r="Z106" t="n">
         <v>1</v>
       </c>
-      <c r="AB106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE106" t="n">
+      <c r="AD106" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Meiosis</t>
+          <t>Mitosis y ciclo celular</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6411,16 +6675,25 @@
         <v>9</v>
       </c>
       <c r="F107" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G107" t="n">
         <v>8.5</v>
       </c>
+      <c r="I107" t="n">
+        <v>8</v>
+      </c>
+      <c r="J107" t="n">
+        <v>7</v>
+      </c>
+      <c r="K107" t="n">
+        <v>9</v>
+      </c>
       <c r="L107" t="n">
         <v>11</v>
       </c>
       <c r="M107" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="N107" t="n">
         <v>1</v>
@@ -6431,6 +6704,12 @@
       <c r="P107" t="n">
         <v>1</v>
       </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" t="n">
+        <v>1</v>
+      </c>
       <c r="U107" t="n">
         <v>1</v>
       </c>
@@ -6446,13 +6725,7 @@
       <c r="Z107" t="n">
         <v>1</v>
       </c>
-      <c r="AA107" t="n">
-        <v>1</v>
-      </c>
       <c r="AB107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC107" t="n">
         <v>1</v>
       </c>
       <c r="AD107" t="n">
@@ -6465,7 +6738,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Membrana celular</t>
+          <t>Modelos ecológicos basados en muestreo</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6474,35 +6747,17 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D108" t="n">
-        <v>9</v>
-      </c>
-      <c r="F108" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="G108" t="n">
         <v>6</v>
       </c>
-      <c r="J108" t="n">
-        <v>9</v>
-      </c>
-      <c r="L108" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O108" t="n">
-        <v>1</v>
-      </c>
       <c r="P108" t="n">
         <v>1</v>
       </c>
-      <c r="S108" t="n">
-        <v>1</v>
-      </c>
-      <c r="U108" t="n">
-        <v>1</v>
-      </c>
       <c r="W108" t="n">
         <v>1</v>
       </c>
@@ -6516,19 +6771,13 @@
         <v>1</v>
       </c>
       <c r="AC108" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD108" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE108" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Microorganismos</t>
+          <t>Mutaciones</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6537,19 +6786,16 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D109" t="n">
         <v>10</v>
       </c>
       <c r="F109" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G109" t="n">
-        <v>4</v>
-      </c>
-      <c r="I109" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J109" t="n">
         <v>9</v>
@@ -6557,15 +6803,15 @@
       <c r="L109" t="n">
         <v>9.5</v>
       </c>
+      <c r="M109" t="n">
+        <v>7</v>
+      </c>
       <c r="O109" t="n">
         <v>1</v>
       </c>
       <c r="P109" t="n">
         <v>1</v>
       </c>
-      <c r="R109" t="n">
-        <v>1</v>
-      </c>
       <c r="S109" t="n">
         <v>1</v>
       </c>
@@ -6581,14 +6827,26 @@
       <c r="Z109" t="n">
         <v>1</v>
       </c>
+      <c r="AA109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1</v>
+      </c>
       <c r="AD109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE109" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Mitosis y ciclo celular</t>
+          <t>Necesidades de los seres vivos</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6597,34 +6855,25 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E110" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F110" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G110" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="I110" t="n">
-        <v>8</v>
-      </c>
-      <c r="K110" t="n">
-        <v>9</v>
-      </c>
-      <c r="L110" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M110" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N110" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O110" t="n">
         <v>1</v>
@@ -6632,18 +6881,6 @@
       <c r="P110" t="n">
         <v>1</v>
       </c>
-      <c r="R110" t="n">
-        <v>1</v>
-      </c>
-      <c r="T110" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" t="n">
-        <v>1</v>
-      </c>
-      <c r="V110" t="n">
-        <v>1</v>
-      </c>
       <c r="W110" t="n">
         <v>1</v>
       </c>
@@ -6653,20 +6890,14 @@
       <c r="Z110" t="n">
         <v>1</v>
       </c>
-      <c r="AB110" t="n">
-        <v>1</v>
-      </c>
       <c r="AD110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE110" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Modelos ecológicos basados en muestreo</t>
+          <t>Nicho ecológico y exclusión competitiva</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6675,13 +6906,22 @@
         </is>
       </c>
       <c r="C111" t="n">
+        <v>4</v>
+      </c>
+      <c r="D111" t="n">
+        <v>11</v>
+      </c>
+      <c r="F111" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M111" t="n">
         <v>7</v>
       </c>
-      <c r="D111" t="n">
-        <v>10</v>
-      </c>
-      <c r="G111" t="n">
-        <v>6</v>
+      <c r="O111" t="n">
+        <v>1</v>
       </c>
       <c r="P111" t="n">
         <v>1</v>
@@ -6689,23 +6929,23 @@
       <c r="W111" t="n">
         <v>1</v>
       </c>
-      <c r="Y111" t="n">
-        <v>1</v>
-      </c>
       <c r="Z111" t="n">
         <v>1</v>
       </c>
+      <c r="AA111" t="n">
+        <v>1</v>
+      </c>
       <c r="AB111" t="n">
         <v>1</v>
       </c>
-      <c r="AC111" t="n">
+      <c r="AD111" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mutaciones</t>
+          <t>Niveles de organización de los seres vivos</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6714,35 +6954,47 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D112" t="n">
         <v>10</v>
       </c>
+      <c r="E112" t="n">
+        <v>7</v>
+      </c>
       <c r="F112" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G112" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
+        <v>7</v>
+      </c>
+      <c r="K112" t="n">
         <v>9</v>
       </c>
       <c r="L112" t="n">
         <v>9.5</v>
       </c>
+      <c r="M112" t="n">
+        <v>7</v>
+      </c>
       <c r="O112" t="n">
         <v>1</v>
       </c>
       <c r="P112" t="n">
         <v>1</v>
       </c>
-      <c r="S112" t="n">
+      <c r="T112" t="n">
         <v>1</v>
       </c>
       <c r="U112" t="n">
         <v>1</v>
       </c>
+      <c r="V112" t="n">
+        <v>1</v>
+      </c>
       <c r="W112" t="n">
         <v>1</v>
       </c>
@@ -6750,9 +7002,6 @@
         <v>1</v>
       </c>
       <c r="Z112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA112" t="n">
         <v>1</v>
       </c>
       <c r="AB112" t="n">
@@ -6771,7 +7020,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Necesidades de los seres vivos</t>
+          <t>Niveles de organización ecológica</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6780,22 +7029,25 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
         <v>11</v>
       </c>
-      <c r="E113" t="n">
-        <v>2</v>
-      </c>
       <c r="F113" t="n">
         <v>8</v>
       </c>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="I113" t="n">
-        <v>4</v>
+        <v>9.5</v>
+      </c>
+      <c r="K113" t="n">
+        <v>8</v>
+      </c>
+      <c r="M113" t="n">
+        <v>7</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -6803,6 +7055,9 @@
       <c r="P113" t="n">
         <v>1</v>
       </c>
+      <c r="R113" t="n">
+        <v>1</v>
+      </c>
       <c r="W113" t="n">
         <v>1</v>
       </c>
@@ -6812,14 +7067,23 @@
       <c r="Z113" t="n">
         <v>1</v>
       </c>
+      <c r="AB113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>1</v>
+      </c>
       <c r="AD113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE113" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Nicho ecológico y exclusión competitiva</t>
+          <t>Nutrición autótrofa y heterótrofa</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6828,16 +7092,22 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F114" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>8.5</v>
+        <v>2</v>
+      </c>
+      <c r="L114" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M114" t="n">
+        <v>7</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
@@ -6845,16 +7115,13 @@
       <c r="P114" t="n">
         <v>1</v>
       </c>
-      <c r="W114" t="n">
+      <c r="U114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y114" t="n">
         <v>1</v>
       </c>
       <c r="Z114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA114" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB114" t="n">
         <v>1</v>
       </c>
       <c r="AD114" t="n">
@@ -6864,7 +7131,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Niveles de organización de los seres vivos</t>
+          <t>Nutrientes y sus funciones</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6873,13 +7140,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>10</v>
-      </c>
-      <c r="E115" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F115" t="n">
         <v>8</v>
@@ -6887,31 +7151,19 @@
       <c r="G115" t="n">
         <v>6</v>
       </c>
-      <c r="K115" t="n">
-        <v>9</v>
-      </c>
       <c r="L115" t="n">
         <v>9.5</v>
       </c>
-      <c r="M115" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
       <c r="P115" t="n">
         <v>1</v>
       </c>
-      <c r="T115" t="n">
-        <v>1</v>
-      </c>
       <c r="U115" t="n">
         <v>1</v>
       </c>
-      <c r="V115" t="n">
-        <v>1</v>
-      </c>
-      <c r="W115" t="n">
+      <c r="X115" t="n">
         <v>1</v>
       </c>
       <c r="Y115" t="n">
@@ -6920,23 +7172,17 @@
       <c r="Z115" t="n">
         <v>1</v>
       </c>
-      <c r="AB115" t="n">
-        <v>1</v>
-      </c>
       <c r="AC115" t="n">
         <v>1</v>
       </c>
       <c r="AD115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE115" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Niveles de organización ecológica</t>
+          <t>Organelos de la célula eucariota</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6945,20 +7191,32 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D116" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E116" t="n">
+        <v>7</v>
       </c>
       <c r="F116" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="I116" t="n">
         <v>9.5</v>
       </c>
+      <c r="K116" t="n">
+        <v>9</v>
+      </c>
+      <c r="L116" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M116" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O116" t="n">
         <v>1</v>
       </c>
@@ -6966,6 +7224,15 @@
         <v>1</v>
       </c>
       <c r="R116" t="n">
+        <v>1</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" t="n">
+        <v>1</v>
+      </c>
+      <c r="V116" t="n">
         <v>1</v>
       </c>
       <c r="W116" t="n">
@@ -6993,7 +7260,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Nutrición autótrofa y heterótrofa</t>
+          <t>Órganos de los sentidos</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7002,7 +7269,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D117" t="n">
         <v>10</v>
@@ -7013,8 +7280,14 @@
       <c r="G117" t="n">
         <v>2</v>
       </c>
-      <c r="L117" t="n">
-        <v>9.5</v>
+      <c r="I117" t="n">
+        <v>7</v>
+      </c>
+      <c r="J117" t="n">
+        <v>7</v>
+      </c>
+      <c r="M117" t="n">
+        <v>7</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
@@ -7022,23 +7295,23 @@
       <c r="P117" t="n">
         <v>1</v>
       </c>
-      <c r="U117" t="n">
-        <v>1</v>
-      </c>
       <c r="Y117" t="n">
         <v>1</v>
       </c>
-      <c r="Z117" t="n">
+      <c r="AA117" t="n">
         <v>1</v>
       </c>
       <c r="AD117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE117" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nutrientes y sus funciones</t>
+          <t>Osmorregulación y equilibrio hídrico</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7047,16 +7320,13 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F118" t="n">
-        <v>8</v>
-      </c>
-      <c r="G118" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="L118" t="n">
         <v>9.5</v>
@@ -7064,13 +7334,10 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
-      <c r="P118" t="n">
-        <v>1</v>
-      </c>
       <c r="U118" t="n">
         <v>1</v>
       </c>
-      <c r="X118" t="n">
+      <c r="W118" t="n">
         <v>1</v>
       </c>
       <c r="Y118" t="n">
@@ -7089,7 +7356,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Organelos de la célula eucariota</t>
+          <t>Plantas y animales útiles al ser humano</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7098,31 +7365,16 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>10</v>
-      </c>
-      <c r="E119" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F119" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G119" t="n">
-        <v>6</v>
-      </c>
-      <c r="I119" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="K119" t="n">
-        <v>9</v>
-      </c>
-      <c r="L119" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M119" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
         <v>1</v>
@@ -7130,44 +7382,23 @@
       <c r="P119" t="n">
         <v>1</v>
       </c>
-      <c r="R119" t="n">
-        <v>1</v>
-      </c>
-      <c r="T119" t="n">
-        <v>1</v>
-      </c>
-      <c r="U119" t="n">
-        <v>1</v>
-      </c>
-      <c r="V119" t="n">
-        <v>1</v>
-      </c>
-      <c r="W119" t="n">
-        <v>1</v>
-      </c>
       <c r="Y119" t="n">
         <v>1</v>
       </c>
       <c r="Z119" t="n">
         <v>1</v>
       </c>
-      <c r="AB119" t="n">
-        <v>1</v>
-      </c>
       <c r="AC119" t="n">
         <v>1</v>
       </c>
       <c r="AD119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE119" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Órganos de los sentidos</t>
+          <t>Productores, consumidores y descomponedores</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7176,10 +7407,13 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E120" t="n">
+        <v>3</v>
       </c>
       <c r="F120" t="n">
         <v>8</v>
@@ -7188,6 +7422,18 @@
         <v>2</v>
       </c>
       <c r="I120" t="n">
+        <v>8</v>
+      </c>
+      <c r="J120" t="n">
+        <v>9</v>
+      </c>
+      <c r="K120" t="n">
+        <v>8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M120" t="n">
         <v>7</v>
       </c>
       <c r="O120" t="n">
@@ -7196,23 +7442,38 @@
       <c r="P120" t="n">
         <v>1</v>
       </c>
+      <c r="R120" t="n">
+        <v>1</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="U120" t="n">
+        <v>1</v>
+      </c>
       <c r="Y120" t="n">
         <v>1</v>
       </c>
+      <c r="Z120" t="n">
+        <v>1</v>
+      </c>
       <c r="AA120" t="n">
         <v>1</v>
       </c>
+      <c r="AB120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>1</v>
+      </c>
       <c r="AD120" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE120" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Osmorregulación y equilibrio hídrico</t>
+          <t>Proteínas: estructura y función</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7221,43 +7482,79 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F121" t="n">
         <v>10.5</v>
       </c>
+      <c r="G121" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I121" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J121" t="n">
+        <v>9</v>
+      </c>
       <c r="L121" t="n">
         <v>9.5</v>
       </c>
+      <c r="M121" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O121" t="n">
         <v>1</v>
       </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
       <c r="U121" t="n">
         <v>1</v>
       </c>
+      <c r="V121" t="n">
+        <v>1</v>
+      </c>
       <c r="W121" t="n">
         <v>1</v>
       </c>
+      <c r="X121" t="n">
+        <v>1</v>
+      </c>
       <c r="Y121" t="n">
         <v>1</v>
       </c>
       <c r="Z121" t="n">
         <v>1</v>
       </c>
+      <c r="AA121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>1</v>
+      </c>
       <c r="AC121" t="n">
         <v>1</v>
       </c>
       <c r="AD121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE121" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Plantas y animales útiles al ser humano</t>
+          <t>Redes tróficas</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7266,21 +7563,48 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D122" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="E122" t="n">
+        <v>6</v>
       </c>
       <c r="F122" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G122" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="I122" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J122" t="n">
+        <v>9</v>
+      </c>
+      <c r="L122" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M122" t="n">
+        <v>7</v>
       </c>
       <c r="O122" t="n">
         <v>1</v>
       </c>
       <c r="P122" t="n">
+        <v>1</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="U122" t="n">
+        <v>1</v>
+      </c>
+      <c r="W122" t="n">
         <v>1</v>
       </c>
       <c r="Y122" t="n">
@@ -7299,7 +7623,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Productores, consumidores y descomponedores</t>
+          <t>Replicación del ADN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7308,44 +7632,32 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D123" t="n">
-        <v>9</v>
-      </c>
-      <c r="E123" t="n">
-        <v>3</v>
-      </c>
-      <c r="F123" t="n">
-        <v>8</v>
-      </c>
-      <c r="G123" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I123" t="n">
-        <v>8</v>
-      </c>
-      <c r="J123" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="L123" t="n">
+        <v>11</v>
+      </c>
+      <c r="M123" t="n">
         <v>9.5</v>
       </c>
-      <c r="O123" t="n">
-        <v>1</v>
-      </c>
-      <c r="P123" t="n">
-        <v>1</v>
-      </c>
       <c r="R123" t="n">
         <v>1</v>
       </c>
-      <c r="S123" t="n">
-        <v>1</v>
-      </c>
       <c r="U123" t="n">
         <v>1</v>
       </c>
+      <c r="V123" t="n">
+        <v>1</v>
+      </c>
+      <c r="W123" t="n">
+        <v>1</v>
+      </c>
       <c r="Y123" t="n">
         <v>1</v>
       </c>
@@ -7362,13 +7674,16 @@
         <v>1</v>
       </c>
       <c r="AD123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE123" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Proteínas: estructura y función</t>
+          <t>Reproducción humana y pubertad</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7377,28 +7692,28 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D124" t="n">
         <v>9</v>
       </c>
+      <c r="E124" t="n">
+        <v>8</v>
+      </c>
       <c r="F124" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G124" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="I124" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J124" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L124" t="n">
         <v>9.5</v>
       </c>
       <c r="M124" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O124" t="n">
         <v>1</v>
@@ -7406,34 +7721,13 @@
       <c r="P124" t="n">
         <v>1</v>
       </c>
-      <c r="R124" t="n">
-        <v>1</v>
-      </c>
-      <c r="S124" t="n">
-        <v>1</v>
-      </c>
       <c r="U124" t="n">
         <v>1</v>
       </c>
-      <c r="V124" t="n">
-        <v>1</v>
-      </c>
-      <c r="W124" t="n">
-        <v>1</v>
-      </c>
-      <c r="X124" t="n">
-        <v>1</v>
-      </c>
       <c r="Y124" t="n">
         <v>1</v>
       </c>
       <c r="Z124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB124" t="n">
         <v>1</v>
       </c>
       <c r="AC124" t="n">
@@ -7449,7 +7743,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Redes tróficas</t>
+          <t>Reproducción sexual y asexual</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7458,44 +7752,47 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D125" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F125" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G125" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I125" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J125" t="n">
+        <v>8</v>
+      </c>
+      <c r="K125" t="n">
         <v>9</v>
       </c>
       <c r="L125" t="n">
         <v>9.5</v>
       </c>
+      <c r="M125" t="n">
+        <v>7</v>
+      </c>
       <c r="O125" t="n">
         <v>1</v>
       </c>
       <c r="P125" t="n">
         <v>1</v>
       </c>
-      <c r="R125" t="n">
-        <v>1</v>
-      </c>
-      <c r="S125" t="n">
+      <c r="T125" t="n">
         <v>1</v>
       </c>
       <c r="U125" t="n">
         <v>1</v>
       </c>
+      <c r="V125" t="n">
+        <v>1</v>
+      </c>
       <c r="W125" t="n">
         <v>1</v>
       </c>
@@ -7509,13 +7806,16 @@
         <v>1</v>
       </c>
       <c r="AD125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE125" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Replicación del ADN</t>
+          <t>Requerimientos de materia y energía de la célula</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7524,24 +7824,30 @@
         </is>
       </c>
       <c r="C126" t="n">
+        <v>6</v>
+      </c>
+      <c r="D126" t="n">
+        <v>10</v>
+      </c>
+      <c r="F126" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G126" t="n">
+        <v>6</v>
+      </c>
+      <c r="J126" t="n">
+        <v>9</v>
+      </c>
+      <c r="M126" t="n">
         <v>7</v>
       </c>
-      <c r="D126" t="n">
-        <v>11</v>
-      </c>
-      <c r="I126" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L126" t="n">
-        <v>11</v>
-      </c>
-      <c r="M126" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R126" t="n">
-        <v>1</v>
-      </c>
-      <c r="U126" t="n">
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
+      <c r="S126" t="n">
         <v>1</v>
       </c>
       <c r="V126" t="n">
@@ -7554,28 +7860,13 @@
         <v>1</v>
       </c>
       <c r="Z126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE126" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Reproducción humana y pubertad</t>
+          <t>Antibióticos y resistencia bacteriana</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7584,32 +7875,26 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D127" t="n">
+        <v>11</v>
+      </c>
+      <c r="G127" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J127" t="n">
         <v>9</v>
-      </c>
-      <c r="E127" t="n">
-        <v>8</v>
-      </c>
-      <c r="F127" t="n">
-        <v>8</v>
-      </c>
-      <c r="G127" t="n">
-        <v>3</v>
-      </c>
-      <c r="I127" t="n">
-        <v>4</v>
       </c>
       <c r="L127" t="n">
         <v>9.5</v>
       </c>
-      <c r="O127" t="n">
-        <v>1</v>
-      </c>
       <c r="P127" t="n">
         <v>1</v>
       </c>
+      <c r="S127" t="n">
+        <v>1</v>
+      </c>
       <c r="U127" t="n">
         <v>1</v>
       </c>
@@ -7623,16 +7908,13 @@
         <v>1</v>
       </c>
       <c r="AD127" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE127" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Reproducción sexual y asexual</t>
+          <t>Respiración celular</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7644,7 +7926,7 @@
         <v>6</v>
       </c>
       <c r="D128" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E128" t="n">
         <v>8</v>
@@ -7653,19 +7935,22 @@
         <v>8</v>
       </c>
       <c r="G128" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I128" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J128" t="n">
+        <v>7</v>
+      </c>
+      <c r="K128" t="n">
         <v>8</v>
-      </c>
-      <c r="K128" t="n">
-        <v>9</v>
       </c>
       <c r="L128" t="n">
         <v>9.5</v>
       </c>
       <c r="M128" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O128" t="n">
         <v>1</v>
@@ -7673,7 +7958,7 @@
       <c r="P128" t="n">
         <v>1</v>
       </c>
-      <c r="T128" t="n">
+      <c r="R128" t="n">
         <v>1</v>
       </c>
       <c r="U128" t="n">
@@ -7685,10 +7970,19 @@
       <c r="W128" t="n">
         <v>1</v>
       </c>
+      <c r="X128" t="n">
+        <v>1</v>
+      </c>
       <c r="Y128" t="n">
         <v>1</v>
       </c>
       <c r="Z128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB128" t="n">
         <v>1</v>
       </c>
       <c r="AC128" t="n">
@@ -7704,7 +7998,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Requerimientos de materia y energía de la célula</t>
+          <t>Respuesta de los seres vivos a estímulos</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7713,22 +8007,25 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
         <v>10</v>
       </c>
+      <c r="E129" t="n">
+        <v>8</v>
+      </c>
       <c r="F129" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G129" t="n">
-        <v>6</v>
-      </c>
-      <c r="J129" t="n">
-        <v>9</v>
+        <v>8.5</v>
+      </c>
+      <c r="I129" t="n">
+        <v>3</v>
       </c>
       <c r="M129" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O129" t="n">
         <v>1</v>
@@ -7736,12 +8033,6 @@
       <c r="P129" t="n">
         <v>1</v>
       </c>
-      <c r="S129" t="n">
-        <v>1</v>
-      </c>
-      <c r="V129" t="n">
-        <v>1</v>
-      </c>
       <c r="W129" t="n">
         <v>1</v>
       </c>
@@ -7749,13 +8040,25 @@
         <v>1</v>
       </c>
       <c r="Z129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE129" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Antibióticos y resistencia bacteriana</t>
+          <t>Selección artificial</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7772,21 +8075,9 @@
       <c r="G130" t="n">
         <v>8.5</v>
       </c>
-      <c r="J130" t="n">
-        <v>9</v>
-      </c>
-      <c r="L130" t="n">
-        <v>9.5</v>
-      </c>
       <c r="P130" t="n">
         <v>1</v>
       </c>
-      <c r="S130" t="n">
-        <v>1</v>
-      </c>
-      <c r="U130" t="n">
-        <v>1</v>
-      </c>
       <c r="Y130" t="n">
         <v>1</v>
       </c>
@@ -7794,16 +8085,13 @@
         <v>1</v>
       </c>
       <c r="AC130" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD130" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Respiración celular</t>
+          <t>Selección natural</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7812,22 +8100,22 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D131" t="n">
+        <v>10</v>
+      </c>
+      <c r="E131" t="n">
         <v>9</v>
-      </c>
-      <c r="E131" t="n">
-        <v>8</v>
       </c>
       <c r="F131" t="n">
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>6</v>
-      </c>
-      <c r="I131" t="n">
-        <v>9.5</v>
+        <v>4</v>
+      </c>
+      <c r="J131" t="n">
+        <v>9</v>
       </c>
       <c r="L131" t="n">
         <v>9.5</v>
@@ -7835,13 +8123,16 @@
       <c r="M131" t="n">
         <v>9.5</v>
       </c>
+      <c r="N131" t="n">
+        <v>1</v>
+      </c>
       <c r="O131" t="n">
         <v>1</v>
       </c>
       <c r="P131" t="n">
         <v>1</v>
       </c>
-      <c r="R131" t="n">
+      <c r="S131" t="n">
         <v>1</v>
       </c>
       <c r="U131" t="n">
@@ -7851,9 +8142,6 @@
         <v>1</v>
       </c>
       <c r="W131" t="n">
-        <v>1</v>
-      </c>
-      <c r="X131" t="n">
         <v>1</v>
       </c>
       <c r="Y131" t="n">
@@ -7881,7 +8169,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Respuesta de los seres vivos a estímulos</t>
+          <t>Seres vivos y no vivos</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7893,52 +8181,43 @@
         <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E132" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G132" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>9.5</v>
+      </c>
+      <c r="M132" t="n">
+        <v>7</v>
       </c>
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="P132" t="n">
-        <v>1</v>
-      </c>
-      <c r="W132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y132" t="n">
+      <c r="R132" t="n">
         <v>1</v>
       </c>
       <c r="Z132" t="n">
         <v>1</v>
       </c>
-      <c r="AA132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC132" t="n">
+      <c r="AB132" t="n">
         <v>1</v>
       </c>
       <c r="AD132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE132" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Selección artificial</t>
+          <t>Simbiosis: mutualismo, comensalismo y parasitismo</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7947,31 +8226,64 @@
         </is>
       </c>
       <c r="C133" t="n">
+        <v>4</v>
+      </c>
+      <c r="D133" t="n">
+        <v>10</v>
+      </c>
+      <c r="F133" t="n">
+        <v>8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>6</v>
+      </c>
+      <c r="I133" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>9</v>
+      </c>
+      <c r="M133" t="n">
         <v>7</v>
       </c>
-      <c r="D133" t="n">
-        <v>11</v>
-      </c>
-      <c r="G133" t="n">
-        <v>8.5</v>
+      <c r="O133" t="n">
+        <v>1</v>
       </c>
       <c r="P133" t="n">
         <v>1</v>
       </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1</v>
+      </c>
       <c r="Y133" t="n">
         <v>1</v>
       </c>
       <c r="Z133" t="n">
         <v>1</v>
       </c>
+      <c r="AA133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>1</v>
+      </c>
       <c r="AC133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE133" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Selección natural</t>
+          <t>Síntesis de proteínas</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7983,16 +8295,13 @@
         <v>7</v>
       </c>
       <c r="D134" t="n">
-        <v>10</v>
-      </c>
-      <c r="E134" t="n">
         <v>9</v>
       </c>
       <c r="F134" t="n">
-        <v>8</v>
-      </c>
-      <c r="G134" t="n">
-        <v>4</v>
+        <v>10.5</v>
+      </c>
+      <c r="I134" t="n">
+        <v>9.5</v>
       </c>
       <c r="J134" t="n">
         <v>9</v>
@@ -8003,13 +8312,10 @@
       <c r="M134" t="n">
         <v>9.5</v>
       </c>
-      <c r="N134" t="n">
-        <v>1</v>
-      </c>
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="P134" t="n">
+      <c r="R134" t="n">
         <v>1</v>
       </c>
       <c r="S134" t="n">
@@ -8049,7 +8355,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Seres vivos y no vivos</t>
+          <t>Sistema circulatorio</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8058,33 +8364,60 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D135" t="n">
-        <v>11</v>
-      </c>
-      <c r="E135" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F135" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I135" t="n">
+        <v>5</v>
+      </c>
+      <c r="J135" t="n">
+        <v>7</v>
+      </c>
+      <c r="K135" t="n">
+        <v>9</v>
+      </c>
+      <c r="L135" t="n">
         <v>9.5</v>
       </c>
+      <c r="M135" t="n">
+        <v>7</v>
+      </c>
       <c r="O135" t="n">
         <v>1</v>
       </c>
+      <c r="P135" t="n">
+        <v>1</v>
+      </c>
       <c r="R135" t="n">
         <v>1</v>
       </c>
+      <c r="T135" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>1</v>
+      </c>
       <c r="Z135" t="n">
         <v>1</v>
       </c>
       <c r="AB135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC135" t="n">
         <v>1</v>
       </c>
       <c r="AD135" t="n">
@@ -8094,7 +8427,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Simbiosis: mutualismo, comensalismo y parasitismo</t>
+          <t>Sistema nervioso</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8106,20 +8439,29 @@
         <v>4</v>
       </c>
       <c r="D136" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E136" t="n">
+        <v>8</v>
       </c>
       <c r="F136" t="n">
         <v>8</v>
       </c>
       <c r="G136" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="I136" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="J136" t="n">
+        <v>7</v>
+      </c>
+      <c r="K136" t="n">
         <v>9</v>
       </c>
+      <c r="M136" t="n">
+        <v>7</v>
+      </c>
       <c r="O136" t="n">
         <v>1</v>
       </c>
@@ -8129,12 +8471,15 @@
       <c r="R136" t="n">
         <v>1</v>
       </c>
-      <c r="S136" t="n">
+      <c r="T136" t="n">
         <v>1</v>
       </c>
       <c r="W136" t="n">
         <v>1</v>
       </c>
+      <c r="X136" t="n">
+        <v>1</v>
+      </c>
       <c r="Y136" t="n">
         <v>1</v>
       </c>
@@ -8148,6 +8493,9 @@
         <v>1</v>
       </c>
       <c r="AC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" t="n">
         <v>1</v>
       </c>
       <c r="AE136" t="n">
@@ -8157,7 +8505,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Síntesis de proteínas</t>
+          <t>Sistema respiratorio</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8166,41 +8514,41 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D137" t="n">
         <v>9</v>
       </c>
       <c r="F137" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G137" t="n">
+        <v>6</v>
       </c>
       <c r="I137" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J137" t="n">
+        <v>7</v>
+      </c>
+      <c r="K137" t="n">
         <v>9</v>
       </c>
       <c r="L137" t="n">
         <v>9.5</v>
       </c>
       <c r="M137" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="R137" t="n">
-        <v>1</v>
-      </c>
-      <c r="S137" t="n">
+      <c r="T137" t="n">
         <v>1</v>
       </c>
       <c r="U137" t="n">
         <v>1</v>
       </c>
-      <c r="V137" t="n">
-        <v>1</v>
-      </c>
       <c r="W137" t="n">
         <v>1</v>
       </c>
@@ -8210,9 +8558,6 @@
       <c r="Z137" t="n">
         <v>1</v>
       </c>
-      <c r="AA137" t="n">
-        <v>1</v>
-      </c>
       <c r="AB137" t="n">
         <v>1</v>
       </c>
@@ -8220,16 +8565,13 @@
         <v>1</v>
       </c>
       <c r="AD137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE137" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sistema circulatorio</t>
+          <t>Sostenibilidad de la biosfera</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8238,7 +8580,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D138" t="n">
         <v>9</v>
@@ -8247,27 +8589,30 @@
         <v>8</v>
       </c>
       <c r="G138" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="I138" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="J138" t="n">
+        <v>9</v>
       </c>
       <c r="K138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L138" t="n">
         <v>9.5</v>
       </c>
+      <c r="M138" t="n">
+        <v>7</v>
+      </c>
       <c r="O138" t="n">
         <v>1</v>
       </c>
       <c r="P138" t="n">
         <v>1</v>
       </c>
-      <c r="R138" t="n">
-        <v>1</v>
-      </c>
-      <c r="T138" t="n">
+      <c r="S138" t="n">
         <v>1</v>
       </c>
       <c r="U138" t="n">
@@ -8276,13 +8621,16 @@
       <c r="W138" t="n">
         <v>1</v>
       </c>
+      <c r="X138" t="n">
+        <v>1</v>
+      </c>
       <c r="Y138" t="n">
         <v>1</v>
       </c>
       <c r="Z138" t="n">
         <v>1</v>
       </c>
-      <c r="AB138" t="n">
+      <c r="AA138" t="n">
         <v>1</v>
       </c>
       <c r="AC138" t="n">
@@ -8295,7 +8643,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sistema nervioso</t>
+          <t>Sucesión ecológica</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8304,60 +8652,39 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D139" t="n">
-        <v>9</v>
-      </c>
-      <c r="E139" t="n">
+        <v>11</v>
+      </c>
+      <c r="F139" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I139" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K139" t="n">
         <v>8</v>
       </c>
-      <c r="F139" t="n">
-        <v>8</v>
-      </c>
-      <c r="G139" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I139" t="n">
+      <c r="M139" t="n">
         <v>7</v>
       </c>
-      <c r="K139" t="n">
-        <v>9</v>
-      </c>
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="P139" t="n">
-        <v>1</v>
-      </c>
       <c r="R139" t="n">
         <v>1</v>
       </c>
-      <c r="T139" t="n">
-        <v>1</v>
-      </c>
       <c r="W139" t="n">
         <v>1</v>
       </c>
-      <c r="X139" t="n">
-        <v>1</v>
-      </c>
       <c r="Y139" t="n">
         <v>1</v>
       </c>
       <c r="Z139" t="n">
         <v>1</v>
       </c>
-      <c r="AA139" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>1</v>
-      </c>
       <c r="AC139" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD139" t="n">
         <v>1</v>
       </c>
       <c r="AE139" t="n">
@@ -8367,7 +8694,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sistema respiratorio</t>
+          <t>Tejidos animales</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8379,21 +8706,21 @@
         <v>4</v>
       </c>
       <c r="D140" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E140" t="n">
+        <v>7</v>
       </c>
       <c r="F140" t="n">
         <v>8</v>
       </c>
-      <c r="G140" t="n">
-        <v>6</v>
-      </c>
-      <c r="I140" t="n">
-        <v>5</v>
-      </c>
       <c r="K140" t="n">
         <v>9</v>
       </c>
       <c r="L140" t="n">
+        <v>11</v>
+      </c>
+      <c r="M140" t="n">
         <v>9.5</v>
       </c>
       <c r="O140" t="n">
@@ -8405,6 +8732,9 @@
       <c r="U140" t="n">
         <v>1</v>
       </c>
+      <c r="V140" t="n">
+        <v>1</v>
+      </c>
       <c r="W140" t="n">
         <v>1</v>
       </c>
@@ -8414,20 +8744,17 @@
       <c r="Z140" t="n">
         <v>1</v>
       </c>
-      <c r="AB140" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>1</v>
-      </c>
       <c r="AD140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE140" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sostenibilidad de la biosfera</t>
+          <t>Tejidos vegetales</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8436,10 +8763,13 @@
         </is>
       </c>
       <c r="C141" t="n">
+        <v>8</v>
+      </c>
+      <c r="D141" t="n">
+        <v>11</v>
+      </c>
+      <c r="E141" t="n">
         <v>7</v>
-      </c>
-      <c r="D141" t="n">
-        <v>9</v>
       </c>
       <c r="F141" t="n">
         <v>8</v>
@@ -8447,22 +8777,22 @@
       <c r="G141" t="n">
         <v>8.5</v>
       </c>
-      <c r="I141" t="n">
-        <v>8</v>
-      </c>
-      <c r="J141" t="n">
+      <c r="K141" t="n">
         <v>9</v>
       </c>
       <c r="L141" t="n">
         <v>9.5</v>
       </c>
+      <c r="M141" t="n">
+        <v>7</v>
+      </c>
       <c r="O141" t="n">
         <v>1</v>
       </c>
       <c r="P141" t="n">
         <v>1</v>
       </c>
-      <c r="S141" t="n">
+      <c r="T141" t="n">
         <v>1</v>
       </c>
       <c r="U141" t="n">
@@ -8471,29 +8801,26 @@
       <c r="W141" t="n">
         <v>1</v>
       </c>
-      <c r="X141" t="n">
-        <v>1</v>
-      </c>
       <c r="Y141" t="n">
         <v>1</v>
       </c>
       <c r="Z141" t="n">
         <v>1</v>
       </c>
-      <c r="AA141" t="n">
-        <v>1</v>
-      </c>
       <c r="AC141" t="n">
         <v>1</v>
       </c>
       <c r="AD141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE141" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sucesión ecológica</t>
+          <t>Tipos de patógenos</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8502,21 +8829,30 @@
         </is>
       </c>
       <c r="C142" t="n">
+        <v>3</v>
+      </c>
+      <c r="D142" t="n">
+        <v>9</v>
+      </c>
+      <c r="F142" t="n">
+        <v>8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L142" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M142" t="n">
         <v>7</v>
       </c>
-      <c r="D142" t="n">
-        <v>11</v>
-      </c>
-      <c r="F142" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I142" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="R142" t="n">
+      <c r="P142" t="n">
+        <v>1</v>
+      </c>
+      <c r="U142" t="n">
         <v>1</v>
       </c>
       <c r="W142" t="n">
@@ -8528,17 +8864,17 @@
       <c r="Z142" t="n">
         <v>1</v>
       </c>
-      <c r="AC142" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE142" t="n">
+      <c r="AB142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD142" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Tejidos animales</t>
+          <t>Transporte activo y endocitosis</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8547,38 +8883,29 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
         <v>10</v>
       </c>
-      <c r="E143" t="n">
-        <v>7</v>
-      </c>
       <c r="F143" t="n">
-        <v>8</v>
-      </c>
-      <c r="K143" t="n">
-        <v>9</v>
+        <v>10.5</v>
+      </c>
+      <c r="G143" t="n">
+        <v>8.5</v>
       </c>
       <c r="L143" t="n">
         <v>11</v>
       </c>
-      <c r="M143" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O143" t="n">
         <v>1</v>
       </c>
-      <c r="T143" t="n">
+      <c r="P143" t="n">
         <v>1</v>
       </c>
       <c r="U143" t="n">
         <v>1</v>
       </c>
-      <c r="V143" t="n">
-        <v>1</v>
-      </c>
       <c r="W143" t="n">
         <v>1</v>
       </c>
@@ -8586,6 +8913,12 @@
         <v>1</v>
       </c>
       <c r="Z143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC143" t="n">
         <v>1</v>
       </c>
       <c r="AD143" t="n">
@@ -8598,7 +8931,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Tejidos vegetales</t>
+          <t>Transporte en plantas: xilema y floema</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8612,29 +8945,17 @@
       <c r="D144" t="n">
         <v>11</v>
       </c>
-      <c r="E144" t="n">
-        <v>7</v>
-      </c>
-      <c r="F144" t="n">
-        <v>8</v>
-      </c>
       <c r="G144" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K144" t="n">
-        <v>9</v>
+        <v>2</v>
+      </c>
+      <c r="I144" t="n">
+        <v>5</v>
       </c>
       <c r="L144" t="n">
         <v>9.5</v>
       </c>
-      <c r="O144" t="n">
-        <v>1</v>
-      </c>
-      <c r="P144" t="n">
-        <v>1</v>
-      </c>
-      <c r="T144" t="n">
-        <v>1</v>
+      <c r="M144" t="n">
+        <v>7</v>
       </c>
       <c r="U144" t="n">
         <v>1</v>
@@ -8646,12 +8967,6 @@
         <v>1</v>
       </c>
       <c r="Z144" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC144" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD144" t="n">
         <v>1</v>
       </c>
       <c r="AE144" t="n">
@@ -8661,7 +8976,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Tipos de patógenos</t>
+          <t>Tropismos y hormonas vegetales</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8673,46 +8988,25 @@
         <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>9</v>
-      </c>
-      <c r="F145" t="n">
-        <v>8</v>
-      </c>
-      <c r="G145" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L145" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O145" t="n">
-        <v>1</v>
-      </c>
-      <c r="P145" t="n">
-        <v>1</v>
-      </c>
-      <c r="U145" t="n">
-        <v>1</v>
-      </c>
-      <c r="W145" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y145" t="n">
         <v>1</v>
       </c>
-      <c r="Z145" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB145" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD145" t="n">
+      <c r="AA145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE145" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Transporte activo y endocitosis</t>
+          <t>Variación genética en la descendencia</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8724,16 +9018,22 @@
         <v>6</v>
       </c>
       <c r="D146" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F146" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G146" t="n">
-        <v>8.5</v>
+        <v>4</v>
+      </c>
+      <c r="J146" t="n">
+        <v>7</v>
       </c>
       <c r="L146" t="n">
-        <v>11</v>
+        <v>9.5</v>
+      </c>
+      <c r="M146" t="n">
+        <v>7</v>
       </c>
       <c r="O146" t="n">
         <v>1</v>
@@ -8741,9 +9041,15 @@
       <c r="P146" t="n">
         <v>1</v>
       </c>
+      <c r="S146" t="n">
+        <v>1</v>
+      </c>
       <c r="U146" t="n">
         <v>1</v>
       </c>
+      <c r="V146" t="n">
+        <v>1</v>
+      </c>
       <c r="W146" t="n">
         <v>1</v>
       </c>
@@ -8751,6 +9057,9 @@
         <v>1</v>
       </c>
       <c r="Z146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA146" t="n">
         <v>1</v>
       </c>
       <c r="AB146" t="n">
@@ -8769,30 +9078,33 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Transporte en plantas: xilema y floema</t>
+          <t>Capacidad de carga</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D147" t="n">
         <v>11</v>
       </c>
-      <c r="G147" t="n">
-        <v>2</v>
-      </c>
-      <c r="I147" t="n">
-        <v>5</v>
-      </c>
-      <c r="L147" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="U147" t="n">
+      <c r="F147" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J147" t="n">
+        <v>9</v>
+      </c>
+      <c r="M147" t="n">
+        <v>7</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="n">
         <v>1</v>
       </c>
       <c r="W147" t="n">
@@ -8801,37 +9113,58 @@
       <c r="Y147" t="n">
         <v>1</v>
       </c>
-      <c r="Z147" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE147" t="n">
+      <c r="AC147" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tropismos y hormonas vegetales</t>
+          <t>Fases de la fotosíntesis y ciclo de Calvin</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D148" t="n">
+        <v>10</v>
+      </c>
+      <c r="F148" t="n">
+        <v>8</v>
+      </c>
+      <c r="G148" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L148" t="n">
         <v>11</v>
       </c>
+      <c r="O148" t="n">
+        <v>1</v>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+      <c r="U148" t="n">
+        <v>1</v>
+      </c>
       <c r="Y148" t="n">
         <v>1</v>
       </c>
-      <c r="AA148" t="n">
+      <c r="Z148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB148" t="n">
         <v>1</v>
       </c>
       <c r="AC148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD148" t="n">
         <v>1</v>
       </c>
       <c r="AE148" t="n">
@@ -8841,50 +9174,26 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Variación genética en la descendencia</t>
+          <t>Secuenciación del ADN y perfiles genéticos</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>solo_especializacion</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D149" t="n">
-        <v>11</v>
-      </c>
-      <c r="F149" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G149" t="n">
-        <v>4</v>
-      </c>
-      <c r="J149" t="n">
-        <v>9</v>
-      </c>
-      <c r="L149" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M149" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O149" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="P149" t="n">
         <v>1</v>
       </c>
-      <c r="S149" t="n">
-        <v>1</v>
-      </c>
-      <c r="U149" t="n">
-        <v>1</v>
-      </c>
-      <c r="V149" t="n">
-        <v>1</v>
-      </c>
       <c r="W149" t="n">
         <v>1</v>
       </c>
@@ -8895,9 +9204,6 @@
         <v>1</v>
       </c>
       <c r="AA149" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB149" t="n">
         <v>1</v>
       </c>
       <c r="AC149" t="n">
@@ -8913,7 +9219,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Secuenciación del ADN y perfiles genéticos</t>
+          <t>Glucólisis, ciclo de Krebs y cadena respiratoria</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -8922,18 +9228,15 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D150" t="n">
-        <v>9</v>
-      </c>
-      <c r="G150" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="P150" t="n">
-        <v>1</v>
-      </c>
-      <c r="W150" t="n">
+        <v>10</v>
+      </c>
+      <c r="L150" t="n">
+        <v>11</v>
+      </c>
+      <c r="U150" t="n">
         <v>1</v>
       </c>
       <c r="Y150" t="n">
@@ -8942,7 +9245,7 @@
       <c r="Z150" t="n">
         <v>1</v>
       </c>
-      <c r="AA150" t="n">
+      <c r="AB150" t="n">
         <v>1</v>
       </c>
       <c r="AC150" t="n">
@@ -8958,7 +9261,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Glucólisis, ciclo de Krebs y cadena respiratoria</t>
+          <t>PCR y electroforesis en gel</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8967,15 +9270,15 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D151" t="n">
-        <v>10</v>
-      </c>
-      <c r="L151" t="n">
-        <v>11</v>
-      </c>
-      <c r="U151" t="n">
+        <v>9</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1</v>
+      </c>
+      <c r="X151" t="n">
         <v>1</v>
       </c>
       <c r="Y151" t="n">
@@ -8984,7 +9287,7 @@
       <c r="Z151" t="n">
         <v>1</v>
       </c>
-      <c r="AB151" t="n">
+      <c r="AA151" t="n">
         <v>1</v>
       </c>
       <c r="AC151" t="n">
@@ -9000,7 +9303,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PCR y electroforesis en gel</t>
+          <t>Presión y flujo de fluidos en los seres vivos</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9009,40 +9312,34 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D152" t="n">
-        <v>9</v>
-      </c>
-      <c r="W152" t="n">
-        <v>1</v>
-      </c>
-      <c r="X152" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y152" t="n">
+        <v>11</v>
+      </c>
+      <c r="L152" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M152" t="n">
+        <v>7</v>
+      </c>
+      <c r="U152" t="n">
         <v>1</v>
       </c>
       <c r="Z152" t="n">
         <v>1</v>
       </c>
-      <c r="AA152" t="n">
-        <v>1</v>
-      </c>
       <c r="AC152" t="n">
         <v>1</v>
       </c>
       <c r="AD152" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE152" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Presión y flujo de fluidos en los seres vivos</t>
+          <t>Relaciones intraespecíficas</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9056,26 +9353,20 @@
       <c r="D153" t="n">
         <v>11</v>
       </c>
-      <c r="L153" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="U153" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z153" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC153" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD153" t="n">
+      <c r="W153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB153" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Relaciones intraespecíficas</t>
+          <t>Termorregulación</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9084,18 +9375,33 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D154" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="F154" t="n">
+        <v>8</v>
+      </c>
+      <c r="G154" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1</v>
       </c>
       <c r="W154" t="n">
         <v>1</v>
       </c>
-      <c r="AA154" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB154" t="n">
+      <c r="Y154" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD154" t="n">
         <v>1</v>
       </c>
     </row>

--- a/internacional/Contraste_biologia.xlsx
+++ b/internacional/Contraste_biologia.xlsx
@@ -7502,9 +7502,6 @@
       <c r="L121" t="n">
         <v>9.5</v>
       </c>
-      <c r="M121" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O121" t="n">
         <v>1</v>
       </c>
@@ -7518,9 +7515,6 @@
         <v>1</v>
       </c>
       <c r="U121" t="n">
-        <v>1</v>
-      </c>
-      <c r="V121" t="n">
         <v>1</v>
       </c>
       <c r="W121" t="n">

--- a/internacional/Contraste_biologia.xlsx
+++ b/internacional/Contraste_biologia.xlsx
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>sin_referente</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D143" t="n">
         <v>10</v>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>sin_referente</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">

--- a/internacional/Contraste_biologia.xlsx
+++ b/internacional/Contraste_biologia.xlsx
@@ -2500,83 +2500,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Estructuras celulares básicas</t>
+          <t>Especies clave</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>7</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8</v>
-      </c>
-      <c r="G27" t="n">
-        <v>6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
-        <v>7</v>
-      </c>
-      <c r="L27" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
         <v>1</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1</v>
-      </c>
       <c r="Z27" t="n">
         <v>1</v>
       </c>
-      <c r="AA27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1</v>
-      </c>
       <c r="AC27" t="n">
         <v>1</v>
       </c>
-      <c r="AD27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>9</v>
-      </c>
       <c r="AG27" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -2584,131 +2533,143 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>no_aplica</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Factores limitantes de las poblaciones</t>
+          <t>Organelos de la célula eucariota</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>no_retomado</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
         <v>7</v>
       </c>
-      <c r="D28" t="n">
-        <v>11</v>
-      </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="n">
-        <v>7</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>11</v>
-      </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>tardio</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Historia de la vida en la Tierra</t>
+          <t>Adaptaciones estructurales</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
-      </c>
-      <c r="I29" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>2.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>7</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
+      <c r="U29" t="n">
         <v>1</v>
       </c>
       <c r="W29" t="n">
@@ -2720,17 +2681,17 @@
       <c r="Z29" t="n">
         <v>1</v>
       </c>
-      <c r="AA29" t="n">
-        <v>1</v>
-      </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
       <c r="AE29" t="n">
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -2739,166 +2700,112 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>La célula como unidad de la vida</t>
+          <t>Biomas y clasificación de ambientes</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
-      </c>
-      <c r="D30" t="n">
-        <v>9</v>
-      </c>
-      <c r="E30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
         <v>8</v>
       </c>
-      <c r="G30" t="n">
-        <v>6</v>
-      </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="n">
         <v>7</v>
       </c>
-      <c r="J30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>7</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>6</v>
-      </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Transmisión de patógenos</t>
+          <t>Cadena alimentaria</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>incierto</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
         <v>3</v>
       </c>
-      <c r="D31" t="n">
-        <v>9</v>
-      </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G31" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
         <v>3</v>
       </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
       <c r="J31" t="n">
         <v>2.5</v>
       </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
       <c r="L31" t="n">
-        <v>7.5</v>
+        <v>6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="P31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
       <c r="U31" t="n">
         <v>1</v>
       </c>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1</v>
-      </c>
       <c r="Y31" t="n">
         <v>1</v>
       </c>
@@ -2908,6 +2815,9 @@
       <c r="AD31" t="n">
         <v>1</v>
       </c>
+      <c r="AF31" t="n">
+        <v>4</v>
+      </c>
       <c r="AG31" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -2915,103 +2825,127 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>faltante</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Especies clave</t>
+          <t>Ciclo de vida de los animales</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.5</v>
       </c>
       <c r="K32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1</v>
+      <c r="M32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>no_aplica</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Organelos de la célula eucariota</t>
+          <t>Clasificación de seres vivos por sus rasgos</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>9.5</v>
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.5</v>
       </c>
       <c r="K33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
       <c r="R33" t="n">
         <v>1</v>
       </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
       <c r="W33" t="n">
         <v>1</v>
       </c>
@@ -3027,30 +2961,24 @@
       <c r="AC33" t="n">
         <v>1</v>
       </c>
-      <c r="AD33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1</v>
-      </c>
       <c r="AF33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>no_retomado</t>
+          <t>previo</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Adaptaciones estructurales</t>
+          <t>Competencia por recursos</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3059,39 +2987,42 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
         <v>11</v>
       </c>
-      <c r="E34" t="n">
-        <v>4</v>
-      </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H34" t="n">
         <v>3</v>
       </c>
+      <c r="I34" t="n">
+        <v>9.5</v>
+      </c>
       <c r="J34" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="W34" t="n">
@@ -3103,6 +3034,12 @@
       <c r="Z34" t="n">
         <v>1</v>
       </c>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1</v>
+      </c>
       <c r="AC34" t="n">
         <v>1</v>
       </c>
@@ -3113,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="AF34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -3129,7 +3066,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomas y clasificación de ambientes</t>
+          <t>Depredación</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3138,38 +3075,65 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>8</v>
+        <v>2.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>9.5</v>
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>9</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
       <c r="R35" t="n">
         <v>1</v>
       </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
       <c r="W35" t="n">
         <v>1</v>
       </c>
       <c r="Z35" t="n">
         <v>1</v>
       </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
       <c r="AE35" t="n">
         <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
@@ -3181,7 +3145,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cadena alimentaria</t>
+          <t>Ecosistemas naturales, rurales y urbanos</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3190,55 +3154,34 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7</v>
+      </c>
+      <c r="M36" t="n">
         <v>2.5</v>
       </c>
-      <c r="G36" t="n">
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="n">
         <v>2</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I36" t="n">
-        <v>5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6</v>
-      </c>
-      <c r="M36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>4</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -3254,7 +3197,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ciclo de vida de los animales</t>
+          <t>Fecundación y desarrollo embrionario</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3263,34 +3206,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F37" t="n">
         <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M37" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -3298,6 +3235,27 @@
       <c r="U37" t="n">
         <v>1</v>
       </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
       <c r="AD37" t="n">
         <v>1</v>
       </c>
@@ -3305,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
@@ -3321,7 +3279,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Clasificación de seres vivos por sus rasgos</t>
+          <t>Grupos de plantas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3330,65 +3288,41 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
-        <v>11</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H38" t="n">
         <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="L38" t="n">
+        <v>5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
         <v>3</v>
       </c>
-      <c r="M38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2</v>
-      </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
@@ -3400,7 +3334,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Competencia por recursos</t>
+          <t>Grupos de vertebrados</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3409,70 +3343,37 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
         <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
         <v>6</v>
       </c>
-      <c r="H39" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J39" t="n">
-        <v>9</v>
-      </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1</v>
-      </c>
       <c r="AB39" t="n">
         <v>1</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1</v>
-      </c>
       <c r="AF39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -3488,7 +3389,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Depredación</t>
+          <t>Hábitat y ecosistemas comunes</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3497,11 +3398,14 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
         <v>11</v>
       </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
       <c r="F40" t="n">
         <v>2.5</v>
       </c>
@@ -3509,49 +3413,37 @@
         <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="K40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
         <v>6</v>
       </c>
+      <c r="M40" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1</v>
-      </c>
       <c r="Z40" t="n">
         <v>1</v>
       </c>
-      <c r="AB40" t="n">
-        <v>1</v>
-      </c>
       <c r="AC40" t="n">
         <v>1</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AD40" t="n">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -3567,7 +3459,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ecosistemas naturales, rurales y urbanos</t>
+          <t>Intercambio de gases en animales</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3576,38 +3468,59 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6</v>
       </c>
       <c r="H41" t="n">
         <v>7</v>
       </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5</v>
+      </c>
       <c r="M41" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
       <c r="Z41" t="n">
         <v>1</v>
       </c>
-      <c r="AA41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE41" t="n">
+      <c r="AC41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH41" t="inlineStr">
@@ -3619,7 +3532,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fecundación y desarrollo embrionario</t>
+          <t>Invertebrados e insectos</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3628,28 +3541,25 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G42" t="n">
         <v>6</v>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" t="n">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -3657,35 +3567,11 @@
       <c r="U42" t="n">
         <v>1</v>
       </c>
-      <c r="V42" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE42" t="n">
+      <c r="AC42" t="n">
         <v>1</v>
       </c>
       <c r="AF42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -3701,7 +3587,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Grupos de plantas</t>
+          <t>Necesidades de los seres vivos</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3710,41 +3596,62 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>11</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>2.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.5</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
       </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1</v>
+      </c>
       <c r="Z43" t="n">
         <v>1</v>
       </c>
-      <c r="AB43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC43" t="n">
+      <c r="AD43" t="n">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
@@ -3756,7 +3663,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Grupos de vertebrados</t>
+          <t>Osmorregulación y equilibrio hídrico</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3765,37 +3672,40 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G44" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" t="n">
-        <v>2</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2</v>
-      </c>
-      <c r="M44" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
+      </c>
+      <c r="L44" t="n">
+        <v>9.5</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="U44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="n">
         <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -3811,7 +3721,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hábitat y ecosistemas comunes</t>
+          <t>Partes de la planta y sus funciones</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3825,9 +3735,6 @@
       <c r="D45" t="n">
         <v>11</v>
       </c>
-      <c r="E45" t="n">
-        <v>2</v>
-      </c>
       <c r="F45" t="n">
         <v>2.5</v>
       </c>
@@ -3847,7 +3754,7 @@
         <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M45" t="n">
         <v>2.5</v>
@@ -3855,13 +3762,34 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1</v>
+      </c>
       <c r="Z45" t="n">
         <v>1</v>
       </c>
+      <c r="AB45" t="n">
+        <v>1</v>
+      </c>
       <c r="AC45" t="n">
         <v>1</v>
       </c>
       <c r="AD45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1</v>
       </c>
       <c r="AF45" t="n">
@@ -3881,7 +3809,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Intercambio de gases en animales</t>
+          <t>Plantas y animales útiles al ser humano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3890,28 +3818,25 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G46" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>7</v>
-      </c>
-      <c r="I46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>7</v>
-      </c>
-      <c r="L46" t="n">
-        <v>5</v>
+        <v>2.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
@@ -3919,12 +3844,6 @@
       <c r="P46" t="n">
         <v>1</v>
       </c>
-      <c r="U46" t="n">
-        <v>1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1</v>
-      </c>
       <c r="Y46" t="n">
         <v>1</v>
       </c>
@@ -3938,7 +3857,7 @@
         <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -3954,7 +3873,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Invertebrados e insectos</t>
+          <t>Grandes grupos taxonómicos</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3966,27 +3885,33 @@
         <v>2</v>
       </c>
       <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" t="n">
         <v>2.5</v>
       </c>
-      <c r="G47" t="n">
-        <v>6</v>
-      </c>
-      <c r="H47" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2</v>
-      </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L47" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="U47" t="n">
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB47" t="n">
         <v>1</v>
       </c>
       <c r="AC47" t="n">
@@ -4009,7 +3934,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Necesidades de los seres vivos</t>
+          <t>Reproducción sexual de las plantas con flor</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4018,16 +3943,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
         <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F48" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
@@ -4038,38 +3963,32 @@
       <c r="I48" t="n">
         <v>4</v>
       </c>
-      <c r="J48" t="n">
-        <v>2.5</v>
-      </c>
       <c r="K48" t="n">
         <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
       </c>
-      <c r="P48" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1</v>
-      </c>
       <c r="Z48" t="n">
         <v>1</v>
       </c>
+      <c r="AC48" t="n">
+        <v>1</v>
+      </c>
       <c r="AD48" t="n">
         <v>1</v>
       </c>
+      <c r="AE48" t="n">
+        <v>1</v>
+      </c>
       <c r="AF48" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -4085,7 +4004,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Osmorregulación y equilibrio hídrico</t>
+          <t>Reproducción humana y pubertad</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4094,26 +4013,38 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4</v>
+      </c>
+      <c r="L49" t="n">
+        <v>5</v>
+      </c>
+      <c r="M49" t="n">
         <v>7</v>
       </c>
-      <c r="D49" t="n">
-        <v>9</v>
-      </c>
-      <c r="F49" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L49" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
       <c r="U49" t="n">
         <v>1</v>
       </c>
-      <c r="W49" t="n">
-        <v>1</v>
-      </c>
       <c r="Y49" t="n">
         <v>1</v>
       </c>
@@ -4126,12 +4057,15 @@
       <c r="AD49" t="n">
         <v>1</v>
       </c>
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
       <c r="AF49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
@@ -4143,7 +4077,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Partes de la planta y sus funciones</t>
+          <t>Seres vivos y no vivos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4155,7 +4089,10 @@
         <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
       </c>
       <c r="F50" t="n">
         <v>2.5</v>
@@ -4167,16 +4104,13 @@
         <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="K50" t="n">
         <v>2</v>
       </c>
       <c r="L50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
         <v>2.5</v>
@@ -4184,19 +4118,7 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="P50" t="n">
-        <v>1</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y50" t="n">
+      <c r="R50" t="n">
         <v>1</v>
       </c>
       <c r="Z50" t="n">
@@ -4205,13 +4127,7 @@
       <c r="AB50" t="n">
         <v>1</v>
       </c>
-      <c r="AC50" t="n">
-        <v>1</v>
-      </c>
       <c r="AD50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE50" t="n">
         <v>1</v>
       </c>
       <c r="AF50" t="n">
@@ -4231,7 +4147,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Plantas y animales útiles al ser humano</t>
+          <t>Sistema digestivo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4240,38 +4156,50 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="L51" t="n">
+        <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y51" t="n">
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>1</v>
       </c>
       <c r="Z51" t="n">
         <v>1</v>
       </c>
+      <c r="AB51" t="n">
+        <v>1</v>
+      </c>
       <c r="AC51" t="n">
         <v>1</v>
       </c>
@@ -4279,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -4295,7 +4223,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Grandes grupos taxonómicos</t>
+          <t>Sistema excretor</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4304,43 +4232,52 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>5</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>7</v>
+      </c>
+      <c r="L52" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="n">
         <v>4</v>
-      </c>
-      <c r="G52" t="n">
-        <v>4</v>
-      </c>
-      <c r="H52" t="n">
-        <v>4</v>
-      </c>
-      <c r="I52" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K52" t="n">
-        <v>5</v>
-      </c>
-      <c r="L52" t="n">
-        <v>3</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>2</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -4356,7 +4293,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Reproducción sexual de las plantas con flor</t>
+          <t>Sistema locomotor</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4365,13 +4302,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
-      </c>
-      <c r="D53" t="n">
-        <v>11</v>
-      </c>
-      <c r="E53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F53" t="n">
         <v>8</v>
@@ -4383,38 +4314,35 @@
         <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4.5</v>
       </c>
       <c r="K53" t="n">
         <v>2</v>
       </c>
-      <c r="L53" t="n">
-        <v>5</v>
-      </c>
       <c r="M53" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
       </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
       <c r="Z53" t="n">
         <v>1</v>
       </c>
-      <c r="AC53" t="n">
-        <v>1</v>
-      </c>
       <c r="AD53" t="n">
         <v>1</v>
       </c>
-      <c r="AE53" t="n">
-        <v>1</v>
-      </c>
       <c r="AF53" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
@@ -4426,196 +4354,220 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Reproducción humana y pubertad</t>
+          <t>Acervo génico y frecuencias alélicas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>11</v>
       </c>
       <c r="F54" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" t="n">
-        <v>4</v>
-      </c>
-      <c r="I54" t="n">
-        <v>4</v>
+        <v>8.5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>9</v>
       </c>
       <c r="L54" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="M54" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
         <v>7</v>
       </c>
-      <c r="O54" t="n">
-        <v>1</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>4</v>
-      </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Seres vivos y no vivos</t>
+          <t>Adaptaciones conductuales</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
         <v>2.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" t="n">
-        <v>9.5</v>
       </c>
       <c r="K55" t="n">
         <v>2</v>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M55" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="R55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB55" t="n">
+      <c r="U55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC55" t="n">
         <v>1</v>
       </c>
       <c r="AD55" t="n">
         <v>1</v>
       </c>
-      <c r="AF55" t="n">
-        <v>2</v>
+      <c r="AE55" t="n">
+        <v>1</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>previo</t>
         </is>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sistema digestivo</t>
+          <t>ADN y cromosomas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>9</v>
+      </c>
+      <c r="E56" t="n">
+        <v>9</v>
       </c>
       <c r="F56" t="n">
         <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="J56" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L56" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="M56" t="n">
         <v>7</v>
       </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="T56" t="n">
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
         <v>1</v>
       </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
+      <c r="Y56" t="n">
+        <v>1</v>
+      </c>
       <c r="Z56" t="n">
         <v>1</v>
       </c>
@@ -4628,51 +4580,54 @@
       <c r="AD56" t="n">
         <v>1</v>
       </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
       <c r="AF56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sistema excretor</t>
+          <t>Agricultura y seguridad alimentaria</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>11</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>5</v>
-      </c>
-      <c r="I57" t="n">
-        <v>5</v>
-      </c>
-      <c r="J57" t="n">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2</v>
       </c>
       <c r="L57" t="n">
-        <v>9.5</v>
+        <v>11</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4.5</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
@@ -4683,7 +4638,7 @@
       <c r="U57" t="n">
         <v>1</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>1</v>
       </c>
       <c r="Y57" t="n">
@@ -4699,35 +4654,38 @@
         <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sistema locomotor</t>
+          <t>Amenazas a la biodiversidad</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>9</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
         <v>2</v>
@@ -4736,14 +4694,17 @@
         <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>9.5</v>
       </c>
       <c r="J58" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="K58" t="n">
         <v>2</v>
       </c>
+      <c r="L58" t="n">
+        <v>6</v>
+      </c>
       <c r="M58" t="n">
         <v>4.5</v>
       </c>
@@ -4753,30 +4714,54 @@
       <c r="P58" t="n">
         <v>1</v>
       </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1</v>
+      </c>
       <c r="Z58" t="n">
         <v>1</v>
       </c>
+      <c r="AA58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1</v>
+      </c>
       <c r="AD58" t="n">
         <v>1</v>
       </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
       <c r="AF58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Acervo génico y frecuencias alélicas</t>
+          <t>ATP y energía en los sistemas vivos</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4785,10 +4770,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
         <v>10.5</v>
@@ -4796,11 +4781,17 @@
       <c r="G59" t="n">
         <v>8.5</v>
       </c>
+      <c r="H59" t="n">
+        <v>7</v>
+      </c>
+      <c r="I59" t="n">
+        <v>9.5</v>
+      </c>
       <c r="J59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L59" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M59" t="n">
         <v>9.5</v>
@@ -4811,6 +4802,9 @@
       <c r="P59" t="n">
         <v>1</v>
       </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
       <c r="S59" t="n">
         <v>1</v>
       </c>
@@ -4823,6 +4817,9 @@
       <c r="W59" t="n">
         <v>1</v>
       </c>
+      <c r="X59" t="n">
+        <v>1</v>
+      </c>
       <c r="Y59" t="n">
         <v>1</v>
       </c>
@@ -4832,6 +4829,12 @@
       <c r="AA59" t="n">
         <v>1</v>
       </c>
+      <c r="AB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1</v>
+      </c>
       <c r="AD59" t="n">
         <v>1</v>
       </c>
@@ -4839,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="AF59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -4855,7 +4858,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Adaptaciones conductuales</t>
+          <t>Atributos de las poblaciones</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4864,25 +4867,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
-      </c>
-      <c r="E60" t="n">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="D60" t="n">
+        <v>11</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>3</v>
-      </c>
-      <c r="I60" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K60" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="G60" t="n">
+        <v>8.5</v>
       </c>
       <c r="L60" t="n">
         <v>6</v>
@@ -4893,7 +4887,7 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="U60" t="n">
+      <c r="P60" t="n">
         <v>1</v>
       </c>
       <c r="W60" t="n">
@@ -4902,33 +4896,36 @@
       <c r="Y60" t="n">
         <v>1</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="Z60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB60" t="n">
         <v>1</v>
       </c>
       <c r="AC60" t="n">
         <v>1</v>
       </c>
-      <c r="AD60" t="n">
-        <v>1</v>
-      </c>
       <c r="AE60" t="n">
         <v>1</v>
       </c>
+      <c r="AF60" t="n">
+        <v>7</v>
+      </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>previo</t>
+          <t>retomado</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>faltante</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADN y cromosomas</t>
+          <t>Biodiversidad</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4937,31 +4934,37 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
         <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F61" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G61" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" t="n">
         <v>6</v>
       </c>
-      <c r="I61" t="n">
-        <v>9.5</v>
-      </c>
       <c r="J61" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2</v>
       </c>
       <c r="L61" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="M61" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="N61" t="n">
         <v>1</v>
@@ -4987,12 +4990,18 @@
       <c r="W61" t="n">
         <v>1</v>
       </c>
+      <c r="X61" t="n">
+        <v>1</v>
+      </c>
       <c r="Y61" t="n">
         <v>1</v>
       </c>
       <c r="Z61" t="n">
         <v>1</v>
       </c>
+      <c r="AA61" t="n">
+        <v>1</v>
+      </c>
       <c r="AB61" t="n">
         <v>1</v>
       </c>
@@ -5006,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="AF61" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -5022,7 +5031,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Agricultura y seguridad alimentaria</t>
+          <t>Biomoléculas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5031,52 +5040,73 @@
         </is>
       </c>
       <c r="C62" t="n">
+        <v>6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" t="n">
+        <v>8</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H62" t="n">
         <v>2</v>
       </c>
-      <c r="D62" t="n">
-        <v>11</v>
-      </c>
-      <c r="F62" t="n">
-        <v>5</v>
-      </c>
-      <c r="G62" t="n">
+      <c r="J62" t="n">
+        <v>7</v>
+      </c>
+      <c r="L62" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>7</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF62" t="n">
         <v>6</v>
-      </c>
-      <c r="K62" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" t="n">
-        <v>11</v>
-      </c>
-      <c r="M62" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" t="n">
-        <v>1</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1</v>
-      </c>
-      <c r="X62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>2</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -5092,7 +5122,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Amenazas a la biodiversidad</t>
+          <t>Biotecnología microbiana</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5101,19 +5131,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
-      </c>
-      <c r="G63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I63" t="n">
         <v>9.5</v>
@@ -5121,25 +5148,16 @@
       <c r="J63" t="n">
         <v>2.5</v>
       </c>
-      <c r="K63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" t="n">
-        <v>6</v>
-      </c>
       <c r="M63" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
       <c r="R63" t="n">
         <v>1</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>1</v>
       </c>
       <c r="W63" t="n">
@@ -5154,7 +5172,7 @@
       <c r="Z63" t="n">
         <v>1</v>
       </c>
-      <c r="AA63" t="n">
+      <c r="AB63" t="n">
         <v>1</v>
       </c>
       <c r="AC63" t="n">
@@ -5167,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="AF63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -5183,7 +5201,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ATP y energía en los sistemas vivos</t>
+          <t>Biotecnología vegetal y agroindustria</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5195,50 +5213,26 @@
         <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G64" t="n">
         <v>8.5</v>
       </c>
-      <c r="H64" t="n">
+      <c r="M64" t="n">
         <v>7</v>
       </c>
-      <c r="I64" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J64" t="n">
-        <v>7</v>
-      </c>
-      <c r="L64" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M64" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O64" t="n">
         <v>1</v>
       </c>
       <c r="P64" t="n">
         <v>1</v>
       </c>
-      <c r="R64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1</v>
-      </c>
       <c r="V64" t="n">
         <v>1</v>
       </c>
-      <c r="W64" t="n">
-        <v>1</v>
-      </c>
       <c r="X64" t="n">
         <v>1</v>
       </c>
@@ -5246,9 +5240,6 @@
         <v>1</v>
       </c>
       <c r="Z64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA64" t="n">
         <v>1</v>
       </c>
       <c r="AB64" t="n">
@@ -5280,7 +5271,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Atributos de las poblaciones</t>
+          <t>Célula procariota y eucariota</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5289,10 +5280,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F65" t="n">
         <v>8</v>
@@ -5300,38 +5291,56 @@
       <c r="G65" t="n">
         <v>8.5</v>
       </c>
+      <c r="I65" t="n">
+        <v>9.5</v>
+      </c>
       <c r="L65" t="n">
+        <v>11</v>
+      </c>
+      <c r="M65" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
         <v>6</v>
-      </c>
-      <c r="M65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>7</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -5347,7 +5356,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Biodiversidad</t>
+          <t>Ciclo de vida de las plantas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5359,13 +5368,13 @@
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -5374,7 +5383,7 @@
         <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J66" t="n">
         <v>2.5</v>
@@ -5388,46 +5397,13 @@
       <c r="M66" t="n">
         <v>2.5</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
       <c r="O66" t="n">
         <v>1</v>
       </c>
-      <c r="P66" t="n">
-        <v>1</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1</v>
-      </c>
-      <c r="X66" t="n">
-        <v>1</v>
-      </c>
       <c r="Y66" t="n">
         <v>1</v>
       </c>
       <c r="Z66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC66" t="n">
         <v>1</v>
       </c>
       <c r="AD66" t="n">
@@ -5453,7 +5429,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Biomoléculas</t>
+          <t>Ciclos del carbono y del oxígeno</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5465,25 +5441,34 @@
         <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E67" t="n">
+        <v>8</v>
       </c>
       <c r="F67" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G67" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H67" t="n">
+        <v>5</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K67" t="n">
         <v>2</v>
-      </c>
-      <c r="J67" t="n">
-        <v>7</v>
       </c>
       <c r="L67" t="n">
         <v>7.5</v>
       </c>
       <c r="M67" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O67" t="n">
         <v>1</v>
@@ -5491,7 +5476,10 @@
       <c r="P67" t="n">
         <v>1</v>
       </c>
-      <c r="S67" t="n">
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
@@ -5528,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
@@ -5544,7 +5532,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Biotecnología microbiana</t>
+          <t>Circulación e intercambio capilar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5553,7 +5541,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
         <v>11</v>
@@ -5561,53 +5549,41 @@
       <c r="F68" t="n">
         <v>8</v>
       </c>
+      <c r="G68" t="n">
+        <v>8.5</v>
+      </c>
       <c r="H68" t="n">
         <v>7</v>
       </c>
-      <c r="I68" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J68" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M68" t="n">
-        <v>7</v>
+      <c r="L68" t="n">
+        <v>7.5</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
-      <c r="V68" t="n">
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
         <v>1</v>
       </c>
       <c r="W68" t="n">
         <v>1</v>
       </c>
-      <c r="X68" t="n">
-        <v>1</v>
-      </c>
       <c r="Y68" t="n">
         <v>1</v>
       </c>
       <c r="Z68" t="n">
         <v>1</v>
       </c>
-      <c r="AB68" t="n">
-        <v>1</v>
-      </c>
       <c r="AC68" t="n">
         <v>1</v>
       </c>
       <c r="AD68" t="n">
         <v>1</v>
       </c>
-      <c r="AE68" t="n">
-        <v>1</v>
-      </c>
       <c r="AF68" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AG68" t="inlineStr">
         <is>
@@ -5616,14 +5592,14 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>alineado</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Biotecnología vegetal y agroindustria</t>
+          <t>Clasificación jerárquica y nomenclatura</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5632,30 +5608,39 @@
         </is>
       </c>
       <c r="C69" t="n">
+        <v>7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="n">
         <v>6</v>
       </c>
-      <c r="D69" t="n">
-        <v>9</v>
-      </c>
       <c r="F69" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
         <v>8.5</v>
       </c>
+      <c r="H69" t="n">
+        <v>7</v>
+      </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
+      <c r="K69" t="n">
+        <v>5</v>
+      </c>
       <c r="M69" t="n">
         <v>7</v>
       </c>
-      <c r="O69" t="n">
-        <v>1</v>
-      </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
       <c r="V69" t="n">
         <v>1</v>
       </c>
-      <c r="X69" t="n">
+      <c r="W69" t="n">
         <v>1</v>
       </c>
       <c r="Y69" t="n">
@@ -5673,11 +5658,8 @@
       <c r="AD69" t="n">
         <v>1</v>
       </c>
-      <c r="AE69" t="n">
-        <v>1</v>
-      </c>
       <c r="AF69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG69" t="inlineStr">
         <is>
@@ -5693,7 +5675,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Célula procariota y eucariota</t>
+          <t>Concepto de especie</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5702,41 +5684,32 @@
         </is>
       </c>
       <c r="C70" t="n">
+        <v>7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>11</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G70" t="n">
         <v>6</v>
       </c>
-      <c r="D70" t="n">
-        <v>9</v>
-      </c>
-      <c r="F70" t="n">
-        <v>8</v>
-      </c>
-      <c r="G70" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I70" t="n">
-        <v>9.5</v>
+      <c r="J70" t="n">
+        <v>7</v>
       </c>
       <c r="L70" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M70" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="P70" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
       <c r="U70" t="n">
         <v>1</v>
       </c>
-      <c r="V70" t="n">
-        <v>1</v>
-      </c>
       <c r="W70" t="n">
         <v>1</v>
       </c>
@@ -5746,12 +5719,6 @@
       <c r="Z70" t="n">
         <v>1</v>
       </c>
-      <c r="AA70" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>1</v>
-      </c>
       <c r="AC70" t="n">
         <v>1</v>
       </c>
@@ -5762,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="AF70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG70" t="inlineStr">
         <is>
@@ -5778,7 +5745,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las plantas</t>
+          <t>Conservación de la biodiversidad</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5790,22 +5757,19 @@
         <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>11</v>
-      </c>
-      <c r="E71" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F71" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H71" t="n">
         <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J71" t="n">
         <v>2.5</v>
@@ -5814,12 +5778,24 @@
         <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="M71" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
         <v>1</v>
       </c>
       <c r="Y71" t="n">
@@ -5851,7 +5827,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ciclos del carbono y del oxígeno</t>
+          <t>Conservación e inocuidad de los alimentos</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5860,85 +5836,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>9</v>
-      </c>
-      <c r="E72" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" t="n">
         <v>8</v>
       </c>
-      <c r="F72" t="n">
-        <v>5</v>
-      </c>
-      <c r="G72" t="n">
-        <v>6</v>
-      </c>
       <c r="H72" t="n">
-        <v>5</v>
-      </c>
-      <c r="I72" t="n">
-        <v>5</v>
-      </c>
-      <c r="J72" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K72" t="n">
         <v>2</v>
       </c>
-      <c r="L72" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M72" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O72" t="n">
         <v>1</v>
       </c>
-      <c r="P72" t="n">
-        <v>1</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
-      <c r="T72" t="n">
-        <v>1</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1</v>
-      </c>
-      <c r="V72" t="n">
-        <v>1</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1</v>
-      </c>
-      <c r="X72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>1</v>
-      </c>
       <c r="Z72" t="n">
         <v>1</v>
       </c>
-      <c r="AA72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE72" t="n">
-        <v>1</v>
-      </c>
       <c r="AF72" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
@@ -5954,7 +5870,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Circulación e intercambio capilar</t>
+          <t>Contagio y prevención de enfermedades</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5963,10 +5879,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>8</v>
@@ -5975,10 +5891,16 @@
         <v>8.5</v>
       </c>
       <c r="H73" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>9</v>
       </c>
       <c r="L73" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5986,6 +5908,9 @@
       <c r="P73" t="n">
         <v>1</v>
       </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
       <c r="U73" t="n">
         <v>1</v>
       </c>
@@ -5998,14 +5923,11 @@
       <c r="Z73" t="n">
         <v>1</v>
       </c>
-      <c r="AC73" t="n">
-        <v>1</v>
-      </c>
       <c r="AD73" t="n">
         <v>1</v>
       </c>
       <c r="AF73" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr">
         <is>
@@ -6014,14 +5936,14 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>alineado</t>
+          <t>retomado</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Clasificación jerárquica y nomenclatura</t>
+          <t>Contaminación y sus efectos en los seres vivos</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6030,44 +5952,38 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>10</v>
-      </c>
-      <c r="E74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F74" t="n">
         <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H74" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="K74" t="n">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="L74" t="n">
+        <v>6</v>
       </c>
       <c r="M74" t="n">
-        <v>7</v>
-      </c>
-      <c r="P74" t="n">
-        <v>1</v>
-      </c>
-      <c r="V74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U74" t="n">
         <v>1</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
-      <c r="Y74" t="n">
-        <v>1</v>
-      </c>
       <c r="Z74" t="n">
         <v>1</v>
       </c>
@@ -6081,7 +5997,7 @@
         <v>1</v>
       </c>
       <c r="AF74" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
@@ -6097,7 +6013,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Concepto de especie</t>
+          <t>Crecimiento poblacional</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6112,27 +6028,30 @@
         <v>11</v>
       </c>
       <c r="F75" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G75" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>7</v>
       </c>
       <c r="J75" t="n">
+        <v>9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M75" t="n">
         <v>7</v>
       </c>
-      <c r="L75" t="n">
-        <v>6</v>
-      </c>
-      <c r="M75" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O75" t="n">
         <v>1</v>
       </c>
-      <c r="U75" t="n">
-        <v>1</v>
-      </c>
-      <c r="W75" t="n">
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
         <v>1</v>
       </c>
       <c r="Y75" t="n">
@@ -6141,10 +6060,10 @@
       <c r="Z75" t="n">
         <v>1</v>
       </c>
+      <c r="AA75" t="n">
+        <v>1</v>
+      </c>
       <c r="AC75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD75" t="n">
         <v>1</v>
       </c>
       <c r="AE75" t="n">
@@ -6167,7 +6086,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Conservación de la biodiversidad</t>
+          <t>Diferenciación y especialización celular</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6176,34 +6095,34 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E76" t="n">
+        <v>7</v>
       </c>
       <c r="F76" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="G76" t="n">
         <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
-      </c>
-      <c r="I76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J76" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L76" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="M76" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
@@ -6211,21 +6130,33 @@
       <c r="P76" t="n">
         <v>1</v>
       </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="n">
+      <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
         <v>1</v>
       </c>
+      <c r="V76" t="n">
+        <v>1</v>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X76" t="n">
+        <v>1</v>
+      </c>
       <c r="Y76" t="n">
         <v>1</v>
       </c>
       <c r="Z76" t="n">
         <v>1</v>
       </c>
+      <c r="AA76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>1</v>
+      </c>
       <c r="AD76" t="n">
         <v>1</v>
       </c>
@@ -6233,7 +6164,7 @@
         <v>1</v>
       </c>
       <c r="AF76" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
@@ -6249,7 +6180,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Conservación e inocuidad de los alimentos</t>
+          <t>Difusión y ósmosis</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6258,25 +6189,61 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F77" t="n">
-        <v>8</v>
-      </c>
-      <c r="H77" t="n">
-        <v>2</v>
+        <v>10.5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>6</v>
+      </c>
+      <c r="J77" t="n">
+        <v>9</v>
+      </c>
+      <c r="K77" t="n">
+        <v>7</v>
+      </c>
+      <c r="L77" t="n">
+        <v>7.5</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
       </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
+      </c>
+      <c r="W77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1</v>
+      </c>
       <c r="Z77" t="n">
         <v>1</v>
       </c>
+      <c r="AB77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1</v>
+      </c>
       <c r="AF77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
@@ -6292,7 +6259,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Contagio y prevención de enfermedades</t>
+          <t>Digestión química y absorción de nutrientes</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6301,55 +6268,52 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F78" t="n">
         <v>8</v>
       </c>
       <c r="G78" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H78" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="I78" t="n">
+        <v>5</v>
       </c>
       <c r="J78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K78" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L78" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
+      </c>
+      <c r="M78" t="n">
+        <v>7</v>
       </c>
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="P78" t="n">
-        <v>1</v>
-      </c>
-      <c r="T78" t="n">
-        <v>1</v>
-      </c>
       <c r="U78" t="n">
         <v>1</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
-      <c r="Y78" t="n">
-        <v>1</v>
-      </c>
       <c r="Z78" t="n">
         <v>1</v>
       </c>
+      <c r="AB78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>1</v>
+      </c>
       <c r="AD78" t="n">
         <v>1</v>
       </c>
       <c r="AF78" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
@@ -6365,7 +6329,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Contaminación y sus efectos en los seres vivos</t>
+          <t>Diversidad genética de poblaciones</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6374,31 +6338,34 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F79" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>7</v>
+      </c>
+      <c r="K79" t="n">
         <v>5</v>
       </c>
-      <c r="G79" t="n">
-        <v>6</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2</v>
-      </c>
-      <c r="J79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K79" t="n">
-        <v>4</v>
-      </c>
       <c r="L79" t="n">
-        <v>6</v>
-      </c>
-      <c r="M79" t="n">
-        <v>2.5</v>
+        <v>11</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
       </c>
       <c r="U79" t="n">
         <v>1</v>
@@ -6406,6 +6373,9 @@
       <c r="W79" t="n">
         <v>1</v>
       </c>
+      <c r="Y79" t="n">
+        <v>1</v>
+      </c>
       <c r="Z79" t="n">
         <v>1</v>
       </c>
@@ -6418,8 +6388,11 @@
       <c r="AD79" t="n">
         <v>1</v>
       </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
       <c r="AF79" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
@@ -6435,7 +6408,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Crecimiento poblacional</t>
+          <t>Ecosistemas acuáticos y marinos</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6444,55 +6417,37 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D80" t="n">
-        <v>11</v>
-      </c>
-      <c r="F80" t="n">
-        <v>8</v>
-      </c>
-      <c r="G80" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="H80" t="n">
         <v>7</v>
       </c>
       <c r="J80" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="L80" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M80" t="n">
-        <v>7</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y80" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="U80" t="n">
         <v>1</v>
       </c>
       <c r="Z80" t="n">
         <v>1</v>
       </c>
-      <c r="AA80" t="n">
-        <v>1</v>
-      </c>
       <c r="AC80" t="n">
         <v>1</v>
       </c>
+      <c r="AD80" t="n">
+        <v>1</v>
+      </c>
       <c r="AE80" t="n">
         <v>1</v>
       </c>
       <c r="AF80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
@@ -6508,7 +6463,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Diferenciación y especialización celular</t>
+          <t>Energía de los alimentos y balance energético</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6517,76 +6472,49 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
-      </c>
-      <c r="E81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F81" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G81" t="n">
         <v>6</v>
       </c>
       <c r="H81" t="n">
-        <v>7</v>
-      </c>
-      <c r="J81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L81" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M81" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
-      <c r="T81" t="n">
-        <v>1</v>
-      </c>
       <c r="U81" t="n">
         <v>1</v>
       </c>
-      <c r="V81" t="n">
-        <v>1</v>
-      </c>
-      <c r="W81" t="n">
-        <v>1</v>
-      </c>
       <c r="X81" t="n">
         <v>1</v>
       </c>
-      <c r="Y81" t="n">
-        <v>1</v>
-      </c>
       <c r="Z81" t="n">
         <v>1</v>
       </c>
-      <c r="AA81" t="n">
-        <v>1</v>
-      </c>
       <c r="AB81" t="n">
         <v>1</v>
       </c>
+      <c r="AC81" t="n">
+        <v>1</v>
+      </c>
       <c r="AD81" t="n">
         <v>1</v>
       </c>
-      <c r="AE81" t="n">
-        <v>1</v>
-      </c>
       <c r="AF81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
@@ -6602,7 +6530,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Difusión y ósmosis</t>
+          <t>Enfermedades infecciosas y no infecciosas</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6611,22 +6539,25 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
         <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G82" t="n">
         <v>6</v>
       </c>
+      <c r="H82" t="n">
+        <v>3</v>
+      </c>
       <c r="J82" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L82" t="n">
         <v>7.5</v>
@@ -6640,12 +6571,18 @@
       <c r="S82" t="n">
         <v>1</v>
       </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
       <c r="U82" t="n">
         <v>1</v>
       </c>
       <c r="W82" t="n">
         <v>1</v>
       </c>
+      <c r="X82" t="n">
+        <v>1</v>
+      </c>
       <c r="Y82" t="n">
         <v>1</v>
       </c>
@@ -6661,11 +6598,8 @@
       <c r="AD82" t="n">
         <v>1</v>
       </c>
-      <c r="AE82" t="n">
-        <v>1</v>
-      </c>
       <c r="AF82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
@@ -6681,7 +6615,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Digestión química y absorción de nutrientes</t>
+          <t>Enzimas</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6690,19 +6624,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
         <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="G83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="J83" t="n">
         <v>7</v>
@@ -6716,15 +6650,33 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
       <c r="U83" t="n">
         <v>1</v>
       </c>
       <c r="W83" t="n">
         <v>1</v>
       </c>
+      <c r="X83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>1</v>
+      </c>
       <c r="Z83" t="n">
         <v>1</v>
       </c>
+      <c r="AA83" t="n">
+        <v>1</v>
+      </c>
       <c r="AB83" t="n">
         <v>1</v>
       </c>
@@ -6734,8 +6686,11 @@
       <c r="AD83" t="n">
         <v>1</v>
       </c>
+      <c r="AE83" t="n">
+        <v>1</v>
+      </c>
       <c r="AF83" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG83" t="inlineStr">
         <is>
@@ -6751,7 +6706,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Diversidad genética de poblaciones</t>
+          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6760,61 +6715,34 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
         <v>11</v>
       </c>
       <c r="F84" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G84" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J84" t="n">
-        <v>7</v>
-      </c>
-      <c r="K84" t="n">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3</v>
       </c>
       <c r="L84" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="M84" t="n">
+        <v>4.5</v>
       </c>
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="P84" t="n">
-        <v>1</v>
-      </c>
-      <c r="S84" t="n">
-        <v>1</v>
-      </c>
-      <c r="U84" t="n">
-        <v>1</v>
-      </c>
-      <c r="W84" t="n">
-        <v>1</v>
-      </c>
       <c r="Y84" t="n">
         <v>1</v>
       </c>
       <c r="Z84" t="n">
         <v>1</v>
       </c>
-      <c r="AB84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>1</v>
-      </c>
       <c r="AF84" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG84" t="inlineStr">
         <is>
@@ -6830,7 +6758,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ecosistemas acuáticos y marinos</t>
+          <t>Estructura del ADN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6839,26 +6767,59 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
         <v>9</v>
       </c>
-      <c r="H85" t="n">
-        <v>7</v>
+      <c r="F85" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>6</v>
+      </c>
+      <c r="I85" t="n">
+        <v>9.5</v>
       </c>
       <c r="J85" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="L85" t="n">
         <v>9.5</v>
       </c>
+      <c r="M85" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
       <c r="U85" t="n">
         <v>1</v>
       </c>
+      <c r="V85" t="n">
+        <v>1</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1</v>
+      </c>
       <c r="Z85" t="n">
         <v>1</v>
       </c>
+      <c r="AB85" t="n">
+        <v>1</v>
+      </c>
       <c r="AC85" t="n">
         <v>1</v>
       </c>
@@ -6869,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="AF85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
@@ -6885,7 +6846,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Energía de los alimentos y balance energético</t>
+          <t>Estructuras celulares básicas</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6894,11 +6855,14 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D86" t="n">
         <v>9</v>
       </c>
+      <c r="E86" t="n">
+        <v>7</v>
+      </c>
       <c r="F86" t="n">
         <v>8</v>
       </c>
@@ -6906,26 +6870,47 @@
         <v>6</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="J86" t="n">
+        <v>4.5</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L86" t="n">
-        <v>6</v>
+        <v>7.5</v>
+      </c>
+      <c r="M86" t="n">
+        <v>7</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
       </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1</v>
+      </c>
       <c r="U86" t="n">
         <v>1</v>
       </c>
-      <c r="X86" t="n">
+      <c r="V86" t="n">
+        <v>1</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y86" t="n">
         <v>1</v>
       </c>
       <c r="Z86" t="n">
         <v>1</v>
       </c>
+      <c r="AA86" t="n">
+        <v>1</v>
+      </c>
       <c r="AB86" t="n">
         <v>1</v>
       </c>
@@ -6936,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="AF86" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG86" t="inlineStr">
         <is>
@@ -6945,14 +6930,14 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Enfermedades infecciosas y no infecciosas</t>
+          <t>Estructuras del cuerpo animal y su función</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6961,28 +6946,37 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E87" t="n">
+        <v>7</v>
       </c>
       <c r="F87" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" t="n">
         <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>2.5</v>
       </c>
       <c r="K87" t="n">
+        <v>2</v>
+      </c>
+      <c r="L87" t="n">
         <v>4</v>
       </c>
-      <c r="L87" t="n">
-        <v>7.5</v>
+      <c r="M87" t="n">
+        <v>2.5</v>
       </c>
       <c r="O87" t="n">
         <v>1</v>
@@ -6990,7 +6984,7 @@
       <c r="P87" t="n">
         <v>1</v>
       </c>
-      <c r="S87" t="n">
+      <c r="R87" t="n">
         <v>1</v>
       </c>
       <c r="T87" t="n">
@@ -7002,9 +6996,6 @@
       <c r="W87" t="n">
         <v>1</v>
       </c>
-      <c r="X87" t="n">
-        <v>1</v>
-      </c>
       <c r="Y87" t="n">
         <v>1</v>
       </c>
@@ -7020,8 +7011,11 @@
       <c r="AD87" t="n">
         <v>1</v>
       </c>
+      <c r="AE87" t="n">
+        <v>1</v>
+      </c>
       <c r="AF87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
@@ -7037,7 +7031,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enzimas</t>
+          <t>Extinción de especies</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7046,73 +7040,58 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G88" t="n">
         <v>6</v>
       </c>
+      <c r="H88" t="n">
+        <v>5</v>
+      </c>
       <c r="I88" t="n">
         <v>9.5</v>
       </c>
       <c r="J88" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3</v>
       </c>
       <c r="L88" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="M88" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="P88" t="n">
-        <v>1</v>
-      </c>
       <c r="R88" t="n">
         <v>1</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
       </c>
-      <c r="U88" t="n">
-        <v>1</v>
-      </c>
       <c r="W88" t="n">
         <v>1</v>
       </c>
       <c r="X88" t="n">
         <v>1</v>
       </c>
-      <c r="Y88" t="n">
-        <v>1</v>
-      </c>
       <c r="Z88" t="n">
         <v>1</v>
       </c>
-      <c r="AA88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>1</v>
-      </c>
       <c r="AC88" t="n">
         <v>1</v>
       </c>
-      <c r="AD88" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>1</v>
-      </c>
       <c r="AF88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG88" t="inlineStr">
         <is>
@@ -7128,7 +7107,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Estrategias reproductivas y supervivencia de la descendencia</t>
+          <t>Factores bióticos y abióticos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7137,34 +7116,76 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
       </c>
       <c r="F89" t="n">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>6</v>
       </c>
       <c r="H89" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="I89" t="n">
+        <v>5</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M89" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O89" t="n">
         <v>1</v>
       </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
+        <v>1</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1</v>
+      </c>
       <c r="Y89" t="n">
         <v>1</v>
       </c>
       <c r="Z89" t="n">
         <v>1</v>
       </c>
+      <c r="AA89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>1</v>
+      </c>
       <c r="AF89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
@@ -7180,7 +7201,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Estructura del ADN</t>
+          <t>Factores limitantes de las poblaciones</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7189,28 +7210,28 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F90" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>6</v>
-      </c>
-      <c r="I90" t="n">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="J90" t="n">
         <v>9</v>
       </c>
+      <c r="K90" t="n">
+        <v>3</v>
+      </c>
       <c r="L90" t="n">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="M90" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O90" t="n">
         <v>1</v>
@@ -7218,18 +7239,9 @@
       <c r="P90" t="n">
         <v>1</v>
       </c>
-      <c r="R90" t="n">
-        <v>1</v>
-      </c>
       <c r="S90" t="n">
         <v>1</v>
       </c>
-      <c r="U90" t="n">
-        <v>1</v>
-      </c>
-      <c r="V90" t="n">
-        <v>1</v>
-      </c>
       <c r="W90" t="n">
         <v>1</v>
       </c>
@@ -7239,20 +7251,17 @@
       <c r="Z90" t="n">
         <v>1</v>
       </c>
-      <c r="AB90" t="n">
+      <c r="AA90" t="n">
         <v>1</v>
       </c>
       <c r="AC90" t="n">
         <v>1</v>
       </c>
-      <c r="AD90" t="n">
-        <v>1</v>
-      </c>
       <c r="AE90" t="n">
         <v>1</v>
       </c>
       <c r="AF90" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AG90" t="inlineStr">
         <is>
@@ -7261,14 +7270,14 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>tardio</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Estructuras del cuerpo animal y su función</t>
+          <t>Fermentación y respiración anaerobia</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7277,76 +7286,52 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>10</v>
-      </c>
-      <c r="E91" t="n">
+        <v>9</v>
+      </c>
+      <c r="F91" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>6</v>
+      </c>
+      <c r="L91" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M91" t="n">
         <v>7</v>
       </c>
-      <c r="F91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G91" t="n">
-        <v>2</v>
-      </c>
-      <c r="H91" t="n">
-        <v>2</v>
-      </c>
-      <c r="I91" t="n">
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF91" t="n">
         <v>3</v>
-      </c>
-      <c r="J91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2</v>
-      </c>
-      <c r="L91" t="n">
-        <v>4</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O91" t="n">
-        <v>1</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1</v>
-      </c>
-      <c r="T91" t="n">
-        <v>1</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1</v>
-      </c>
-      <c r="W91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>2</v>
       </c>
       <c r="AG91" t="inlineStr">
         <is>
@@ -7362,7 +7347,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Extinción de especies</t>
+          <t>Filogenia y parentesco evolutivo</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7371,58 +7356,58 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D92" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F92" t="n">
         <v>8</v>
       </c>
       <c r="G92" t="n">
-        <v>6</v>
-      </c>
-      <c r="H92" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="I92" t="n">
         <v>9.5</v>
       </c>
-      <c r="J92" t="n">
-        <v>9</v>
-      </c>
-      <c r="K92" t="n">
-        <v>3</v>
-      </c>
-      <c r="L92" t="n">
-        <v>6</v>
-      </c>
       <c r="M92" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
       </c>
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
       <c r="R92" t="n">
         <v>1</v>
       </c>
-      <c r="S92" t="n">
+      <c r="V92" t="n">
         <v>1</v>
       </c>
       <c r="W92" t="n">
         <v>1</v>
       </c>
-      <c r="X92" t="n">
+      <c r="Y92" t="n">
         <v>1</v>
       </c>
       <c r="Z92" t="n">
         <v>1</v>
       </c>
+      <c r="AA92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>1</v>
+      </c>
       <c r="AC92" t="n">
         <v>1</v>
       </c>
+      <c r="AD92" t="n">
+        <v>1</v>
+      </c>
       <c r="AF92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
@@ -7438,7 +7423,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Factores bióticos y abióticos</t>
+          <t>Flujo de energía y pirámides ecológicas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7447,76 +7432,79 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
         <v>9</v>
       </c>
       <c r="E93" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H93" t="n">
         <v>5</v>
       </c>
-      <c r="F93" t="n">
+      <c r="J93" t="n">
+        <v>9</v>
+      </c>
+      <c r="K93" t="n">
+        <v>6</v>
+      </c>
+      <c r="L93" t="n">
+        <v>6</v>
+      </c>
+      <c r="M93" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" t="n">
+        <v>1</v>
+      </c>
+      <c r="W93" t="n">
+        <v>1</v>
+      </c>
+      <c r="X93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF93" t="n">
         <v>5</v>
-      </c>
-      <c r="G93" t="n">
-        <v>6</v>
-      </c>
-      <c r="H93" t="n">
-        <v>2</v>
-      </c>
-      <c r="I93" t="n">
-        <v>5</v>
-      </c>
-      <c r="J93" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K93" t="n">
-        <v>2</v>
-      </c>
-      <c r="L93" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M93" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O93" t="n">
-        <v>1</v>
-      </c>
-      <c r="P93" t="n">
-        <v>1</v>
-      </c>
-      <c r="R93" t="n">
-        <v>1</v>
-      </c>
-      <c r="S93" t="n">
-        <v>1</v>
-      </c>
-      <c r="U93" t="n">
-        <v>1</v>
-      </c>
-      <c r="W93" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF93" t="n">
-        <v>4</v>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
@@ -7532,7 +7520,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Fermentación y respiración anaerobia</t>
+          <t>Fósiles y registro fósil</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7547,16 +7535,25 @@
         <v>9</v>
       </c>
       <c r="F94" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="G94" t="n">
-        <v>6</v>
-      </c>
-      <c r="L94" t="n">
-        <v>9.5</v>
+        <v>2</v>
+      </c>
+      <c r="H94" t="n">
+        <v>4</v>
+      </c>
+      <c r="I94" t="n">
+        <v>5</v>
+      </c>
+      <c r="J94" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K94" t="n">
+        <v>3</v>
       </c>
       <c r="M94" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O94" t="n">
         <v>1</v>
@@ -7564,7 +7561,16 @@
       <c r="P94" t="n">
         <v>1</v>
       </c>
-      <c r="U94" t="n">
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="n">
+        <v>1</v>
+      </c>
+      <c r="W94" t="n">
         <v>1</v>
       </c>
       <c r="Y94" t="n">
@@ -7577,9 +7583,6 @@
         <v>1</v>
       </c>
       <c r="AC94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD94" t="n">
         <v>1</v>
       </c>
       <c r="AE94" t="n">
@@ -7602,7 +7605,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Filogenia y parentesco evolutivo</t>
+          <t>Fotosíntesis</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7611,22 +7614,37 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D95" t="n">
         <v>9</v>
       </c>
+      <c r="E95" t="n">
+        <v>8</v>
+      </c>
       <c r="F95" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G95" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>5</v>
+      </c>
+      <c r="J95" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K95" t="n">
+        <v>2</v>
+      </c>
+      <c r="L95" t="n">
+        <v>6</v>
       </c>
       <c r="M95" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -7637,12 +7655,18 @@
       <c r="R95" t="n">
         <v>1</v>
       </c>
+      <c r="U95" t="n">
+        <v>1</v>
+      </c>
       <c r="V95" t="n">
         <v>1</v>
       </c>
       <c r="W95" t="n">
         <v>1</v>
       </c>
+      <c r="X95" t="n">
+        <v>1</v>
+      </c>
       <c r="Y95" t="n">
         <v>1</v>
       </c>
@@ -7661,8 +7685,11 @@
       <c r="AD95" t="n">
         <v>1</v>
       </c>
+      <c r="AE95" t="n">
+        <v>1</v>
+      </c>
       <c r="AF95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
@@ -7678,7 +7705,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Flujo de energía y pirámides ecológicas</t>
+          <t>Genes y alelos</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7687,34 +7714,37 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
         <v>9</v>
       </c>
       <c r="E96" t="n">
+        <v>9</v>
+      </c>
+      <c r="F96" t="n">
+        <v>8</v>
+      </c>
+      <c r="G96" t="n">
         <v>6</v>
       </c>
-      <c r="F96" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G96" t="n">
-        <v>8.5</v>
-      </c>
       <c r="H96" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="I96" t="n">
+        <v>8</v>
       </c>
       <c r="J96" t="n">
-        <v>9</v>
-      </c>
-      <c r="K96" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L96" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="M96" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
+      </c>
+      <c r="N96" t="n">
+        <v>1</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -7722,6 +7752,9 @@
       <c r="P96" t="n">
         <v>1</v>
       </c>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
       <c r="S96" t="n">
         <v>1</v>
       </c>
@@ -7734,9 +7767,6 @@
       <c r="W96" t="n">
         <v>1</v>
       </c>
-      <c r="X96" t="n">
-        <v>1</v>
-      </c>
       <c r="Y96" t="n">
         <v>1</v>
       </c>
@@ -7759,7 +7789,7 @@
         <v>1</v>
       </c>
       <c r="AF96" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
@@ -7775,7 +7805,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Fósiles y registro fósil</t>
+          <t>Genotipo y fenotipo</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7784,7 +7814,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D97" t="n">
         <v>9</v>
@@ -7793,22 +7823,19 @@
         <v>8</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="H97" t="n">
-        <v>4</v>
-      </c>
-      <c r="I97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K97" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="L97" t="n">
+        <v>9.5</v>
       </c>
       <c r="M97" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O97" t="n">
         <v>1</v>
@@ -7816,10 +7843,7 @@
       <c r="P97" t="n">
         <v>1</v>
       </c>
-      <c r="R97" t="n">
-        <v>1</v>
-      </c>
-      <c r="S97" t="n">
+      <c r="U97" t="n">
         <v>1</v>
       </c>
       <c r="V97" t="n">
@@ -7834,17 +7858,17 @@
       <c r="Z97" t="n">
         <v>1</v>
       </c>
-      <c r="AB97" t="n">
+      <c r="AA97" t="n">
         <v>1</v>
       </c>
       <c r="AC97" t="n">
         <v>1</v>
       </c>
-      <c r="AE97" t="n">
+      <c r="AD97" t="n">
         <v>1</v>
       </c>
       <c r="AF97" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
@@ -7860,7 +7884,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Fotosíntesis</t>
+          <t>Grupos de alimentos y dieta balanceada</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7869,82 +7893,40 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D98" t="n">
         <v>9</v>
       </c>
-      <c r="E98" t="n">
+      <c r="F98" t="n">
         <v>8</v>
       </c>
-      <c r="F98" t="n">
-        <v>5</v>
-      </c>
       <c r="G98" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
         <v>2</v>
       </c>
-      <c r="I98" t="n">
-        <v>5</v>
-      </c>
-      <c r="J98" t="n">
-        <v>4.5</v>
-      </c>
       <c r="K98" t="n">
+        <v>4</v>
+      </c>
+      <c r="L98" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
+      <c r="X98" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" t="n">
         <v>2</v>
-      </c>
-      <c r="L98" t="n">
-        <v>6</v>
-      </c>
-      <c r="M98" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O98" t="n">
-        <v>1</v>
-      </c>
-      <c r="P98" t="n">
-        <v>1</v>
-      </c>
-      <c r="R98" t="n">
-        <v>1</v>
-      </c>
-      <c r="U98" t="n">
-        <v>1</v>
-      </c>
-      <c r="V98" t="n">
-        <v>1</v>
-      </c>
-      <c r="W98" t="n">
-        <v>1</v>
-      </c>
-      <c r="X98" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y98" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF98" t="n">
-        <v>6</v>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
@@ -7960,7 +7942,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Genes y alelos</t>
+          <t>Hábitos de vida saludable</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7969,37 +7951,28 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D99" t="n">
         <v>9</v>
       </c>
-      <c r="E99" t="n">
-        <v>9</v>
-      </c>
       <c r="F99" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>7</v>
-      </c>
-      <c r="I99" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>7</v>
+        <v>2.5</v>
+      </c>
+      <c r="K99" t="n">
+        <v>4</v>
       </c>
       <c r="L99" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M99" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="N99" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
@@ -8007,30 +7980,15 @@
       <c r="P99" t="n">
         <v>1</v>
       </c>
-      <c r="R99" t="n">
-        <v>1</v>
-      </c>
-      <c r="S99" t="n">
-        <v>1</v>
-      </c>
       <c r="U99" t="n">
         <v>1</v>
       </c>
-      <c r="V99" t="n">
-        <v>1</v>
-      </c>
-      <c r="W99" t="n">
-        <v>1</v>
-      </c>
       <c r="Y99" t="n">
         <v>1</v>
       </c>
       <c r="Z99" t="n">
         <v>1</v>
       </c>
-      <c r="AA99" t="n">
-        <v>1</v>
-      </c>
       <c r="AB99" t="n">
         <v>1</v>
       </c>
@@ -8040,11 +7998,8 @@
       <c r="AD99" t="n">
         <v>1</v>
       </c>
-      <c r="AE99" t="n">
-        <v>1</v>
-      </c>
       <c r="AF99" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
@@ -8060,7 +8015,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Genotipo y fenotipo</t>
+          <t>Herencia mendeliana</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8074,6 +8029,9 @@
       <c r="D100" t="n">
         <v>9</v>
       </c>
+      <c r="E100" t="n">
+        <v>9</v>
+      </c>
       <c r="F100" t="n">
         <v>8</v>
       </c>
@@ -8081,7 +8039,10 @@
         <v>8.5</v>
       </c>
       <c r="H100" t="n">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="I100" t="n">
+        <v>8</v>
       </c>
       <c r="J100" t="n">
         <v>7</v>
@@ -8092,6 +8053,9 @@
       <c r="M100" t="n">
         <v>7</v>
       </c>
+      <c r="N100" t="n">
+        <v>1</v>
+      </c>
       <c r="O100" t="n">
         <v>1</v>
       </c>
@@ -8116,10 +8080,16 @@
       <c r="AA100" t="n">
         <v>1</v>
       </c>
+      <c r="AB100" t="n">
+        <v>1</v>
+      </c>
       <c r="AC100" t="n">
         <v>1</v>
       </c>
       <c r="AD100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE100" t="n">
         <v>1</v>
       </c>
       <c r="AF100" t="n">
@@ -8139,7 +8109,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Grupos de alimentos y dieta balanceada</t>
+          <t>Historia de la vida en la Tierra</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8151,37 +8121,58 @@
         <v>2</v>
       </c>
       <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="n">
         <v>9</v>
       </c>
       <c r="F101" t="n">
         <v>8</v>
       </c>
-      <c r="G101" t="n">
-        <v>2</v>
-      </c>
-      <c r="H101" t="n">
-        <v>2</v>
-      </c>
-      <c r="K101" t="n">
-        <v>4</v>
-      </c>
-      <c r="L101" t="n">
-        <v>7.5</v>
+      <c r="I101" t="n">
+        <v>8</v>
+      </c>
+      <c r="J101" t="n">
+        <v>9</v>
       </c>
       <c r="M101" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
       </c>
       <c r="O101" t="n">
         <v>1</v>
       </c>
-      <c r="X101" t="n">
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y101" t="n">
         <v>1</v>
       </c>
       <c r="Z101" t="n">
         <v>1</v>
       </c>
+      <c r="AA101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1</v>
+      </c>
       <c r="AF101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
@@ -8190,14 +8181,14 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Hábitos de vida saludable</t>
+          <t>Impacto humano en los ecosistemas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8220,14 +8211,20 @@
       <c r="H102" t="n">
         <v>2</v>
       </c>
+      <c r="I102" t="n">
+        <v>5</v>
+      </c>
       <c r="J102" t="n">
         <v>2.5</v>
       </c>
       <c r="K102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L102" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
@@ -8235,15 +8232,30 @@
       <c r="P102" t="n">
         <v>1</v>
       </c>
+      <c r="R102" t="n">
+        <v>1</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
       <c r="U102" t="n">
         <v>1</v>
       </c>
+      <c r="W102" t="n">
+        <v>1</v>
+      </c>
+      <c r="X102" t="n">
+        <v>1</v>
+      </c>
       <c r="Y102" t="n">
         <v>1</v>
       </c>
       <c r="Z102" t="n">
         <v>1</v>
       </c>
+      <c r="AA102" t="n">
+        <v>1</v>
+      </c>
       <c r="AB102" t="n">
         <v>1</v>
       </c>
@@ -8251,6 +8263,9 @@
         <v>1</v>
       </c>
       <c r="AD102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE102" t="n">
         <v>1</v>
       </c>
       <c r="AF102" t="n">
@@ -8270,7 +8285,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Herencia mendeliana</t>
+          <t>Inmunidad activa, pasiva y vacunas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8279,14 +8294,11 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
         <v>9</v>
       </c>
-      <c r="E103" t="n">
-        <v>9</v>
-      </c>
       <c r="F103" t="n">
         <v>8</v>
       </c>
@@ -8294,35 +8306,26 @@
         <v>8.5</v>
       </c>
       <c r="H103" t="n">
-        <v>7</v>
-      </c>
-      <c r="I103" t="n">
-        <v>8</v>
-      </c>
-      <c r="J103" t="n">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="K103" t="n">
+        <v>9</v>
       </c>
       <c r="L103" t="n">
         <v>9.5</v>
       </c>
-      <c r="M103" t="n">
-        <v>7</v>
-      </c>
-      <c r="N103" t="n">
-        <v>1</v>
-      </c>
       <c r="O103" t="n">
         <v>1</v>
       </c>
       <c r="P103" t="n">
         <v>1</v>
       </c>
+      <c r="T103" t="n">
+        <v>1</v>
+      </c>
       <c r="U103" t="n">
         <v>1</v>
       </c>
-      <c r="V103" t="n">
-        <v>1</v>
-      </c>
       <c r="W103" t="n">
         <v>1</v>
       </c>
@@ -8332,23 +8335,14 @@
       <c r="Z103" t="n">
         <v>1</v>
       </c>
-      <c r="AA103" t="n">
-        <v>1</v>
-      </c>
       <c r="AB103" t="n">
         <v>1</v>
       </c>
-      <c r="AC103" t="n">
-        <v>1</v>
-      </c>
       <c r="AD103" t="n">
         <v>1</v>
       </c>
-      <c r="AE103" t="n">
-        <v>1</v>
-      </c>
       <c r="AF103" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
@@ -8364,7 +8358,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Impacto humano en los ecosistemas</t>
+          <t>Intercambio de gases en plantas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8373,79 +8367,43 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
-      </c>
-      <c r="F104" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
-      </c>
-      <c r="H104" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I104" t="n">
+        <v>7</v>
+      </c>
+      <c r="J104" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L104" t="n">
         <v>5</v>
       </c>
-      <c r="J104" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K104" t="n">
-        <v>2</v>
-      </c>
-      <c r="L104" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M104" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O104" t="n">
-        <v>1</v>
-      </c>
       <c r="P104" t="n">
         <v>1</v>
       </c>
-      <c r="R104" t="n">
-        <v>1</v>
-      </c>
-      <c r="S104" t="n">
-        <v>1</v>
-      </c>
       <c r="U104" t="n">
         <v>1</v>
       </c>
       <c r="W104" t="n">
         <v>1</v>
       </c>
-      <c r="X104" t="n">
-        <v>1</v>
-      </c>
       <c r="Y104" t="n">
         <v>1</v>
       </c>
       <c r="Z104" t="n">
         <v>1</v>
       </c>
-      <c r="AA104" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>1</v>
-      </c>
       <c r="AD104" t="n">
         <v>1</v>
       </c>
-      <c r="AE104" t="n">
-        <v>1</v>
-      </c>
       <c r="AF104" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
@@ -8461,7 +8419,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Inmunidad activa, pasiva y vacunas</t>
+          <t>La célula como unidad de la vida</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8470,25 +8428,37 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D105" t="n">
         <v>9</v>
       </c>
+      <c r="E105" t="n">
+        <v>7</v>
+      </c>
       <c r="F105" t="n">
         <v>8</v>
       </c>
       <c r="G105" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H105" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="I105" t="n">
+        <v>7</v>
+      </c>
+      <c r="J105" t="n">
+        <v>4.5</v>
       </c>
       <c r="K105" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L105" t="n">
-        <v>9.5</v>
+        <v>5</v>
+      </c>
+      <c r="M105" t="n">
+        <v>4.5</v>
       </c>
       <c r="O105" t="n">
         <v>1</v>
@@ -8496,29 +8466,50 @@
       <c r="P105" t="n">
         <v>1</v>
       </c>
+      <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1</v>
+      </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="n">
         <v>1</v>
       </c>
+      <c r="V105" t="n">
+        <v>1</v>
+      </c>
       <c r="W105" t="n">
         <v>1</v>
       </c>
+      <c r="X105" t="n">
+        <v>1</v>
+      </c>
       <c r="Y105" t="n">
         <v>1</v>
       </c>
       <c r="Z105" t="n">
         <v>1</v>
       </c>
+      <c r="AA105" t="n">
+        <v>1</v>
+      </c>
       <c r="AB105" t="n">
         <v>1</v>
       </c>
+      <c r="AC105" t="n">
+        <v>1</v>
+      </c>
       <c r="AD105" t="n">
         <v>1</v>
       </c>
+      <c r="AE105" t="n">
+        <v>1</v>
+      </c>
       <c r="AF105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
@@ -8527,14 +8518,14 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>no_retomado</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Intercambio de gases en plantas</t>
+          <t>Mecanismos de microevolución</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8543,43 +8534,52 @@
         </is>
       </c>
       <c r="C106" t="n">
+        <v>7</v>
+      </c>
+      <c r="D106" t="n">
+        <v>9</v>
+      </c>
+      <c r="F106" t="n">
         <v>8</v>
       </c>
-      <c r="D106" t="n">
-        <v>10</v>
-      </c>
-      <c r="G106" t="n">
-        <v>6</v>
-      </c>
-      <c r="I106" t="n">
+      <c r="L106" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="M106" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="U106" t="n">
+        <v>1</v>
+      </c>
+      <c r="V106" t="n">
+        <v>1</v>
+      </c>
+      <c r="W106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF106" t="n">
         <v>7</v>
-      </c>
-      <c r="J106" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L106" t="n">
-        <v>5</v>
-      </c>
-      <c r="P106" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" t="n">
-        <v>1</v>
-      </c>
-      <c r="W106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>8</v>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mecanismos de microevolución</t>
+          <t>Medidas de biodiversidad</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8607,25 +8607,13 @@
         <v>7</v>
       </c>
       <c r="D107" t="n">
-        <v>9</v>
-      </c>
-      <c r="F107" t="n">
-        <v>8</v>
-      </c>
-      <c r="L107" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M107" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
-      <c r="U107" t="n">
-        <v>1</v>
-      </c>
-      <c r="V107" t="n">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="G107" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H107" t="n">
+        <v>7</v>
       </c>
       <c r="W107" t="n">
         <v>1</v>
@@ -8636,13 +8624,7 @@
       <c r="Z107" t="n">
         <v>1</v>
       </c>
-      <c r="AA107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD107" t="n">
+      <c r="AB107" t="n">
         <v>1</v>
       </c>
       <c r="AE107" t="n">
@@ -8665,7 +8647,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Medidas de biodiversidad</t>
+          <t>Meiosis</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8674,17 +8656,44 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D108" t="n">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="E108" t="n">
+        <v>9</v>
+      </c>
+      <c r="F108" t="n">
+        <v>8</v>
       </c>
       <c r="G108" t="n">
         <v>8.5</v>
       </c>
-      <c r="H108" t="n">
+      <c r="J108" t="n">
         <v>7</v>
       </c>
+      <c r="L108" t="n">
+        <v>11</v>
+      </c>
+      <c r="M108" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="N108" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="P108" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" t="n">
+        <v>1</v>
+      </c>
+      <c r="V108" t="n">
+        <v>1</v>
+      </c>
       <c r="W108" t="n">
         <v>1</v>
       </c>
@@ -8694,14 +8703,23 @@
       <c r="Z108" t="n">
         <v>1</v>
       </c>
+      <c r="AA108" t="n">
+        <v>1</v>
+      </c>
       <c r="AB108" t="n">
         <v>1</v>
       </c>
+      <c r="AC108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>1</v>
+      </c>
       <c r="AE108" t="n">
         <v>1</v>
       </c>
       <c r="AF108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG108" t="inlineStr">
         <is>
@@ -8717,7 +8735,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Meiosis</t>
+          <t>Membrana celular</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8731,39 +8749,33 @@
       <c r="D109" t="n">
         <v>9</v>
       </c>
-      <c r="E109" t="n">
+      <c r="F109" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G109" t="n">
+        <v>6</v>
+      </c>
+      <c r="J109" t="n">
         <v>9</v>
       </c>
-      <c r="F109" t="n">
-        <v>8</v>
-      </c>
-      <c r="G109" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J109" t="n">
+      <c r="K109" t="n">
         <v>7</v>
       </c>
       <c r="L109" t="n">
-        <v>11</v>
-      </c>
-      <c r="M109" t="n">
         <v>9.5</v>
       </c>
-      <c r="N109" t="n">
-        <v>1</v>
-      </c>
       <c r="O109" t="n">
         <v>1</v>
       </c>
       <c r="P109" t="n">
         <v>1</v>
       </c>
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
       <c r="U109" t="n">
         <v>1</v>
       </c>
-      <c r="V109" t="n">
-        <v>1</v>
-      </c>
       <c r="W109" t="n">
         <v>1</v>
       </c>
@@ -8771,9 +8783,6 @@
         <v>1</v>
       </c>
       <c r="Z109" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA109" t="n">
         <v>1</v>
       </c>
       <c r="AB109" t="n">
@@ -8805,7 +8814,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Membrana celular</t>
+          <t>Microorganismos</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8814,32 +8823,41 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D110" t="n">
         <v>9</v>
       </c>
       <c r="F110" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="G110" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>8</v>
       </c>
       <c r="J110" t="n">
-        <v>9</v>
-      </c>
-      <c r="K110" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L110" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M110" t="n">
         <v>7</v>
       </c>
-      <c r="L110" t="n">
-        <v>9.5</v>
-      </c>
       <c r="O110" t="n">
         <v>1</v>
       </c>
       <c r="P110" t="n">
         <v>1</v>
       </c>
+      <c r="R110" t="n">
+        <v>1</v>
+      </c>
       <c r="S110" t="n">
         <v>1</v>
       </c>
@@ -8855,20 +8873,11 @@
       <c r="Z110" t="n">
         <v>1</v>
       </c>
-      <c r="AB110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC110" t="n">
-        <v>1</v>
-      </c>
       <c r="AD110" t="n">
         <v>1</v>
       </c>
-      <c r="AE110" t="n">
-        <v>1</v>
-      </c>
       <c r="AF110" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
@@ -8884,7 +8893,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Microorganismos</t>
+          <t>Mitosis y ciclo celular</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8893,25 +8902,31 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
         <v>9</v>
       </c>
+      <c r="E111" t="n">
+        <v>9</v>
+      </c>
       <c r="F111" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="G111" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I111" t="n">
         <v>8</v>
       </c>
       <c r="J111" t="n">
-        <v>2.5</v>
+        <v>7</v>
+      </c>
+      <c r="K111" t="n">
+        <v>7</v>
       </c>
       <c r="L111" t="n">
         <v>7.5</v>
@@ -8919,6 +8934,9 @@
       <c r="M111" t="n">
         <v>7</v>
       </c>
+      <c r="N111" t="n">
+        <v>1</v>
+      </c>
       <c r="O111" t="n">
         <v>1</v>
       </c>
@@ -8928,12 +8946,15 @@
       <c r="R111" t="n">
         <v>1</v>
       </c>
-      <c r="S111" t="n">
+      <c r="T111" t="n">
         <v>1</v>
       </c>
       <c r="U111" t="n">
         <v>1</v>
       </c>
+      <c r="V111" t="n">
+        <v>1</v>
+      </c>
       <c r="W111" t="n">
         <v>1</v>
       </c>
@@ -8943,11 +8964,17 @@
       <c r="Z111" t="n">
         <v>1</v>
       </c>
+      <c r="AB111" t="n">
+        <v>1</v>
+      </c>
       <c r="AD111" t="n">
         <v>1</v>
       </c>
+      <c r="AE111" t="n">
+        <v>1</v>
+      </c>
       <c r="AF111" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
@@ -8963,7 +8990,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mitosis y ciclo celular</t>
+          <t>Modelos ecológicos basados en muestreo</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8972,79 +8999,34 @@
         </is>
       </c>
       <c r="C112" t="n">
+        <v>7</v>
+      </c>
+      <c r="D112" t="n">
+        <v>11</v>
+      </c>
+      <c r="G112" t="n">
         <v>6</v>
       </c>
-      <c r="D112" t="n">
-        <v>9</v>
-      </c>
-      <c r="E112" t="n">
-        <v>9</v>
-      </c>
-      <c r="F112" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G112" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H112" t="n">
+      <c r="P112" t="n">
+        <v>1</v>
+      </c>
+      <c r="W112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" t="n">
         <v>7</v>
-      </c>
-      <c r="I112" t="n">
-        <v>8</v>
-      </c>
-      <c r="J112" t="n">
-        <v>7</v>
-      </c>
-      <c r="K112" t="n">
-        <v>7</v>
-      </c>
-      <c r="L112" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="M112" t="n">
-        <v>7</v>
-      </c>
-      <c r="N112" t="n">
-        <v>1</v>
-      </c>
-      <c r="O112" t="n">
-        <v>1</v>
-      </c>
-      <c r="P112" t="n">
-        <v>1</v>
-      </c>
-      <c r="R112" t="n">
-        <v>1</v>
-      </c>
-      <c r="T112" t="n">
-        <v>1</v>
-      </c>
-      <c r="U112" t="n">
-        <v>1</v>
-      </c>
-      <c r="V112" t="n">
-        <v>1</v>
-      </c>
-      <c r="W112" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF112" t="n">
-        <v>6</v>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
@@ -9060,7 +9042,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Modelos ecológicos basados en muestreo</t>
+          <t>Nicho ecológico y exclusión competitiva</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9069,13 +9051,22 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
         <v>11</v>
       </c>
+      <c r="F113" t="n">
+        <v>10.5</v>
+      </c>
       <c r="G113" t="n">
-        <v>6</v>
+        <v>8.5</v>
+      </c>
+      <c r="M113" t="n">
+        <v>7</v>
+      </c>
+      <c r="O113" t="n">
+        <v>1</v>
       </c>
       <c r="P113" t="n">
         <v>1</v>
@@ -9083,20 +9074,20 @@
       <c r="W113" t="n">
         <v>1</v>
       </c>
-      <c r="Y113" t="n">
-        <v>1</v>
-      </c>
       <c r="Z113" t="n">
         <v>1</v>
       </c>
+      <c r="AA113" t="n">
+        <v>1</v>
+      </c>
       <c r="AB113" t="n">
         <v>1</v>
       </c>
-      <c r="AC113" t="n">
+      <c r="AD113" t="n">
         <v>1</v>
       </c>
       <c r="AF113" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
@@ -9112,7 +9103,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Nicho ecológico y exclusión competitiva</t>
+          <t>Niveles de organización de los seres vivos</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9124,16 +9115,31 @@
         <v>4</v>
       </c>
       <c r="D114" t="n">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E114" t="n">
+        <v>7</v>
       </c>
       <c r="F114" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="G114" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H114" t="n">
+        <v>7</v>
+      </c>
+      <c r="J114" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K114" t="n">
+        <v>7</v>
+      </c>
+      <c r="L114" t="n">
+        <v>4.5</v>
       </c>
       <c r="M114" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
@@ -9141,19 +9147,34 @@
       <c r="P114" t="n">
         <v>1</v>
       </c>
+      <c r="T114" t="n">
+        <v>1</v>
+      </c>
+      <c r="U114" t="n">
+        <v>1</v>
+      </c>
+      <c r="V114" t="n">
+        <v>1</v>
+      </c>
       <c r="W114" t="n">
         <v>1</v>
       </c>
+      <c r="Y114" t="n">
+        <v>1</v>
+      </c>
       <c r="Z114" t="n">
         <v>1</v>
       </c>
-      <c r="AA114" t="n">
-        <v>1</v>
-      </c>
       <c r="AB114" t="n">
         <v>1</v>
       </c>
+      <c r="AC114" t="n">
+        <v>1</v>
+      </c>
       <c r="AD114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE114" t="n">
         <v>1</v>
       </c>
       <c r="AF114" t="n">
@@ -9173,7 +9194,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Niveles de organización de los seres vivos</t>
+          <t>Niveles de organización ecológica</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9185,28 +9206,28 @@
         <v>4</v>
       </c>
       <c r="D115" t="n">
-        <v>10</v>
-      </c>
-      <c r="E115" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F115" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G115" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3</v>
+      </c>
+      <c r="I115" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K115" t="n">
+        <v>3</v>
+      </c>
+      <c r="L115" t="n">
         <v>6</v>
-      </c>
-      <c r="H115" t="n">
-        <v>7</v>
-      </c>
-      <c r="J115" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K115" t="n">
-        <v>7</v>
-      </c>
-      <c r="L115" t="n">
-        <v>4.5</v>
       </c>
       <c r="M115" t="n">
         <v>4.5</v>
@@ -9217,13 +9238,7 @@
       <c r="P115" t="n">
         <v>1</v>
       </c>
-      <c r="T115" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" t="n">
-        <v>1</v>
-      </c>
-      <c r="V115" t="n">
+      <c r="R115" t="n">
         <v>1</v>
       </c>
       <c r="W115" t="n">
@@ -9264,7 +9279,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Niveles de organización ecológica</t>
+          <t>Nutrición autótrofa y heterótrofa</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9273,67 +9288,52 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F116" t="n">
         <v>2.5</v>
       </c>
       <c r="G116" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
-        <v>3</v>
-      </c>
-      <c r="I116" t="n">
-        <v>9.5</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>2.5</v>
       </c>
       <c r="K116" t="n">
+        <v>2</v>
+      </c>
+      <c r="L116" t="n">
+        <v>5</v>
+      </c>
+      <c r="M116" t="n">
+        <v>7</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF116" t="n">
         <v>3</v>
-      </c>
-      <c r="L116" t="n">
-        <v>6</v>
-      </c>
-      <c r="M116" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O116" t="n">
-        <v>1</v>
-      </c>
-      <c r="P116" t="n">
-        <v>1</v>
-      </c>
-      <c r="R116" t="n">
-        <v>1</v>
-      </c>
-      <c r="W116" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE116" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF116" t="n">
-        <v>4</v>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Nutrición autótrofa y heterótrofa</t>
+          <t>Nutrientes y sus funciones</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9358,31 +9358,22 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D117" t="n">
         <v>9</v>
       </c>
       <c r="F117" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H117" t="n">
         <v>2</v>
       </c>
-      <c r="J117" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K117" t="n">
-        <v>2</v>
-      </c>
       <c r="L117" t="n">
-        <v>5</v>
-      </c>
-      <c r="M117" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="O117" t="n">
         <v>1</v>
@@ -9393,17 +9384,23 @@
       <c r="U117" t="n">
         <v>1</v>
       </c>
+      <c r="X117" t="n">
+        <v>1</v>
+      </c>
       <c r="Y117" t="n">
         <v>1</v>
       </c>
       <c r="Z117" t="n">
         <v>1</v>
       </c>
+      <c r="AC117" t="n">
+        <v>1</v>
+      </c>
       <c r="AD117" t="n">
         <v>1</v>
       </c>
       <c r="AF117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
@@ -9419,7 +9416,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nutrientes y sus funciones</t>
+          <t>Órganos de los sentidos</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9431,19 +9428,28 @@
         <v>4</v>
       </c>
       <c r="D118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F118" t="n">
         <v>8</v>
       </c>
       <c r="G118" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H118" t="n">
         <v>2</v>
       </c>
-      <c r="L118" t="n">
-        <v>7.5</v>
+      <c r="I118" t="n">
+        <v>7</v>
+      </c>
+      <c r="J118" t="n">
+        <v>7</v>
+      </c>
+      <c r="K118" t="n">
+        <v>2</v>
+      </c>
+      <c r="M118" t="n">
+        <v>2.5</v>
       </c>
       <c r="O118" t="n">
         <v>1</v>
@@ -9451,22 +9457,16 @@
       <c r="P118" t="n">
         <v>1</v>
       </c>
-      <c r="U118" t="n">
-        <v>1</v>
-      </c>
-      <c r="X118" t="n">
-        <v>1</v>
-      </c>
       <c r="Y118" t="n">
         <v>1</v>
       </c>
-      <c r="Z118" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC118" t="n">
+      <c r="AA118" t="n">
         <v>1</v>
       </c>
       <c r="AD118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE118" t="n">
         <v>1</v>
       </c>
       <c r="AF118" t="n">
@@ -9486,7 +9486,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Órganos de los sentidos</t>
+          <t>PCR y electroforesis en gel</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9495,52 +9495,40 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D119" t="n">
-        <v>10</v>
-      </c>
-      <c r="F119" t="n">
-        <v>8</v>
-      </c>
-      <c r="G119" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H119" t="n">
-        <v>2</v>
-      </c>
-      <c r="I119" t="n">
         <v>7</v>
       </c>
-      <c r="J119" t="n">
+      <c r="W119" t="n">
+        <v>1</v>
+      </c>
+      <c r="X119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF119" t="n">
         <v>7</v>
-      </c>
-      <c r="K119" t="n">
-        <v>2</v>
-      </c>
-      <c r="M119" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O119" t="n">
-        <v>1</v>
-      </c>
-      <c r="P119" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF119" t="n">
-        <v>4</v>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
@@ -9556,7 +9544,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PCR y electroforesis en gel</t>
+          <t>Productores, consumidores y descomponedores</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9565,18 +9553,51 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
         <v>9</v>
       </c>
+      <c r="E120" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2</v>
+      </c>
       <c r="H120" t="n">
+        <v>3</v>
+      </c>
+      <c r="I120" t="n">
+        <v>8</v>
+      </c>
+      <c r="J120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2</v>
+      </c>
+      <c r="L120" t="n">
+        <v>6</v>
+      </c>
+      <c r="M120" t="n">
         <v>7</v>
       </c>
-      <c r="W120" t="n">
-        <v>1</v>
-      </c>
-      <c r="X120" t="n">
+      <c r="O120" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="U120" t="n">
         <v>1</v>
       </c>
       <c r="Y120" t="n">
@@ -9588,17 +9609,17 @@
       <c r="AA120" t="n">
         <v>1</v>
       </c>
+      <c r="AB120" t="n">
+        <v>1</v>
+      </c>
       <c r="AC120" t="n">
         <v>1</v>
       </c>
       <c r="AD120" t="n">
         <v>1</v>
       </c>
-      <c r="AE120" t="n">
-        <v>1</v>
-      </c>
       <c r="AF120" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG120" t="inlineStr">
         <is>
@@ -9614,7 +9635,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Productores, consumidores y descomponedores</t>
+          <t>Proteínas: estructura y función</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9623,73 +9644,70 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D121" t="n">
         <v>9</v>
       </c>
-      <c r="E121" t="n">
-        <v>3</v>
-      </c>
       <c r="F121" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
-      </c>
-      <c r="H121" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="I121" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="J121" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K121" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L121" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" t="n">
+        <v>1</v>
+      </c>
+      <c r="W121" t="n">
+        <v>1</v>
+      </c>
+      <c r="X121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF121" t="n">
         <v>6</v>
-      </c>
-      <c r="M121" t="n">
-        <v>7</v>
-      </c>
-      <c r="O121" t="n">
-        <v>1</v>
-      </c>
-      <c r="P121" t="n">
-        <v>1</v>
-      </c>
-      <c r="R121" t="n">
-        <v>1</v>
-      </c>
-      <c r="S121" t="n">
-        <v>1</v>
-      </c>
-      <c r="U121" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF121" t="n">
-        <v>3</v>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
@@ -9705,7 +9723,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Proteínas: estructura y función</t>
+          <t>Redes tróficas</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9714,25 +9732,37 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D122" t="n">
         <v>9</v>
       </c>
+      <c r="E122" t="n">
+        <v>6</v>
+      </c>
       <c r="F122" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="G122" t="n">
-        <v>8.5</v>
+        <v>6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>7</v>
       </c>
       <c r="I122" t="n">
         <v>9.5</v>
       </c>
       <c r="J122" t="n">
-        <v>9</v>
+        <v>2.5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3</v>
       </c>
       <c r="L122" t="n">
-        <v>9.5</v>
+        <v>6</v>
+      </c>
+      <c r="M122" t="n">
+        <v>4.5</v>
       </c>
       <c r="O122" t="n">
         <v>1</v>
@@ -9752,32 +9782,20 @@
       <c r="W122" t="n">
         <v>1</v>
       </c>
-      <c r="X122" t="n">
-        <v>1</v>
-      </c>
       <c r="Y122" t="n">
         <v>1</v>
       </c>
       <c r="Z122" t="n">
         <v>1</v>
       </c>
-      <c r="AA122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>1</v>
-      </c>
       <c r="AC122" t="n">
         <v>1</v>
       </c>
       <c r="AD122" t="n">
         <v>1</v>
       </c>
-      <c r="AE122" t="n">
-        <v>1</v>
-      </c>
       <c r="AF122" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
@@ -9793,7 +9811,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Redes tróficas</t>
+          <t>Replicación del ADN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9802,53 +9820,29 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D123" t="n">
         <v>9</v>
       </c>
-      <c r="E123" t="n">
-        <v>6</v>
-      </c>
-      <c r="F123" t="n">
-        <v>5</v>
-      </c>
-      <c r="G123" t="n">
-        <v>6</v>
-      </c>
-      <c r="H123" t="n">
-        <v>7</v>
-      </c>
       <c r="I123" t="n">
         <v>9.5</v>
       </c>
-      <c r="J123" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K123" t="n">
-        <v>3</v>
-      </c>
       <c r="L123" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M123" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O123" t="n">
-        <v>1</v>
-      </c>
-      <c r="P123" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="R123" t="n">
         <v>1</v>
       </c>
-      <c r="S123" t="n">
-        <v>1</v>
-      </c>
       <c r="U123" t="n">
         <v>1</v>
       </c>
+      <c r="V123" t="n">
+        <v>1</v>
+      </c>
       <c r="W123" t="n">
         <v>1</v>
       </c>
@@ -9858,14 +9852,23 @@
       <c r="Z123" t="n">
         <v>1</v>
       </c>
+      <c r="AA123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>1</v>
+      </c>
       <c r="AC123" t="n">
         <v>1</v>
       </c>
       <c r="AD123" t="n">
         <v>1</v>
       </c>
+      <c r="AE123" t="n">
+        <v>1</v>
+      </c>
       <c r="AF123" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
@@ -9881,7 +9884,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Replicación del ADN</t>
+          <t>Reproducción sexual y asexual</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9890,21 +9893,42 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D124" t="n">
         <v>9</v>
       </c>
+      <c r="E124" t="n">
+        <v>8</v>
+      </c>
+      <c r="F124" t="n">
+        <v>8</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3</v>
+      </c>
       <c r="I124" t="n">
-        <v>9.5</v>
+        <v>8</v>
+      </c>
+      <c r="K124" t="n">
+        <v>9</v>
       </c>
       <c r="L124" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M124" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R124" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O124" t="n">
+        <v>1</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1</v>
+      </c>
+      <c r="T124" t="n">
         <v>1</v>
       </c>
       <c r="U124" t="n">
@@ -9922,12 +9946,6 @@
       <c r="Z124" t="n">
         <v>1</v>
       </c>
-      <c r="AA124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>1</v>
-      </c>
       <c r="AC124" t="n">
         <v>1</v>
       </c>
@@ -9938,7 +9956,7 @@
         <v>1</v>
       </c>
       <c r="AF124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
@@ -9954,7 +9972,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Reproducción sexual y asexual</t>
+          <t>Respiración celular</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9972,25 +9990,28 @@
         <v>8</v>
       </c>
       <c r="F125" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H125" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I125" t="n">
-        <v>8</v>
+        <v>9.5</v>
+      </c>
+      <c r="J125" t="n">
+        <v>7</v>
       </c>
       <c r="K125" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M125" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
@@ -9998,7 +10019,7 @@
       <c r="P125" t="n">
         <v>1</v>
       </c>
-      <c r="T125" t="n">
+      <c r="R125" t="n">
         <v>1</v>
       </c>
       <c r="U125" t="n">
@@ -10010,10 +10031,19 @@
       <c r="W125" t="n">
         <v>1</v>
       </c>
+      <c r="X125" t="n">
+        <v>1</v>
+      </c>
       <c r="Y125" t="n">
         <v>1</v>
       </c>
       <c r="Z125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB125" t="n">
         <v>1</v>
       </c>
       <c r="AC125" t="n">
@@ -10042,7 +10072,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Respiración celular</t>
+          <t>Respuesta de los seres vivos a estímulos</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10051,37 +10081,34 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E126" t="n">
         <v>8</v>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G126" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="H126" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J126" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K126" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L126" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M126" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
@@ -10089,21 +10116,9 @@
       <c r="P126" t="n">
         <v>1</v>
       </c>
-      <c r="R126" t="n">
-        <v>1</v>
-      </c>
-      <c r="U126" t="n">
-        <v>1</v>
-      </c>
-      <c r="V126" t="n">
-        <v>1</v>
-      </c>
       <c r="W126" t="n">
         <v>1</v>
       </c>
-      <c r="X126" t="n">
-        <v>1</v>
-      </c>
       <c r="Y126" t="n">
         <v>1</v>
       </c>
@@ -10113,9 +10128,6 @@
       <c r="AA126" t="n">
         <v>1</v>
       </c>
-      <c r="AB126" t="n">
-        <v>1</v>
-      </c>
       <c r="AC126" t="n">
         <v>1</v>
       </c>
@@ -10126,7 +10138,7 @@
         <v>1</v>
       </c>
       <c r="AF126" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
@@ -10142,7 +10154,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Respuesta de los seres vivos a estímulos</t>
+          <t>Selección artificial</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10154,57 +10166,24 @@
         <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>10</v>
-      </c>
-      <c r="E127" t="n">
-        <v>8</v>
-      </c>
-      <c r="F127" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G127" t="n">
         <v>8.5</v>
       </c>
-      <c r="H127" t="n">
-        <v>2</v>
-      </c>
-      <c r="I127" t="n">
-        <v>3</v>
-      </c>
-      <c r="K127" t="n">
-        <v>2</v>
-      </c>
-      <c r="L127" t="n">
-        <v>3</v>
-      </c>
       <c r="M127" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O127" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
       </c>
-      <c r="W127" t="n">
-        <v>1</v>
-      </c>
       <c r="Y127" t="n">
         <v>1</v>
       </c>
       <c r="Z127" t="n">
         <v>1</v>
       </c>
-      <c r="AA127" t="n">
-        <v>1</v>
-      </c>
       <c r="AC127" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE127" t="n">
         <v>1</v>
       </c>
       <c r="AF127" t="n">
@@ -10224,7 +10203,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Selección artificial</t>
+          <t>Simbiosis: mutualismo, comensalismo y parasitismo</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10233,31 +10212,70 @@
         </is>
       </c>
       <c r="C128" t="n">
+        <v>4</v>
+      </c>
+      <c r="D128" t="n">
+        <v>10</v>
+      </c>
+      <c r="F128" t="n">
+        <v>8</v>
+      </c>
+      <c r="G128" t="n">
+        <v>6</v>
+      </c>
+      <c r="H128" t="n">
+        <v>7</v>
+      </c>
+      <c r="I128" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J128" t="n">
+        <v>9</v>
+      </c>
+      <c r="K128" t="n">
         <v>2</v>
       </c>
-      <c r="D128" t="n">
-        <v>9</v>
-      </c>
-      <c r="G128" t="n">
-        <v>8.5</v>
+      <c r="L128" t="n">
+        <v>7.5</v>
       </c>
       <c r="M128" t="n">
         <v>4.5</v>
       </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
       <c r="P128" t="n">
         <v>1</v>
       </c>
+      <c r="R128" t="n">
+        <v>1</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1</v>
+      </c>
+      <c r="W128" t="n">
+        <v>1</v>
+      </c>
       <c r="Y128" t="n">
         <v>1</v>
       </c>
       <c r="Z128" t="n">
         <v>1</v>
       </c>
+      <c r="AA128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>1</v>
+      </c>
       <c r="AC128" t="n">
         <v>1</v>
       </c>
+      <c r="AE128" t="n">
+        <v>1</v>
+      </c>
       <c r="AF128" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
@@ -10273,7 +10291,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Simbiosis: mutualismo, comensalismo y parasitismo</t>
+          <t>Síntesis de proteínas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10282,19 +10300,13 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D129" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F129" t="n">
-        <v>8</v>
-      </c>
-      <c r="G129" t="n">
-        <v>6</v>
-      </c>
-      <c r="H129" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="I129" t="n">
         <v>9.5</v>
@@ -10302,27 +10314,27 @@
       <c r="J129" t="n">
         <v>9</v>
       </c>
-      <c r="K129" t="n">
-        <v>2</v>
-      </c>
       <c r="L129" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="M129" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="O129" t="n">
         <v>1</v>
       </c>
-      <c r="P129" t="n">
-        <v>1</v>
-      </c>
       <c r="R129" t="n">
         <v>1</v>
       </c>
       <c r="S129" t="n">
         <v>1</v>
       </c>
+      <c r="U129" t="n">
+        <v>1</v>
+      </c>
+      <c r="V129" t="n">
+        <v>1</v>
+      </c>
       <c r="W129" t="n">
         <v>1</v>
       </c>
@@ -10341,11 +10353,14 @@
       <c r="AC129" t="n">
         <v>1</v>
       </c>
+      <c r="AD129" t="n">
+        <v>1</v>
+      </c>
       <c r="AE129" t="n">
         <v>1</v>
       </c>
       <c r="AF129" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
@@ -10361,7 +10376,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Síntesis de proteínas</t>
+          <t>Sistema circulatorio</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10370,41 +10385,50 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D130" t="n">
         <v>9</v>
       </c>
       <c r="F130" t="n">
-        <v>10.5</v>
+        <v>8</v>
+      </c>
+      <c r="G130" t="n">
+        <v>4</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2</v>
       </c>
       <c r="I130" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J130" t="n">
-        <v>9</v>
+        <v>4.5</v>
+      </c>
+      <c r="K130" t="n">
+        <v>4</v>
       </c>
       <c r="L130" t="n">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="M130" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O130" t="n">
         <v>1</v>
       </c>
+      <c r="P130" t="n">
+        <v>1</v>
+      </c>
       <c r="R130" t="n">
         <v>1</v>
       </c>
-      <c r="S130" t="n">
+      <c r="T130" t="n">
         <v>1</v>
       </c>
       <c r="U130" t="n">
         <v>1</v>
       </c>
-      <c r="V130" t="n">
-        <v>1</v>
-      </c>
       <c r="W130" t="n">
         <v>1</v>
       </c>
@@ -10414,9 +10438,6 @@
       <c r="Z130" t="n">
         <v>1</v>
       </c>
-      <c r="AA130" t="n">
-        <v>1</v>
-      </c>
       <c r="AB130" t="n">
         <v>1</v>
       </c>
@@ -10426,11 +10447,8 @@
       <c r="AD130" t="n">
         <v>1</v>
       </c>
-      <c r="AE130" t="n">
-        <v>1</v>
-      </c>
       <c r="AF130" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
@@ -10446,7 +10464,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sistema circulatorio</t>
+          <t>Sistema nervioso</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10460,29 +10478,29 @@
       <c r="D131" t="n">
         <v>9</v>
       </c>
+      <c r="E131" t="n">
+        <v>8</v>
+      </c>
       <c r="F131" t="n">
         <v>8</v>
       </c>
       <c r="G131" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I131" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J131" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="K131" t="n">
         <v>4</v>
       </c>
-      <c r="L131" t="n">
-        <v>4</v>
-      </c>
       <c r="M131" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O131" t="n">
         <v>1</v>
@@ -10496,18 +10514,21 @@
       <c r="T131" t="n">
         <v>1</v>
       </c>
-      <c r="U131" t="n">
-        <v>1</v>
-      </c>
       <c r="W131" t="n">
         <v>1</v>
       </c>
+      <c r="X131" t="n">
+        <v>1</v>
+      </c>
       <c r="Y131" t="n">
         <v>1</v>
       </c>
       <c r="Z131" t="n">
         <v>1</v>
       </c>
+      <c r="AA131" t="n">
+        <v>1</v>
+      </c>
       <c r="AB131" t="n">
         <v>1</v>
       </c>
@@ -10515,6 +10536,9 @@
         <v>1</v>
       </c>
       <c r="AD131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE131" t="n">
         <v>1</v>
       </c>
       <c r="AF131" t="n">
@@ -10534,7 +10558,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sistema nervioso</t>
+          <t>Sistema respiratorio</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10543,62 +10567,53 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D132" t="n">
-        <v>9</v>
-      </c>
-      <c r="E132" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F132" t="n">
         <v>8</v>
       </c>
       <c r="G132" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="H132" t="n">
+        <v>2</v>
+      </c>
+      <c r="I132" t="n">
         <v>5</v>
       </c>
-      <c r="I132" t="n">
-        <v>7</v>
-      </c>
       <c r="J132" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K132" t="n">
         <v>4</v>
       </c>
+      <c r="L132" t="n">
+        <v>4</v>
+      </c>
       <c r="M132" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="P132" t="n">
-        <v>1</v>
-      </c>
-      <c r="R132" t="n">
-        <v>1</v>
-      </c>
       <c r="T132" t="n">
         <v>1</v>
       </c>
+      <c r="U132" t="n">
+        <v>1</v>
+      </c>
       <c r="W132" t="n">
         <v>1</v>
       </c>
-      <c r="X132" t="n">
-        <v>1</v>
-      </c>
       <c r="Y132" t="n">
         <v>1</v>
       </c>
       <c r="Z132" t="n">
         <v>1</v>
       </c>
-      <c r="AA132" t="n">
-        <v>1</v>
-      </c>
       <c r="AB132" t="n">
         <v>1</v>
       </c>
@@ -10606,9 +10621,6 @@
         <v>1</v>
       </c>
       <c r="AD132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE132" t="n">
         <v>1</v>
       </c>
       <c r="AF132" t="n">
@@ -10628,7 +10640,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sistema respiratorio</t>
+          <t>Sostenibilidad de la biosfera</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10637,39 +10649,42 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G133" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H133" t="n">
+        <v>4</v>
+      </c>
+      <c r="I133" t="n">
         <v>8</v>
       </c>
-      <c r="G133" t="n">
-        <v>6</v>
-      </c>
-      <c r="H133" t="n">
+      <c r="J133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K133" t="n">
         <v>2</v>
       </c>
-      <c r="I133" t="n">
-        <v>5</v>
-      </c>
-      <c r="J133" t="n">
+      <c r="L133" t="n">
         <v>4.5</v>
       </c>
-      <c r="K133" t="n">
-        <v>4</v>
-      </c>
-      <c r="L133" t="n">
-        <v>4</v>
-      </c>
       <c r="M133" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O133" t="n">
         <v>1</v>
       </c>
-      <c r="T133" t="n">
+      <c r="P133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
         <v>1</v>
       </c>
       <c r="U133" t="n">
@@ -10678,13 +10693,16 @@
       <c r="W133" t="n">
         <v>1</v>
       </c>
+      <c r="X133" t="n">
+        <v>1</v>
+      </c>
       <c r="Y133" t="n">
         <v>1</v>
       </c>
       <c r="Z133" t="n">
         <v>1</v>
       </c>
-      <c r="AB133" t="n">
+      <c r="AA133" t="n">
         <v>1</v>
       </c>
       <c r="AC133" t="n">
@@ -10694,7 +10712,7 @@
         <v>1</v>
       </c>
       <c r="AF133" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG133" t="inlineStr">
         <is>
@@ -10710,7 +10728,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sostenibilidad de la biosfera</t>
+          <t>Sucesión ecológica</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10719,70 +10737,46 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D134" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F134" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G134" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H134" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="I134" t="n">
-        <v>8</v>
-      </c>
-      <c r="J134" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="K134" t="n">
-        <v>2</v>
-      </c>
-      <c r="L134" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M134" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="P134" t="n">
-        <v>1</v>
-      </c>
-      <c r="S134" t="n">
-        <v>1</v>
-      </c>
-      <c r="U134" t="n">
+      <c r="R134" t="n">
         <v>1</v>
       </c>
       <c r="W134" t="n">
         <v>1</v>
       </c>
-      <c r="X134" t="n">
-        <v>1</v>
-      </c>
       <c r="Y134" t="n">
         <v>1</v>
       </c>
       <c r="Z134" t="n">
         <v>1</v>
       </c>
-      <c r="AA134" t="n">
-        <v>1</v>
-      </c>
       <c r="AC134" t="n">
         <v>1</v>
       </c>
-      <c r="AD134" t="n">
+      <c r="AE134" t="n">
         <v>1</v>
       </c>
       <c r="AF134" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
@@ -10798,7 +10792,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sucesión ecológica</t>
+          <t>Tejidos animales</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10807,27 +10801,39 @@
         </is>
       </c>
       <c r="C135" t="n">
+        <v>6</v>
+      </c>
+      <c r="D135" t="n">
+        <v>9</v>
+      </c>
+      <c r="E135" t="n">
         <v>7</v>
       </c>
-      <c r="D135" t="n">
+      <c r="F135" t="n">
+        <v>8</v>
+      </c>
+      <c r="H135" t="n">
+        <v>7</v>
+      </c>
+      <c r="K135" t="n">
+        <v>9</v>
+      </c>
+      <c r="L135" t="n">
         <v>11</v>
       </c>
-      <c r="F135" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I135" t="n">
+      <c r="M135" t="n">
         <v>9.5</v>
       </c>
-      <c r="K135" t="n">
-        <v>5</v>
-      </c>
-      <c r="M135" t="n">
-        <v>7</v>
-      </c>
       <c r="O135" t="n">
         <v>1</v>
       </c>
-      <c r="R135" t="n">
+      <c r="T135" t="n">
+        <v>1</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" t="n">
         <v>1</v>
       </c>
       <c r="W135" t="n">
@@ -10839,14 +10845,14 @@
       <c r="Z135" t="n">
         <v>1</v>
       </c>
-      <c r="AC135" t="n">
+      <c r="AD135" t="n">
         <v>1</v>
       </c>
       <c r="AE135" t="n">
         <v>1</v>
       </c>
       <c r="AF135" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG135" t="inlineStr">
         <is>
@@ -10862,7 +10868,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Tejidos animales</t>
+          <t>Tejidos vegetales</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10871,7 +10877,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D136" t="n">
         <v>9</v>
@@ -10882,30 +10888,36 @@
       <c r="F136" t="n">
         <v>8</v>
       </c>
+      <c r="G136" t="n">
+        <v>8.5</v>
+      </c>
       <c r="H136" t="n">
         <v>7</v>
       </c>
+      <c r="J136" t="n">
+        <v>4.5</v>
+      </c>
       <c r="K136" t="n">
         <v>9</v>
       </c>
       <c r="L136" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="M136" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="O136" t="n">
         <v>1</v>
       </c>
+      <c r="P136" t="n">
+        <v>1</v>
+      </c>
       <c r="T136" t="n">
         <v>1</v>
       </c>
       <c r="U136" t="n">
         <v>1</v>
       </c>
-      <c r="V136" t="n">
-        <v>1</v>
-      </c>
       <c r="W136" t="n">
         <v>1</v>
       </c>
@@ -10915,6 +10927,9 @@
       <c r="Z136" t="n">
         <v>1</v>
       </c>
+      <c r="AC136" t="n">
+        <v>1</v>
+      </c>
       <c r="AD136" t="n">
         <v>1</v>
       </c>
@@ -10922,7 +10937,7 @@
         <v>1</v>
       </c>
       <c r="AF136" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG136" t="inlineStr">
         <is>
@@ -10938,7 +10953,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tejidos vegetales</t>
+          <t>Tipos de patógenos</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10947,14 +10962,11 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D137" t="n">
         <v>9</v>
       </c>
-      <c r="E137" t="n">
-        <v>7</v>
-      </c>
       <c r="F137" t="n">
         <v>8</v>
       </c>
@@ -10962,13 +10974,7 @@
         <v>8.5</v>
       </c>
       <c r="H137" t="n">
-        <v>7</v>
-      </c>
-      <c r="J137" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K137" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L137" t="n">
         <v>7.5</v>
@@ -10982,9 +10988,6 @@
       <c r="P137" t="n">
         <v>1</v>
       </c>
-      <c r="T137" t="n">
-        <v>1</v>
-      </c>
       <c r="U137" t="n">
         <v>1</v>
       </c>
@@ -10997,17 +11000,14 @@
       <c r="Z137" t="n">
         <v>1</v>
       </c>
-      <c r="AC137" t="n">
+      <c r="AB137" t="n">
         <v>1</v>
       </c>
       <c r="AD137" t="n">
         <v>1</v>
       </c>
-      <c r="AE137" t="n">
-        <v>1</v>
-      </c>
       <c r="AF137" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AG137" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tipos de patógenos</t>
+          <t>Transmisión de patógenos</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11046,39 +11046,39 @@
       <c r="H138" t="n">
         <v>3</v>
       </c>
+      <c r="J138" t="n">
+        <v>2.5</v>
+      </c>
       <c r="L138" t="n">
         <v>7.5</v>
       </c>
-      <c r="M138" t="n">
-        <v>7</v>
-      </c>
       <c r="O138" t="n">
         <v>1</v>
       </c>
       <c r="P138" t="n">
         <v>1</v>
       </c>
+      <c r="S138" t="n">
+        <v>1</v>
+      </c>
       <c r="U138" t="n">
         <v>1</v>
       </c>
       <c r="W138" t="n">
         <v>1</v>
       </c>
+      <c r="X138" t="n">
+        <v>1</v>
+      </c>
       <c r="Y138" t="n">
         <v>1</v>
       </c>
       <c r="Z138" t="n">
         <v>1</v>
       </c>
-      <c r="AB138" t="n">
-        <v>1</v>
-      </c>
       <c r="AD138" t="n">
         <v>1</v>
       </c>
-      <c r="AF138" t="n">
-        <v>3</v>
-      </c>
       <c r="AG138" t="inlineStr">
         <is>
           <t>retomado</t>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>retomado</t>
+          <t>faltante</t>
         </is>
       </c>
     </row>
